--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>38.71</v>
+        <v>44.0481</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>72192.55</v>
@@ -1843,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>9209.41</v>
+        <v>10082.96</v>
       </c>
       <c r="H33" s="5">
         <f>F33*G33</f>
@@ -1880,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>4586.47</v>
+        <v>4435.25</v>
       </c>
       <c r="H34" s="5">
         <f>F34*G34</f>
@@ -1917,7 +1917,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1402.96</v>
+        <v>1436.2</v>
       </c>
       <c r="H35" s="5">
         <f>F35*G35</f>
@@ -1954,7 +1954,7 @@
         <v>300</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>260.01</v>
+        <v>244.02</v>
       </c>
       <c r="H36" s="5">
         <f>F36*G36</f>
@@ -1991,7 +1991,7 @@
         <v>30</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>2594.89</v>
+        <v>2222.88</v>
       </c>
       <c r="H37" s="5">
         <f>F37*G37</f>
@@ -2028,7 +2028,7 @@
         <v>2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1782.25</v>
+        <v>1552.4</v>
       </c>
       <c r="H38" s="5">
         <f>F38*G38</f>
@@ -2065,7 +2065,7 @@
         <v>500</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>37.77</v>
+        <v>74.42</v>
       </c>
       <c r="H39" s="5">
         <f>F39*G39</f>
@@ -2102,7 +2102,7 @@
         <v>2000</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>25.35</v>
+        <v>33.1</v>
       </c>
       <c r="H40" s="5">
         <f>F40*G40</f>
@@ -2139,7 +2139,7 @@
         <v>600</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>15.88</v>
+        <v>23.56</v>
       </c>
       <c r="H41" s="5">
         <f>F41*G41</f>
@@ -2176,7 +2176,7 @@
         <v>100</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>204.16</v>
+        <v>188.13</v>
       </c>
       <c r="H42" s="5">
         <f>F42*G42</f>
@@ -2213,7 +2213,7 @@
         <v>186</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>150.75</v>
+        <v>156.11</v>
       </c>
       <c r="H43" s="5">
         <f>F43*G43</f>
@@ -2250,7 +2250,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>20274.29</v>
+        <v>17410.01</v>
       </c>
       <c r="H44" s="5">
         <f>F44*G44</f>
@@ -2287,7 +2287,7 @@
         <v>16</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>554.74</v>
+        <v>481.15</v>
       </c>
       <c r="H45" s="5">
         <f>F45*G45</f>
@@ -2324,7 +2324,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>607554.0699999999</v>
+        <v>484082.09</v>
       </c>
       <c r="H46" s="5">
         <f>F46*G46</f>
@@ -2361,7 +2361,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>103549.61</v>
+        <v>83282.35000000001</v>
       </c>
       <c r="H47" s="5">
         <f>F47*G47</f>
@@ -2398,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>50107.49</v>
+        <v>44709.81</v>
       </c>
       <c r="H48" s="5">
         <f>F48*G48</f>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>38.71</v>
+        <v>44.0481</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>72192.55</v>
@@ -3471,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>9209.41</v>
+        <v>10082.96</v>
       </c>
       <c r="H77" s="5">
         <f>F77*G77</f>
@@ -3508,7 +3508,7 @@
         <v>1</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>4586.47</v>
+        <v>4435.25</v>
       </c>
       <c r="H78" s="5">
         <f>F78*G78</f>
@@ -3545,7 +3545,7 @@
         <v>2</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1402.96</v>
+        <v>1436.2</v>
       </c>
       <c r="H79" s="5">
         <f>F79*G79</f>
@@ -3582,7 +3582,7 @@
         <v>300</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>260.01</v>
+        <v>244.02</v>
       </c>
       <c r="H80" s="5">
         <f>F80*G80</f>
@@ -3619,7 +3619,7 @@
         <v>30</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>2594.89</v>
+        <v>2222.88</v>
       </c>
       <c r="H81" s="5">
         <f>F81*G81</f>
@@ -3656,7 +3656,7 @@
         <v>2</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1782.25</v>
+        <v>1552.4</v>
       </c>
       <c r="H82" s="5">
         <f>F82*G82</f>
@@ -3693,7 +3693,7 @@
         <v>500</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>37.77</v>
+        <v>74.42</v>
       </c>
       <c r="H83" s="5">
         <f>F83*G83</f>
@@ -3730,7 +3730,7 @@
         <v>2000</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>25.35</v>
+        <v>33.1</v>
       </c>
       <c r="H84" s="5">
         <f>F84*G84</f>
@@ -3767,7 +3767,7 @@
         <v>600</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>15.88</v>
+        <v>23.56</v>
       </c>
       <c r="H85" s="5">
         <f>F85*G85</f>
@@ -3804,7 +3804,7 @@
         <v>100</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>204.16</v>
+        <v>188.13</v>
       </c>
       <c r="H86" s="5">
         <f>F86*G86</f>
@@ -3841,7 +3841,7 @@
         <v>186</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>150.75</v>
+        <v>156.11</v>
       </c>
       <c r="H87" s="5">
         <f>F87*G87</f>
@@ -3878,7 +3878,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>20274.29</v>
+        <v>17410.01</v>
       </c>
       <c r="H88" s="5">
         <f>F88*G88</f>
@@ -3915,7 +3915,7 @@
         <v>16</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>554.74</v>
+        <v>481.15</v>
       </c>
       <c r="H89" s="5">
         <f>F89*G89</f>
@@ -3952,7 +3952,7 @@
         <v>1</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>607554.0699999999</v>
+        <v>484082.09</v>
       </c>
       <c r="H90" s="5">
         <f>F90*G90</f>
@@ -3989,7 +3989,7 @@
         <v>1</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>103549.61</v>
+        <v>83282.35000000001</v>
       </c>
       <c r="H91" s="5">
         <f>F91*G91</f>
@@ -4026,7 +4026,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>50107.49</v>
+        <v>44709.81</v>
       </c>
       <c r="H92" s="5">
         <f>F92*G92</f>
@@ -5321,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>41083.03</v>
+        <v>41783.13</v>
       </c>
       <c r="H127" s="5">
         <f>F127*G127</f>
@@ -5358,7 +5358,7 @@
         <v>1</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>10633.02</v>
+        <v>11631.65</v>
       </c>
       <c r="H128" s="5">
         <f>F128*G128</f>
@@ -5395,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>1955.4</v>
+        <v>2218.15</v>
       </c>
       <c r="H129" s="5">
         <f>F129*G129</f>
@@ -5432,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>6179.11</v>
+        <v>5920.76</v>
       </c>
       <c r="H130" s="5">
         <f>F130*G130</f>
@@ -5469,7 +5469,7 @@
         <v>2</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>1402.96</v>
+        <v>1436.2</v>
       </c>
       <c r="H131" s="5">
         <f>F131*G131</f>
@@ -5506,7 +5506,7 @@
         <v>50</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>360.29</v>
+        <v>332.17</v>
       </c>
       <c r="H132" s="5">
         <f>F132*G132</f>
@@ -5543,7 +5543,7 @@
         <v>50</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>66.63</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="H133" s="5">
         <f>F133*G133</f>
@@ -5580,7 +5580,7 @@
         <v>4</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>8097.86</v>
+        <v>7783.12</v>
       </c>
       <c r="H134" s="5">
         <f>F134*G134</f>
@@ -5617,7 +5617,7 @@
         <v>4</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>9922.59</v>
+        <v>8313.16</v>
       </c>
       <c r="H135" s="5">
         <f>F135*G135</f>
@@ -6584,7 +6584,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>23916998.24</v>
+        <v>24418682.03</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>4132560.74</v>
+        <v>4634244.53</v>
       </c>
       <c r="C7" s="14">
         <f>B7/52.7585</f>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4783399.65</v>
+        <v>4883736.41</v>
       </c>
       <c r="C8" s="6">
         <f>B8/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -6584,7 +6584,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24418682.03</v>
+        <v>24169682.03</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>4634244.53</v>
+        <v>4385244.53</v>
       </c>
       <c r="C7" s="14">
         <f>B7/52.7585</f>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4883736.41</v>
+        <v>4833936.41</v>
       </c>
       <c r="C8" s="6">
         <f>B8/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -10,9 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.5 İcmal" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.1.1 Yapım İşleri" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.1.2 Makine-Ekipman" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.2 Hizmet Alımı" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.3 Görünürlük" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.4 Uygun Olmayan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.4-EK Makine-Ekipman" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.4-EK Yapım" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.2 Hizmet Alımı" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.3 Görünürlük" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A3.4 Uygun Olmayan" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -99,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,14 +114,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -131,6 +137,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -504,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -557,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H136</f>
+        <f>'A3.1.1 Yapım İşleri'!H89</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -566,7 +573,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>8 münferit yapı için ayrı ayrı teklif alınmıştır</t>
+          <t>Kümes A ve B blokları; her münferit yapı için ayrı teklif alınmıştır</t>
         </is>
       </c>
     </row>
@@ -577,7 +584,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>'A3.1.2 Makine-Ekipman'!G21</f>
+        <f>'A3.1.2 Makine-Ekipman'!G13</f>
         <v/>
       </c>
       <c r="C6" s="6">
@@ -586,7 +593,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>20.000 Avro üzeri — üç ayrı tedarikçiden üç teklif zorunlu</t>
+          <t>Hibe kapsamı dışında tutulmuştur; tablo boştur</t>
         </is>
       </c>
     </row>
@@ -633,7 +640,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>TOPLAM YATIRIM (KDV hariç)</t>
+          <t>UYGUN HARCAMA (A3.1.1 + A3.1.2 + A3.2 + A3.3)</t>
         </is>
       </c>
       <c r="B9" s="9">
@@ -644,7 +651,11 @@
         <f>B9/52.7585</f>
         <v/>
       </c>
-      <c r="D9" s="11" t="n"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Hibeye esas tutar; puanlama kriteri 1 bu tutara bakar</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -659,39 +670,110 @@
         <f>B10/52.7585</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="n"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Çağrı rehberi — uygun harcama limitin altındadır</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>UYGUN HARCAMA</t>
-        </is>
-      </c>
-      <c r="B11" s="13">
-        <f>MIN(B9,B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="14">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Puanlama kriteri 1 eşiği (300.000 Avro)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>15827550</v>
+      </c>
+      <c r="C11" s="6">
         <f>B11/52.7585</f>
         <v/>
       </c>
-      <c r="D11" s="15" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Uygun harcama bu eşiğin altında olduğundan 5 puan gelir</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Hibe dışı yapım işleri (A3.4-EK Yapım)</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <f>'A3.4-EK Yapım'!H51</f>
+        <v/>
+      </c>
+      <c r="C12" s="6">
+        <f>B12/52.7585</f>
+        <v/>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Diğer altı yapı ve iki bloktan çıkarılan pozlar — proforma ile beyan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Hibe dışı makine-ekipman (A3.4-EK Makine-Ekipman)</t>
+        </is>
+      </c>
+      <c r="B13" s="5">
+        <f>'A3.4-EK Makine-Ekipman'!G21</f>
+        <v/>
+      </c>
+      <c r="C13" s="6">
+        <f>B13/52.7585</f>
+        <v/>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Proforma ile beyan</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>UYGUN OLMAYAN HARCAMA (öz kaynak)</t>
         </is>
       </c>
-      <c r="B12" s="13">
-        <f>B9-B11</f>
-        <v/>
-      </c>
-      <c r="C12" s="14">
-        <f>B12/52.7585</f>
-        <v/>
-      </c>
-      <c r="D12" s="15" t="n"/>
+      <c r="B14" s="9">
+        <f>B12+B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="10">
+        <f>B14/52.7585</f>
+        <v/>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Tamamı öz kaynaktan karşılanır</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>TOPLAM YATIRIM (KDV hariç)</t>
+        </is>
+      </c>
+      <c r="B15" s="13">
+        <f>B9+B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="14">
+        <f>B15/52.7585</f>
+        <v/>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Uygun harcama + uygun olmayan harcama</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -707,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -730,7 +812,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kalemler keşif özetleri ve yapım işleri teklifiyle birebir aynıdır. Her yapı ayrı bölümdür.</t>
+          <t>Kalemler keşif özetleri ve yapım işleri teklifiyle birebir aynıdır. Hibe kapsamına yalnızca Kümes A ve B blokları girer; her yapı ayrı bölümdür.</t>
         </is>
       </c>
     </row>
@@ -1110,10 +1192,10 @@
         <v/>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="20" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
@@ -1123,12 +1205,12 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0042</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -1137,10 +1219,10 @@
         </is>
       </c>
       <c r="F14" s="20" t="n">
-        <v>1204.98</v>
+        <v>507.91</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1364.72</v>
+        <v>929.28</v>
       </c>
       <c r="H14" s="5">
         <f>F14*G14</f>
@@ -1160,12 +1242,12 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -1174,10 +1256,10 @@
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>507.91</v>
+        <v>49.85</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>929.28</v>
+        <v>1777.52</v>
       </c>
       <c r="H15" s="5">
         <f>F15*G15</f>
@@ -1187,7 +1269,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
@@ -1197,12 +1279,12 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -1211,10 +1293,10 @@
         </is>
       </c>
       <c r="F16" s="20" t="n">
-        <v>49.85</v>
+        <v>557.76</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1777.52</v>
+        <v>372.55</v>
       </c>
       <c r="H16" s="5">
         <f>F16*G16</f>
@@ -1234,12 +1316,12 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -1251,7 +1333,7 @@
         <v>557.76</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>372.55</v>
+        <v>381.49</v>
       </c>
       <c r="H17" s="5">
         <f>F17*G17</f>
@@ -1261,7 +1343,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
@@ -1271,12 +1353,12 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -1288,7 +1370,7 @@
         <v>557.76</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>381.49</v>
+        <v>324.27</v>
       </c>
       <c r="H18" s="5">
         <f>F18*G18</f>
@@ -1308,12 +1390,12 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
@@ -1325,7 +1407,7 @@
         <v>557.76</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>324.27</v>
+        <v>248.75</v>
       </c>
       <c r="H19" s="5">
         <f>F19*G19</f>
@@ -1335,7 +1417,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
@@ -1345,34 +1427,34 @@
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F20" s="20" t="n">
-        <v>557.76</v>
+        <v>674</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>248.75</v>
+        <v>147.67</v>
       </c>
       <c r="H20" s="5">
         <f>F20*G20</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="14" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
@@ -1382,12 +1464,12 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
+          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
@@ -1396,10 +1478,10 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>674</v>
+        <v>319.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>147.67</v>
+        <v>227.85</v>
       </c>
       <c r="H21" s="5">
         <f>F21*G21</f>
@@ -1424,7 +1506,7 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
+          <t>Galvanizli düz sacdan iniş borusu yapılması — ø100</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
@@ -1433,7 +1515,7 @@
         </is>
       </c>
       <c r="F22" s="20" t="n">
-        <v>319.2</v>
+        <v>40.96</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>227.85</v>
@@ -1443,10 +1525,10 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="14" customHeight="1">
+    <row r="23" ht="20" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
@@ -1456,24 +1538,24 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan iniş borusu yapılması — ø100</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F23" s="20" t="n">
-        <v>40.96</v>
+        <v>4.4</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>227.85</v>
+        <v>870.14</v>
       </c>
       <c r="H23" s="5">
         <f>F23*G23</f>
@@ -1498,7 +1580,7 @@
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -1507,7 +1589,7 @@
         </is>
       </c>
       <c r="F24" s="20" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>870.14</v>
@@ -1520,7 +1602,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
@@ -1530,12 +1612,12 @@
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -1544,10 +1626,10 @@
         </is>
       </c>
       <c r="F25" s="20" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>870.14</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H25" s="5">
         <f>F25*G25</f>
@@ -1557,7 +1639,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
@@ -1567,12 +1649,12 @@
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
@@ -1581,10 +1663,10 @@
         </is>
       </c>
       <c r="F26" s="20" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>381.49</v>
       </c>
       <c r="H26" s="5">
         <f>F26*G26</f>
@@ -1594,7 +1676,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
@@ -1604,12 +1686,12 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
+          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
@@ -1618,10 +1700,10 @@
         </is>
       </c>
       <c r="F27" s="20" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>381.49</v>
+        <v>701.48</v>
       </c>
       <c r="H27" s="5">
         <f>F27*G27</f>
@@ -1631,7 +1713,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
@@ -1641,12 +1723,12 @@
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
@@ -1655,10 +1737,10 @@
         </is>
       </c>
       <c r="F28" s="20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>701.48</v>
+        <v>248.75</v>
       </c>
       <c r="H28" s="5">
         <f>F28*G28</f>
@@ -1668,7 +1750,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
@@ -1678,12 +1760,12 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
+          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
@@ -1692,10 +1774,10 @@
         </is>
       </c>
       <c r="F29" s="20" t="n">
-        <v>55</v>
+        <v>5.67</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>248.75</v>
+        <v>2687.73</v>
       </c>
       <c r="H29" s="5">
         <f>F29*G29</f>
@@ -1715,24 +1797,24 @@
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
+          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F30" s="20" t="n">
-        <v>5.67</v>
+        <v>54.315</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>2687.73</v>
+        <v>183.57</v>
       </c>
       <c r="H30" s="5">
         <f>F30*G30</f>
@@ -1742,7 +1824,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
@@ -1752,24 +1834,24 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
+          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F31" s="20" t="n">
-        <v>54.315</v>
+        <v>25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>183.57</v>
+        <v>330.7</v>
       </c>
       <c r="H31" s="5">
         <f>F31*G31</f>
@@ -1779,7 +1861,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
@@ -1789,24 +1871,24 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F32" s="20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>330.7</v>
+        <v>10082.96</v>
       </c>
       <c r="H32" s="5">
         <f>F32*G32</f>
@@ -1826,12 +1908,12 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
@@ -1843,14 +1925,14 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>10082.96</v>
+        <v>4435.25</v>
       </c>
       <c r="H33" s="5">
         <f>F33*G33</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="14" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -1863,12 +1945,12 @@
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
@@ -1877,17 +1959,17 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>4435.25</v>
+        <v>1436.2</v>
       </c>
       <c r="H34" s="5">
         <f>F34*G34</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="14" customHeight="1">
+    <row r="35" ht="20" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -1900,24 +1982,24 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F35" s="20" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1436.2</v>
+        <v>244.02</v>
       </c>
       <c r="H35" s="5">
         <f>F35*G35</f>
@@ -1937,24 +2019,24 @@
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F36" s="20" t="n">
-        <v>300</v>
+        <v>30</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>244.02</v>
+        <v>2222.88</v>
       </c>
       <c r="H36" s="5">
         <f>F36*G36</f>
@@ -1974,12 +2056,12 @@
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
@@ -1988,17 +2070,17 @@
         </is>
       </c>
       <c r="F37" s="20" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>2222.88</v>
+        <v>1552.4</v>
       </c>
       <c r="H37" s="5">
         <f>F37*G37</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="14" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2011,24 +2093,24 @@
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F38" s="20" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1552.4</v>
+        <v>74.42</v>
       </c>
       <c r="H38" s="5">
         <f>F38*G38</f>
@@ -2048,12 +2130,12 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
@@ -2062,10 +2144,10 @@
         </is>
       </c>
       <c r="F39" s="20" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>74.42</v>
+        <v>33.1</v>
       </c>
       <c r="H39" s="5">
         <f>F39*G39</f>
@@ -2085,12 +2167,12 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
@@ -2099,17 +2181,17 @@
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>2000</v>
+        <v>600</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>33.1</v>
+        <v>23.56</v>
       </c>
       <c r="H40" s="5">
         <f>F40*G40</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="14" customHeight="1">
+    <row r="41" ht="20" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2122,12 +2204,12 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
       <c r="E41" s="19" t="inlineStr">
@@ -2136,10 +2218,10 @@
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>23.56</v>
+        <v>188.13</v>
       </c>
       <c r="H41" s="5">
         <f>F41*G41</f>
@@ -2159,12 +2241,12 @@
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
@@ -2173,17 +2255,17 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>188.13</v>
+        <v>156.11</v>
       </c>
       <c r="H42" s="5">
         <f>F42*G42</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
+    <row r="43" ht="14" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2196,31 +2278,31 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>156.11</v>
+        <v>17410.01</v>
       </c>
       <c r="H43" s="5">
         <f>F43*G43</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="14" customHeight="1">
+    <row r="44" ht="20" customHeight="1">
       <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2233,24 +2315,24 @@
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>17410.01</v>
+        <v>481.15</v>
       </c>
       <c r="H44" s="5">
         <f>F44*G44</f>
@@ -2270,31 +2352,31 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>481.15</v>
+        <v>484082.09</v>
       </c>
       <c r="H45" s="5">
         <f>F45*G45</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
+    <row r="46" ht="14" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2307,12 +2389,12 @@
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
@@ -2324,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>484082.09</v>
+        <v>83282.35000000001</v>
       </c>
       <c r="H46" s="5">
         <f>F46*G46</f>
@@ -2334,34 +2416,34 @@
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>1</v>
+        <v>1684.38</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>83282.35000000001</v>
+        <v>52.37</v>
       </c>
       <c r="H47" s="5">
         <f>F47*G47</f>
@@ -2371,44 +2453,44 @@
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>30.120.2016</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A — şebeke/jeneratör geçişi</t>
+          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>1</v>
+        <v>31.4285</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>44709.81</v>
+        <v>2750.45</v>
       </c>
       <c r="H48" s="5">
         <f>F48*G48</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="14" customHeight="1">
+    <row r="49" ht="20" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
@@ -2418,12 +2500,12 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
@@ -2432,20 +2514,20 @@
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>1684.38</v>
+        <v>115.71</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>52.37</v>
+        <v>2960.45</v>
       </c>
       <c r="H49" s="5">
         <f>F49*G49</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="14" customHeight="1">
+    <row r="50" ht="20" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
@@ -2455,12 +2537,12 @@
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
@@ -2469,20 +2551,20 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>31.4285</v>
+        <v>162.63</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2750.45</v>
+        <v>2960.45</v>
       </c>
       <c r="H50" s="5">
         <f>F50*G50</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
+    <row r="51" ht="14" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
@@ -2492,34 +2574,34 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>115.71</v>
+        <v>551.26</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>2960.45</v>
+        <v>863.8</v>
       </c>
       <c r="H51" s="5">
         <f>F51*G51</f>
         <v/>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
+    <row r="52" ht="14" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
@@ -2529,24 +2611,24 @@
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
+          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>162.63</v>
+        <v>4.1599</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>2960.45</v>
+        <v>39045.24</v>
       </c>
       <c r="H52" s="5">
         <f>F52*G52</f>
@@ -2556,7 +2638,7 @@
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2566,24 +2648,24 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
+          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>551.26</v>
+        <v>7.2875</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>863.8</v>
+        <v>37532.19</v>
       </c>
       <c r="H53" s="5">
         <f>F53*G53</f>
@@ -2603,12 +2685,12 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
@@ -2617,20 +2699,20 @@
         </is>
       </c>
       <c r="F54" s="20" t="n">
-        <v>4.1599</v>
+        <v>3.6375</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>39045.24</v>
+        <v>36949.5</v>
       </c>
       <c r="H54" s="5">
         <f>F54*G54</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="14" customHeight="1">
+    <row r="55" ht="20" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2640,12 +2722,12 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
@@ -2654,20 +2736,20 @@
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>7.2875</v>
+        <v>44.0481</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>37532.19</v>
+        <v>72192.55</v>
       </c>
       <c r="H55" s="5">
         <f>F55*G55</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="14" customHeight="1">
+    <row r="56" ht="20" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2677,24 +2759,24 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>3.6375</v>
+        <v>507.91</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>36949.5</v>
+        <v>929.28</v>
       </c>
       <c r="H56" s="5">
         <f>F56*G56</f>
@@ -2704,7 +2786,7 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -2714,34 +2796,34 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>44.0481</v>
+        <v>49.85</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>72192.55</v>
+        <v>1777.52</v>
       </c>
       <c r="H57" s="5">
         <f>F57*G57</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
+    <row r="58" ht="20" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2751,12 +2833,12 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0042</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
@@ -2765,10 +2847,10 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>1204.98</v>
+        <v>557.76</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1364.72</v>
+        <v>372.55</v>
       </c>
       <c r="H58" s="5">
         <f>F58*G58</f>
@@ -2778,7 +2860,7 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2788,12 +2870,12 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
@@ -2802,10 +2884,10 @@
         </is>
       </c>
       <c r="F59" s="20" t="n">
-        <v>507.91</v>
+        <v>557.76</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>929.28</v>
+        <v>381.49</v>
       </c>
       <c r="H59" s="5">
         <f>F59*G59</f>
@@ -2815,7 +2897,7 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2825,12 +2907,12 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
@@ -2839,10 +2921,10 @@
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>49.85</v>
+        <v>557.76</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>1777.52</v>
+        <v>324.27</v>
       </c>
       <c r="H60" s="5">
         <f>F60*G60</f>
@@ -2852,7 +2934,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2862,12 +2944,12 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -2879,7 +2961,7 @@
         <v>557.76</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>372.55</v>
+        <v>248.75</v>
       </c>
       <c r="H61" s="5">
         <f>F61*G61</f>
@@ -2889,7 +2971,7 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -2899,34 +2981,34 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
+          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>557.76</v>
+        <v>674</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>381.49</v>
+        <v>147.67</v>
       </c>
       <c r="H62" s="5">
         <f>F62*G62</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
+    <row r="63" ht="14" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -2936,34 +3018,34 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>557.76</v>
+        <v>319.2</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>324.27</v>
+        <v>227.85</v>
       </c>
       <c r="H63" s="5">
         <f>F63*G63</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
+    <row r="64" ht="14" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -2973,24 +3055,24 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>Galvanizli düz sacdan iniş borusu yapılması — ø100</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>557.76</v>
+        <v>40.96</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>248.75</v>
+        <v>227.85</v>
       </c>
       <c r="H64" s="5">
         <f>F64*G64</f>
@@ -3000,7 +3082,7 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3010,34 +3092,34 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>674</v>
+        <v>4.4</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>147.67</v>
+        <v>870.14</v>
       </c>
       <c r="H65" s="5">
         <f>F65*G65</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="14" customHeight="1">
+    <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3047,34 +3129,34 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>319.2</v>
+        <v>9</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>227.85</v>
+        <v>870.14</v>
       </c>
       <c r="H66" s="5">
         <f>F66*G66</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="14" customHeight="1">
+    <row r="67" ht="20" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3084,24 +3166,24 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan iniş borusu yapılması — ø100</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>40.96</v>
+        <v>45</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>227.85</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H67" s="5">
         <f>F67*G67</f>
@@ -3111,7 +3193,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3121,12 +3203,12 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
@@ -3135,10 +3217,10 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>4.4</v>
+        <v>90</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>870.14</v>
+        <v>381.49</v>
       </c>
       <c r="H68" s="5">
         <f>F68*G68</f>
@@ -3148,7 +3230,7 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3158,12 +3240,12 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
+          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3172,10 +3254,10 @@
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>870.14</v>
+        <v>701.48</v>
       </c>
       <c r="H69" s="5">
         <f>F69*G69</f>
@@ -3185,7 +3267,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3195,12 +3277,12 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
@@ -3209,10 +3291,10 @@
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>248.75</v>
       </c>
       <c r="H70" s="5">
         <f>F70*G70</f>
@@ -3222,7 +3304,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -3232,12 +3314,12 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
+          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3246,10 +3328,10 @@
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>90</v>
+        <v>5.67</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>381.49</v>
+        <v>2687.73</v>
       </c>
       <c r="H71" s="5">
         <f>F71*G71</f>
@@ -3259,7 +3341,7 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -3269,24 +3351,24 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
+          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>60</v>
+        <v>54.315</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>701.48</v>
+        <v>183.57</v>
       </c>
       <c r="H72" s="5">
         <f>F72*G72</f>
@@ -3296,7 +3378,7 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -3306,24 +3388,24 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
+          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>248.75</v>
+        <v>330.7</v>
       </c>
       <c r="H73" s="5">
         <f>F73*G73</f>
@@ -3333,7 +3415,7 @@
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
@@ -3343,24 +3425,24 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>5.67</v>
+        <v>1</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>2687.73</v>
+        <v>10082.96</v>
       </c>
       <c r="H74" s="5">
         <f>F74*G74</f>
@@ -3370,7 +3452,7 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -3380,34 +3462,34 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>54.315</v>
+        <v>1</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>183.57</v>
+        <v>4435.25</v>
       </c>
       <c r="H75" s="5">
         <f>F75*G75</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
+    <row r="76" ht="14" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B76" s="17" t="inlineStr">
@@ -3417,24 +3499,24 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>330.7</v>
+        <v>1436.2</v>
       </c>
       <c r="H76" s="5">
         <f>F76*G76</f>
@@ -3454,24 +3536,24 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F77" s="20" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>10082.96</v>
+        <v>244.02</v>
       </c>
       <c r="H77" s="5">
         <f>F77*G77</f>
@@ -3491,12 +3573,12 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
@@ -3505,17 +3587,17 @@
         </is>
       </c>
       <c r="F78" s="20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>4435.25</v>
+        <v>2222.88</v>
       </c>
       <c r="H78" s="5">
         <f>F78*G78</f>
         <v/>
       </c>
     </row>
-    <row r="79" ht="14" customHeight="1">
+    <row r="79" ht="20" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3528,12 +3610,12 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3545,14 +3627,14 @@
         <v>2</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1436.2</v>
+        <v>1552.4</v>
       </c>
       <c r="H79" s="5">
         <f>F79*G79</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1">
+    <row r="80" ht="14" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3565,12 +3647,12 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
@@ -3579,17 +3661,17 @@
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>244.02</v>
+        <v>74.42</v>
       </c>
       <c r="H80" s="5">
         <f>F80*G80</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="20" customHeight="1">
+    <row r="81" ht="14" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3602,31 +3684,31 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F81" s="20" t="n">
-        <v>30</v>
+        <v>2000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>2222.88</v>
+        <v>33.1</v>
       </c>
       <c r="H81" s="5">
         <f>F81*G81</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
+    <row r="82" ht="14" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3639,31 +3721,31 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F82" s="20" t="n">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1552.4</v>
+        <v>23.56</v>
       </c>
       <c r="H82" s="5">
         <f>F82*G82</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="14" customHeight="1">
+    <row r="83" ht="20" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3676,12 +3758,12 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -3690,17 +3772,17 @@
         </is>
       </c>
       <c r="F83" s="20" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>74.42</v>
+        <v>188.13</v>
       </c>
       <c r="H83" s="5">
         <f>F83*G83</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
+    <row r="84" ht="20" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3713,12 +3795,12 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
@@ -3727,10 +3809,10 @@
         </is>
       </c>
       <c r="F84" s="20" t="n">
-        <v>2000</v>
+        <v>186</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>33.1</v>
+        <v>156.11</v>
       </c>
       <c r="H84" s="5">
         <f>F84*G84</f>
@@ -3750,24 +3832,24 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F85" s="20" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>23.56</v>
+        <v>17410.01</v>
       </c>
       <c r="H85" s="5">
         <f>F85*G85</f>
@@ -3787,12 +3869,12 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
@@ -3801,10 +3883,10 @@
         </is>
       </c>
       <c r="F86" s="20" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>188.13</v>
+        <v>481.15</v>
       </c>
       <c r="H86" s="5">
         <f>F86*G86</f>
@@ -3824,24 +3906,24 @@
       </c>
       <c r="C87" s="18" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F87" s="20" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>156.11</v>
+        <v>484082.09</v>
       </c>
       <c r="H87" s="5">
         <f>F87*G87</f>
@@ -3861,12 +3943,12 @@
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
@@ -3878,1766 +3960,27 @@
         <v>1</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>17410.01</v>
+        <v>83282.35000000001</v>
       </c>
       <c r="H88" s="5">
         <f>F88*G88</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>30.750.2001</t>
-        </is>
-      </c>
-      <c r="D89" s="16" t="inlineStr">
-        <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
-        </is>
-      </c>
-      <c r="E89" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F89" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>481.15</v>
-      </c>
-      <c r="H89" s="5">
-        <f>F89*G89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>30.740.1106</t>
-        </is>
-      </c>
-      <c r="D90" s="16" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
-        </is>
-      </c>
-      <c r="E90" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F90" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>484082.09</v>
-      </c>
-      <c r="H90" s="5">
-        <f>F90*G90</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="14" customHeight="1">
-      <c r="A91" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="D91" s="16" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
-        </is>
-      </c>
-      <c r="E91" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F91" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>83282.35000000001</v>
-      </c>
-      <c r="H91" s="5">
-        <f>F91*G91</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="14" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="inlineStr">
-        <is>
-          <t>30.120.2016</t>
-        </is>
-      </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>Otomatik transfer şalteri 4 x 200 A — şebeke/jeneratör geçişi</t>
-        </is>
-      </c>
-      <c r="E92" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F92" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>44709.81</v>
-      </c>
-      <c r="H92" s="5">
-        <f>F92*G92</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="14" customHeight="1">
-      <c r="A93" s="16" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>Gübre Çukuru</t>
-        </is>
-      </c>
-      <c r="C93" s="18" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D93" s="16" t="inlineStr">
-        <is>
-          <t>Makine ile dar ve derin sandık kazı — gübre çukuru</t>
-        </is>
-      </c>
-      <c r="E93" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F93" s="20" t="n">
-        <v>542.7</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="H93" s="5">
-        <f>F93*G93</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="16" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>Gübre Çukuru</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>C 16/20 hazır beton dökülmesi — gübre çukuru radye altı grobeton</t>
-        </is>
-      </c>
-      <c r="E94" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F94" s="20" t="n">
-        <v>11.934</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>2750.45</v>
-      </c>
-      <c r="H94" s="5">
-        <f>F94*G94</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="14" customHeight="1">
-      <c r="A95" s="16" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>Gübre Çukuru</t>
-        </is>
-      </c>
-      <c r="C95" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D95" s="16" t="inlineStr">
-        <is>
-          <t>C 25/30 hazır beton dökülmesi — gübre çukuru radye temeli</t>
-        </is>
-      </c>
-      <c r="E95" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F95" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>2960.45</v>
-      </c>
-      <c r="H95" s="5">
-        <f>F95*G95</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="16" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>Gübre Çukuru</t>
-        </is>
-      </c>
-      <c r="C96" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>C 25/30 hazır beton dökülmesi — gübre çukuru perde, kolon ve üst döşemesi</t>
-        </is>
-      </c>
-      <c r="E96" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F96" s="20" t="n">
-        <v>47.19</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>2960.45</v>
-      </c>
-      <c r="H96" s="5">
-        <f>F96*G96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="16" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B97" s="17" t="inlineStr">
-        <is>
-          <t>Gübre Çukuru</t>
-        </is>
-      </c>
-      <c r="C97" s="18" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D97" s="16" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — gübre çukuru</t>
-        </is>
-      </c>
-      <c r="E97" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F97" s="20" t="n">
-        <v>363.26</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>863.8</v>
-      </c>
-      <c r="H97" s="5">
-        <f>F97*G97</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="14" customHeight="1">
-      <c r="A98" s="16" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>Gübre Çukuru</t>
-        </is>
-      </c>
-      <c r="C98" s="18" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — gübre çukuru</t>
-        </is>
-      </c>
-      <c r="E98" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F98" s="20" t="n">
-        <v>7.5993</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>39045.24</v>
-      </c>
-      <c r="H98" s="5">
-        <f>F98*G98</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="16" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>Gübre Çukuru</t>
-        </is>
-      </c>
-      <c r="C99" s="18" t="inlineStr">
-        <is>
-          <t>15.160.1004</t>
-        </is>
-      </c>
-      <c r="D99" s="16" t="inlineStr">
-        <is>
-          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — gübre çukuru ve yağmur suyu deposu</t>
-        </is>
-      </c>
-      <c r="E99" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F99" s="20" t="n">
-        <v>0.5641</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>37532.19</v>
-      </c>
-      <c r="H99" s="5">
-        <f>F99*G99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="16" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>Ölü Atma Çukuru</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D100" s="16" t="inlineStr">
-        <is>
-          <t>Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E100" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F100" s="20" t="n">
-        <v>142</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="H100" s="5">
-        <f>F100*G100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="16" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B101" s="17" t="inlineStr">
-        <is>
-          <t>Ölü Atma Çukuru</t>
-        </is>
-      </c>
-      <c r="C101" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D101" s="16" t="inlineStr">
-        <is>
-          <t>C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
-        </is>
-      </c>
-      <c r="E101" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F101" s="20" t="n">
-        <v>1.984</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>2750.45</v>
-      </c>
-      <c r="H101" s="5">
-        <f>F101*G101</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="16" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B102" s="17" t="inlineStr">
-        <is>
-          <t>Ölü Atma Çukuru</t>
-        </is>
-      </c>
-      <c r="C102" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D102" s="16" t="inlineStr">
-        <is>
-          <t>C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
-        </is>
-      </c>
-      <c r="E102" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F102" s="20" t="n">
-        <v>20.85</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>2960.45</v>
-      </c>
-      <c r="H102" s="5">
-        <f>F102*G102</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103" ht="14" customHeight="1">
-      <c r="A103" s="16" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B103" s="17" t="inlineStr">
-        <is>
-          <t>Ölü Atma Çukuru</t>
-        </is>
-      </c>
-      <c r="C103" s="18" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D103" s="16" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
-        </is>
-      </c>
-      <c r="E103" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F103" s="20" t="n">
-        <v>127.2</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>863.8</v>
-      </c>
-      <c r="H103" s="5">
-        <f>F103*G103</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="16" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B104" s="17" t="inlineStr">
-        <is>
-          <t>Ölü Atma Çukuru</t>
-        </is>
-      </c>
-      <c r="C104" s="18" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D104" s="16" t="inlineStr">
-        <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E104" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F104" s="20" t="n">
-        <v>1.6571</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>39045.24</v>
-      </c>
-      <c r="H104" s="5">
-        <f>F104*G104</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="16" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B105" s="17" t="inlineStr">
-        <is>
-          <t>Foseptik</t>
-        </is>
-      </c>
-      <c r="C105" s="18" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D105" s="16" t="inlineStr">
-        <is>
-          <t>Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E105" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F105" s="20" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="H105" s="5">
-        <f>F105*G105</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="16" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B106" s="17" t="inlineStr">
-        <is>
-          <t>Foseptik</t>
-        </is>
-      </c>
-      <c r="C106" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D106" s="16" t="inlineStr">
-        <is>
-          <t>C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
-        </is>
-      </c>
-      <c r="E106" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F106" s="20" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>2750.45</v>
-      </c>
-      <c r="H106" s="5">
-        <f>F106*G106</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" ht="14" customHeight="1">
-      <c r="A107" s="16" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B107" s="17" t="inlineStr">
-        <is>
-          <t>Foseptik</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D107" s="16" t="inlineStr">
-        <is>
-          <t>C 25/30 hazır beton dökülmesi — foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E107" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F107" s="20" t="n">
-        <v>6.175</v>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>2960.45</v>
-      </c>
-      <c r="H107" s="5">
-        <f>F107*G107</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="16" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B108" s="17" t="inlineStr">
-        <is>
-          <t>Foseptik</t>
-        </is>
-      </c>
-      <c r="C108" s="18" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E108" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F108" s="20" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>863.8</v>
-      </c>
-      <c r="H108" s="5">
-        <f>F108*G108</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="16" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B109" s="17" t="inlineStr">
-        <is>
-          <t>Foseptik</t>
-        </is>
-      </c>
-      <c r="C109" s="18" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D109" s="16" t="inlineStr">
-        <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E109" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F109" s="20" t="n">
-        <v>0.5866</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>39045.24</v>
-      </c>
-      <c r="H109" s="5">
-        <f>F109*G109</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="16" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B110" s="17" t="inlineStr">
-        <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
-        </is>
-      </c>
-      <c r="C110" s="18" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D110" s="16" t="inlineStr">
-        <is>
-          <t>Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E110" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F110" s="20" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="H110" s="5">
-        <f>F110*G110</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="16" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B111" s="17" t="inlineStr">
-        <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
-        </is>
-      </c>
-      <c r="C111" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D111" s="16" t="inlineStr">
-        <is>
-          <t>C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
-        </is>
-      </c>
-      <c r="E111" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F111" s="20" t="n">
-        <v>1.922</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>2750.45</v>
-      </c>
-      <c r="H111" s="5">
-        <f>F111*G111</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112" ht="14" customHeight="1">
-      <c r="A112" s="16" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B112" s="17" t="inlineStr">
-        <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
-        </is>
-      </c>
-      <c r="C112" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D112" s="16" t="inlineStr">
-        <is>
-          <t>C 25/30 hazır beton dökülmesi — foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E112" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F112" s="20" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>2960.45</v>
-      </c>
-      <c r="H112" s="5">
-        <f>F112*G112</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="16" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B113" s="17" t="inlineStr">
-        <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
-        </is>
-      </c>
-      <c r="C113" s="18" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D113" s="16" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E113" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F113" s="20" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>863.8</v>
-      </c>
-      <c r="H113" s="5">
-        <f>F113*G113</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="16" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B114" s="17" t="inlineStr">
-        <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
-        </is>
-      </c>
-      <c r="C114" s="18" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E114" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F114" s="20" t="n">
-        <v>0.7569</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>39045.24</v>
-      </c>
-      <c r="H114" s="5">
-        <f>F114*G114</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="16" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B115" s="17" t="inlineStr">
-        <is>
-          <t>Su Deposu</t>
-        </is>
-      </c>
-      <c r="C115" s="18" t="inlineStr">
-        <is>
-          <t>15.120.1101</t>
-        </is>
-      </c>
-      <c r="D115" s="16" t="inlineStr">
-        <is>
-          <t>Makine ile dar ve derin sandık kazı — ölü atma çukuru, depolar, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E115" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F115" s="20" t="n">
-        <v>106.5</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>60.35</v>
-      </c>
-      <c r="H115" s="5">
-        <f>F115*G115</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="16" t="inlineStr">
-        <is>
-          <t>Beton işleri</t>
-        </is>
-      </c>
-      <c r="B116" s="17" t="inlineStr">
-        <is>
-          <t>Su Deposu</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
-        </is>
-      </c>
-      <c r="D116" s="16" t="inlineStr">
-        <is>
-          <t>C 16/20 hazır beton dökülmesi — çukur, depo, foseptik ve silo kaideleri altı grobeton</t>
-        </is>
-      </c>
-      <c r="E116" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F116" s="20" t="n">
-        <v>1.344</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>2750.45</v>
-      </c>
-      <c r="H116" s="5">
-        <f>F116*G116</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="16" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B117" s="17" t="inlineStr">
-        <is>
-          <t>Su Deposu</t>
-        </is>
-      </c>
-      <c r="C117" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D117" s="16" t="inlineStr">
-        <is>
-          <t>C 25/30 hazır beton dökülmesi — ölü atma çukuru, su ve yağmur suyu depoları</t>
-        </is>
-      </c>
-      <c r="E117" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F117" s="20" t="n">
-        <v>15.15</v>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>2960.45</v>
-      </c>
-      <c r="H117" s="5">
-        <f>F117*G117</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118" ht="14" customHeight="1">
-      <c r="A118" s="16" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B118" s="17" t="inlineStr">
-        <is>
-          <t>Su Deposu</t>
-        </is>
-      </c>
-      <c r="C118" s="18" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D118" s="16" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — çukur ve depolar</t>
-        </is>
-      </c>
-      <c r="E118" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F118" s="20" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>863.8</v>
-      </c>
-      <c r="H118" s="5">
-        <f>F118*G118</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="16" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B119" s="17" t="inlineStr">
-        <is>
-          <t>Su Deposu</t>
-        </is>
-      </c>
-      <c r="C119" s="18" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D119" s="16" t="inlineStr">
-        <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — çukur, depo, foseptik ve silo kaideleri</t>
-        </is>
-      </c>
-      <c r="E119" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F119" s="20" t="n">
-        <v>1.2316</v>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>39045.24</v>
-      </c>
-      <c r="H119" s="5">
-        <f>F119*G119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120" ht="14" customHeight="1">
-      <c r="A120" s="16" t="inlineStr">
-        <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
-        </is>
-      </c>
-      <c r="B120" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C120" s="18" t="inlineStr">
-        <is>
-          <t>15.120.1001</t>
-        </is>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>Makine ile kaba tesviye kazısı — tesis içi yol güzergâhı</t>
-        </is>
-      </c>
-      <c r="E120" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F120" s="20" t="n">
-        <v>260.9425</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>52.37</v>
-      </c>
-      <c r="H120" s="5">
-        <f>F120*G120</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="16" t="inlineStr">
-        <is>
-          <t>Çevre düzenlemesi ve çit işleri</t>
-        </is>
-      </c>
-      <c r="B121" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C121" s="18" t="inlineStr">
-        <is>
-          <t>TKDK-0091</t>
-        </is>
-      </c>
-      <c r="D121" s="16" t="inlineStr">
-        <is>
-          <t>1,50 m yükseklikte sıcak daldırma galvanizli tel örgü ile çit yapılması</t>
-        </is>
-      </c>
-      <c r="E121" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F121" s="20" t="n">
-        <v>361.04</v>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>940.84</v>
-      </c>
-      <c r="H121" s="5">
-        <f>F121*G121</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="16" t="inlineStr">
-        <is>
-          <t>Kanalizasyon işleri</t>
-        </is>
-      </c>
-      <c r="B122" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C122" s="18" t="inlineStr">
-        <is>
-          <t>43.527.1001</t>
-        </is>
-      </c>
-      <c r="D122" s="16" t="inlineStr">
-        <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
-        </is>
-      </c>
-      <c r="E122" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F122" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>330.7</v>
-      </c>
-      <c r="H122" s="5">
-        <f>F122*G122</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123" ht="14" customHeight="1">
-      <c r="A123" s="16" t="inlineStr">
-        <is>
-          <t>Betonarme işleri</t>
-        </is>
-      </c>
-      <c r="B123" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C123" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
-        </is>
-      </c>
-      <c r="D123" s="16" t="inlineStr">
-        <is>
-          <t>C 25/30 hazır beton dökülmesi — betonarme rögarlar</t>
-        </is>
-      </c>
-      <c r="E123" s="19" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="F123" s="20" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>2960.45</v>
-      </c>
-      <c r="H123" s="5">
-        <f>F123*G123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="16" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B124" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C124" s="18" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D124" s="16" t="inlineStr">
-        <is>
-          <t>Düz yüzeyli beton ve betonarme kalıbı yapılması — betonarme rögarlar</t>
-        </is>
-      </c>
-      <c r="E124" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F124" s="20" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>863.8</v>
-      </c>
-      <c r="H124" s="5">
-        <f>F124*G124</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="16" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B125" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C125" s="18" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D125" s="16" t="inlineStr">
-        <is>
-          <t>Nervürlü betonarme çeliği ø8-ø12 — betonarme rögarlar</t>
-        </is>
-      </c>
-      <c r="E125" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F125" s="20" t="n">
-        <v>0.1409</v>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>39045.24</v>
-      </c>
-      <c r="H125" s="5">
-        <f>F125*G125</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="16" t="inlineStr">
-        <is>
-          <t>Kanalizasyon işleri</t>
-        </is>
-      </c>
-      <c r="B126" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C126" s="18" t="inlineStr">
-        <is>
-          <t>15.560.1003</t>
-        </is>
-      </c>
-      <c r="D126" s="16" t="inlineStr">
-        <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
-        </is>
-      </c>
-      <c r="E126" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F126" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>3744.3</v>
-      </c>
-      <c r="H126" s="5">
-        <f>F126*G126</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B127" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C127" s="18" t="inlineStr">
-        <is>
-          <t>30.100.1104</t>
-        </is>
-      </c>
-      <c r="D127" s="16" t="inlineStr">
-        <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
-        </is>
-      </c>
-      <c r="E127" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F127" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" s="5" t="n">
-        <v>41783.13</v>
-      </c>
-      <c r="H127" s="5">
-        <f>F127*G127</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B128" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C128" s="18" t="inlineStr">
-        <is>
-          <t>30.100.2106</t>
-        </is>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
-        </is>
-      </c>
-      <c r="E128" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F128" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" s="5" t="n">
-        <v>11631.65</v>
-      </c>
-      <c r="H128" s="5">
-        <f>F128*G128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B129" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C129" s="18" t="inlineStr">
-        <is>
-          <t>30.135.3201</t>
-        </is>
-      </c>
-      <c r="D129" s="16" t="inlineStr">
-        <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
-        </is>
-      </c>
-      <c r="E129" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F129" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" s="5" t="n">
-        <v>2218.15</v>
-      </c>
-      <c r="H129" s="5">
-        <f>F129*G129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" ht="14" customHeight="1">
-      <c r="A130" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B130" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C130" s="18" t="inlineStr">
-        <is>
-          <t>30.110.1104</t>
-        </is>
-      </c>
-      <c r="D130" s="16" t="inlineStr">
-        <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
-        </is>
-      </c>
-      <c r="E130" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F130" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G130" s="5" t="n">
-        <v>5920.76</v>
-      </c>
-      <c r="H130" s="5">
-        <f>F130*G130</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" ht="14" customHeight="1">
-      <c r="A131" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B131" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C131" s="18" t="inlineStr">
-        <is>
-          <t>30.115.1003</t>
-        </is>
-      </c>
-      <c r="D131" s="16" t="inlineStr">
-        <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
-        </is>
-      </c>
-      <c r="E131" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F131" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>1436.2</v>
-      </c>
-      <c r="H131" s="5">
-        <f>F131*G131</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B132" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C132" s="18" t="inlineStr">
-        <is>
-          <t>30.140.3105</t>
-        </is>
-      </c>
-      <c r="D132" s="16" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
-        </is>
-      </c>
-      <c r="E132" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F132" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>332.17</v>
-      </c>
-      <c r="H132" s="5">
-        <f>F132*G132</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B133" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C133" s="18" t="inlineStr">
-        <is>
-          <t>30.140.3101</t>
-        </is>
-      </c>
-      <c r="D133" s="16" t="inlineStr">
-        <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
-        </is>
-      </c>
-      <c r="E133" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F133" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="G133" s="5" t="n">
-        <v>71.31999999999999</v>
-      </c>
-      <c r="H133" s="5">
-        <f>F133*G133</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B134" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C134" s="18" t="inlineStr">
-        <is>
-          <t>30.172.1706</t>
-        </is>
-      </c>
-      <c r="D134" s="16" t="inlineStr">
-        <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
-        </is>
-      </c>
-      <c r="E134" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F134" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>7783.12</v>
-      </c>
-      <c r="H134" s="5">
-        <f>F134*G134</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135" ht="14" customHeight="1">
-      <c r="A135" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B135" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C135" s="18" t="inlineStr">
-        <is>
-          <t>30.170.4002</t>
-        </is>
-      </c>
-      <c r="D135" s="16" t="inlineStr">
-        <is>
-          <t>LED projektör, ışık akısı en az 5100 lm</t>
-        </is>
-      </c>
-      <c r="E135" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F135" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G135" s="5" t="n">
-        <v>8313.16</v>
-      </c>
-      <c r="H135" s="5">
-        <f>F135*G135</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="15" t="n"/>
-      <c r="B136" s="15" t="n"/>
-      <c r="C136" s="15" t="n"/>
-      <c r="D136" s="21" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="21" t="n"/>
+      <c r="B89" s="21" t="n"/>
+      <c r="C89" s="21" t="n"/>
+      <c r="D89" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E136" s="15" t="n"/>
-      <c r="F136" s="15" t="n"/>
-      <c r="G136" s="15" t="n"/>
-      <c r="H136" s="13">
-        <f>SUM(H5:H135)</f>
+      <c r="E89" s="21" t="n"/>
+      <c r="F89" s="21" t="n"/>
+      <c r="G89" s="21" t="n"/>
+      <c r="H89" s="9">
+        <f>SUM(H5:H88)</f>
         <v/>
       </c>
     </row>
@@ -5650,6 +3993,172 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>A3.1.2 — MAKİNE VE EKİPMAN UYGUN HARCAMALARI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bu yatırımda makine-ekipman alımı hibe kapsamı dışında tutulmuştur; kalemler A3.4-EK sayfasında proforma esaslı beyan edilir. Bu tablo boş sunulur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>EK-1 uygun harcama kalemi</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Ürün adı</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Miktar</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Birim fiyat (TL)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Tutar (TL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>A3.1.2 MAKİNE-EKİPMAN TOPLAMI (KDV hariç)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="9">
+        <f>SUM(G5:G12)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5668,16 +4177,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>A3.1.2 — MAKİNE VE EKİPMAN UYGUN HARCAMALARI</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>A3.4-EK — MAKİNE VE EKİPMAN (UYGUN OLMAYAN HARCAMA)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mert Veterinerlik 21.08.2026 tarih ve 1300 numaralı teklifinden; iki kümes bloğu için.</t>
+          <t>Miktarlar kümes mekanik projesinden; birim fiyatlar Mert Veterinerlik 21.08.2026 tarih ve 1300 numaralı teklifinden. Hibe kapsamı dışında olduğundan teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir; iki kümes bloğu için.</t>
         </is>
       </c>
     </row>
@@ -5949,7 +4458,7 @@
         </is>
       </c>
       <c r="E12" s="20" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>25500</v>
@@ -5979,7 +4488,7 @@
         </is>
       </c>
       <c r="E13" s="20" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>1200</v>
@@ -6200,17 +4709,17 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>A3.1.2 MAKİNE-EKİPMAN TOPLAMI (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="13">
+      <c r="A21" s="21" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>MAKİNE-EKİPMAN TOPLAMI (KDV hariç)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="9">
         <f>SUM(G5:G20)</f>
         <v/>
       </c>
@@ -6223,7 +4732,1810 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>A3.4-EK — HİBE DIŞI YAPIM İŞLERİ (UYGUN OLMAYAN HARCAMA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Kümes A ve B blokları dışındaki yapılar ile bu iki bloktan hibe kapsamı dışına çıkarılan pozlar. Bu imalatlar yapılmaya devam eder; teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir ve tamamı öz kaynaktan karşılanır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>EK-1 kalemi</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Yapı</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Poz No</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>İşin adı</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Miktar</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Birim fiyat (TL)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Tutar (TL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="14" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>260.942</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>52.374</v>
+      </c>
+      <c r="H5" s="5">
+        <f>F5*G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Gübre Çukuru</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>542.7</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>60.354</v>
+      </c>
+      <c r="H6" s="5">
+        <f>F6*G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Ölü Atma Çukuru</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>142</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>60.354</v>
+      </c>
+      <c r="H7" s="5">
+        <f>F7*G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Foseptik</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>60.354</v>
+      </c>
+      <c r="H8" s="5">
+        <f>F8*G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Yem Silosu Betonarme Kaideleri</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>60.354</v>
+      </c>
+      <c r="H9" s="5">
+        <f>F9*G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Kazı, dolgu ve reglaj işleri</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Su Deposu</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>15.120.1101</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>60.354</v>
+      </c>
+      <c r="H10" s="5">
+        <f>F10*G10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Gübre Çukuru</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>11.934</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>2750.454</v>
+      </c>
+      <c r="H11" s="5">
+        <f>F11*G11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Ölü Atma Çukuru</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2750.454</v>
+      </c>
+      <c r="H12" s="5">
+        <f>F12*G12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Foseptik</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>2750.454</v>
+      </c>
+      <c r="H13" s="5">
+        <f>F13*G13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Yem Silosu Betonarme Kaideleri</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>1.922</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>2750.454</v>
+      </c>
+      <c r="H14" s="5">
+        <f>F14*G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Beton işleri</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Su Deposu</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>2750.454</v>
+      </c>
+      <c r="H15" s="5">
+        <f>F15*G15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Gübre Çukuru</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="n">
+        <v>93.19</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>2960.454</v>
+      </c>
+      <c r="H16" s="5">
+        <f>F16*G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>Ölü Atma Çukuru</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>2960.454</v>
+      </c>
+      <c r="H17" s="5">
+        <f>F17*G17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Su Deposu</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2960.454</v>
+      </c>
+      <c r="H18" s="5">
+        <f>F18*G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Foseptik</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v>6.175</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>2960.454</v>
+      </c>
+      <c r="H19" s="5">
+        <f>F19*G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Yem Silosu Betonarme Kaideleri</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>2960.454</v>
+      </c>
+      <c r="H20" s="5">
+        <f>F20*G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>Gübre Çukuru</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="n">
+        <v>363.26</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>863.7972</v>
+      </c>
+      <c r="H21" s="5">
+        <f>F21*G21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>Ölü Atma Çukuru</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>863.7972</v>
+      </c>
+      <c r="H22" s="5">
+        <f>F22*G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>Su Deposu</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>863.7972</v>
+      </c>
+      <c r="H23" s="5">
+        <f>F23*G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Foseptik</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>863.7972</v>
+      </c>
+      <c r="H24" s="5">
+        <f>F24*G24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Yem Silosu Betonarme Kaideleri</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>863.7972</v>
+      </c>
+      <c r="H25" s="5">
+        <f>F25*G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Gübre Çukuru</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="n">
+        <v>7.599</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>39045.2412</v>
+      </c>
+      <c r="H26" s="5">
+        <f>F26*G26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Gübre Çukuru</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E27" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>37532.1912</v>
+      </c>
+      <c r="H27" s="5">
+        <f>F27*G27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Ölü Atma Çukuru</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E28" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>1.657</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>39045.2412</v>
+      </c>
+      <c r="H28" s="5">
+        <f>F28*G28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Foseptik</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>39045.2412</v>
+      </c>
+      <c r="H29" s="5">
+        <f>F29*G29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Yem Silosu Betonarme Kaideleri</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>39045.2412</v>
+      </c>
+      <c r="H30" s="5">
+        <f>F30*G30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Su Deposu</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>1.232</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>39045.2412</v>
+      </c>
+      <c r="H31" s="5">
+        <f>F31*G31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Çatı ve sundurma işleri</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>TKDK-0042</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v>1204.98</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>1364.7228</v>
+      </c>
+      <c r="H32" s="5">
+        <f>F32*G32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Çatı ve sundurma işleri</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>TKDK-0042</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>1204.98</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1364.7228</v>
+      </c>
+      <c r="H33" s="5">
+        <f>F33*G33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Çevre düzenlemesi ve çit işleri</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>TKDK-0091</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>361.04</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>940.842</v>
+      </c>
+      <c r="H34" s="5">
+        <f>F34*G34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Kanalizasyon işleri</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>330.6996</v>
+      </c>
+      <c r="H35" s="5">
+        <f>F35*G35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Betonarme işleri</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>2960.454</v>
+      </c>
+      <c r="H36" s="5">
+        <f>F36*G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Kalıp, yapı iskelesi işleri</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>863.7972</v>
+      </c>
+      <c r="H37" s="5">
+        <f>F37*G37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>39045.2412</v>
+      </c>
+      <c r="H38" s="5">
+        <f>F38*G38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Kanalizasyon işleri</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>15.560.1003</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>3744.3</v>
+      </c>
+      <c r="H39" s="5">
+        <f>F39*G39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>30.100.1104</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>41783.1288</v>
+      </c>
+      <c r="H40" s="5">
+        <f>F40*G40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>30.100.2106</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>11631.648</v>
+      </c>
+      <c r="H41" s="5">
+        <f>F41*G41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>30.135.3201</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>2218.1544</v>
+      </c>
+      <c r="H42" s="5">
+        <f>F42*G42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>30.110.1104</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>5920.7568</v>
+      </c>
+      <c r="H43" s="5">
+        <f>F43*G43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>30.115.1003</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>1436.1984</v>
+      </c>
+      <c r="H44" s="5">
+        <f>F44*G44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>30.140.3105</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>332.1696</v>
+      </c>
+      <c r="H45" s="5">
+        <f>F45*G45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>30.140.3101</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>71.3244</v>
+      </c>
+      <c r="H46" s="5">
+        <f>F46*G46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>30.172.1706</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>7783.1208</v>
+      </c>
+      <c r="H47" s="5">
+        <f>F47*G47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>30.170.4002</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>LED projektör, ışık akısı en az 5100 lm</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>8313.1608</v>
+      </c>
+      <c r="H48" s="5">
+        <f>F48*G48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>30.120.2016</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>Otomatik transfer şalteri 4 x 200 A</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>44709.8148</v>
+      </c>
+      <c r="H49" s="5">
+        <f>F49*G49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>30.120.2016</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>Otomatik transfer şalteri 4 x 200 A</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>44709.8148</v>
+      </c>
+      <c r="H50" s="5">
+        <f>F50*G50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="21" t="n"/>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>HİBE DIŞI YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="9">
+        <f>SUM(H5:H50)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6352,16 +6664,16 @@
       <c r="F12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="13">
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="9">
         <f>SUM(F5:F12)</f>
         <v/>
       </c>
@@ -6374,7 +6686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6503,16 +6815,16 @@
       <c r="F12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>TOPLAM (KDV hariç)</t>
         </is>
       </c>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="13">
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="9">
         <f>SUM(F5:F12)</f>
         <v/>
       </c>
@@ -6525,13 +6837,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -6541,7 +6853,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>A3.4 — UYGUN OLMAYAN HARCAMALAR</t>
         </is>
@@ -6550,7 +6862,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>IPARD III broyler yatırımlarında uygun harcama üst limiti 375.000 Avro'dur; aşan kısım uygun olmayan harcamadır ve tamamen öz kaynaktan karşılanır.</t>
+          <t>IPARD III broyler yatırımlarında uygun harcama üst limiti 375.000 Avro'dur. Bu yatırımda uygun harcama, puanlama kriteri 1 gereği 300.000 Avro'nun altında tutulmuştur; yatırımın geri kalanı uygun olmayan harcamadır, proforma fatura ile beyan edilir ve tamamen öz kaynaktan karşılanır.</t>
         </is>
       </c>
     </row>
@@ -6580,11 +6892,11 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Toplam yatırım tutarı (yapım işleri + makine-ekipman, KDV hariç)</t>
+          <t>Toplam yatırım tutarı (KDV hariç)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24169682.03</v>
+        <v>24169695.26</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -6592,18 +6904,18 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>Teklifler</t>
+          <t>Keşif ve proformalar</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>IPARD III broyler uygun harcama üst limiti (375.000,00 Avro)</t>
+          <t>Uygun harcama — Kümes A ve B blokları yapım işleri (A3.1.1)</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>19784437.5</v>
+        <v>15576719.84</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -6611,43 +6923,100 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>Çağrı rehberi</t>
+          <t>Yapım işleri teklifi</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>UYGUN OLMAYAN HARCAMA — üst limiti aşan kısım</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>4385244.53</v>
-      </c>
-      <c r="C7" s="14">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Hibe dışı yapım işleri — diğer yapılar ve çıkarılan pozlar (A3.4-EK Yapım)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>5497755.42</v>
+      </c>
+      <c r="C7" s="6">
         <f>B7/52.7585</f>
         <v/>
       </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>Öz kaynak</t>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Proforma fatura</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>KDV — IPARD'da uygun harcama değildir</t>
+          <t>Hibe dışı makine-ekipman alımı (A3.4-EK Makine-Ekipman)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4833936.41</v>
+        <v>3095220</v>
       </c>
       <c r="C8" s="6">
         <f>B8/52.7585</f>
         <v/>
       </c>
       <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>Proforma fatura</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>UYGUN OLMAYAN HARCAMA — toplam</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>8592975.42</v>
+      </c>
+      <c r="C9" s="10">
+        <f>B9/52.7585</f>
+        <v/>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Öz kaynak</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>IPARD III broyler uygun harcama üst limiti (375.000,00 Avro) — uygun harcama limitin altındadır</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>19784437.5</v>
+      </c>
+      <c r="C10" s="6">
+        <f>B10/52.7585</f>
+        <v/>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Çağrı rehberi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>KDV — IPARD'da uygun harcama değildir</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4833939.05</v>
+      </c>
+      <c r="C11" s="6">
+        <f>B11/52.7585</f>
+        <v/>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Öz kaynak</t>
         </is>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -736,40 +736,59 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Hibe dışı kümes ısıtma sistemi</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>710000</v>
+      </c>
+      <c r="C14" s="6">
+        <f>B14/52.7585</f>
+        <v/>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Ayrı lot; proforma ile beyan</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>UYGUN OLMAYAN HARCAMA (öz kaynak)</t>
         </is>
       </c>
-      <c r="B14" s="9">
-        <f>B12+B13</f>
-        <v/>
-      </c>
-      <c r="C14" s="10">
-        <f>B14/52.7585</f>
-        <v/>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="B15" s="9">
+        <f>B12+B13+B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="10">
+        <f>B15/52.7585</f>
+        <v/>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Tamamı öz kaynaktan karşılanır</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>TOPLAM YATIRIM (KDV hariç)</t>
         </is>
       </c>
-      <c r="B15" s="13">
-        <f>B9+B14</f>
-        <v/>
-      </c>
-      <c r="C15" s="14">
-        <f>B15/52.7585</f>
-        <v/>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="B16" s="13">
+        <f>B9+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="14">
+        <f>B16/52.7585</f>
+        <v/>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>Uygun harcama + uygun olmayan harcama</t>
         </is>
@@ -6843,7 +6862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -6896,7 +6915,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24169695.26</v>
+        <v>24879695.26</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -6966,57 +6985,76 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Hibe dışı kümes ısıtma sistemi — ayrı lot</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>710000</v>
+      </c>
+      <c r="C9" s="6">
+        <f>B9/52.7585</f>
+        <v/>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>Proforma fatura</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
         <is>
           <t>UYGUN OLMAYAN HARCAMA — toplam</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
-        <v>8592975.42</v>
-      </c>
-      <c r="C9" s="10">
-        <f>B9/52.7585</f>
-        <v/>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="B10" s="9" t="n">
+        <v>9302975.42</v>
+      </c>
+      <c r="C10" s="10">
+        <f>B10/52.7585</f>
+        <v/>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>Öz kaynak</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>IPARD III broyler uygun harcama üst limiti (375.000,00 Avro) — uygun harcama limitin altındadır</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>19784437.5</v>
-      </c>
-      <c r="C10" s="6">
-        <f>B10/52.7585</f>
-        <v/>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>Çağrı rehberi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>KDV — IPARD'da uygun harcama değildir</t>
+          <t>IPARD III broyler uygun harcama üst limiti (375.000,00 Avro) — uygun harcama limitin altındadır</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4833939.05</v>
+        <v>19784437.5</v>
       </c>
       <c r="C11" s="6">
         <f>B11/52.7585</f>
         <v/>
       </c>
       <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Çağrı rehberi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>KDV — IPARD'da uygun harcama değildir</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>4975939.05</v>
+      </c>
+      <c r="C12" s="6">
+        <f>B12/52.7585</f>
+        <v/>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Öz kaynak</t>
         </is>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>'A3.4-EK Yapım'!H51</f>
+        <f>'A3.4-EK Yapım'!H56</f>
         <v/>
       </c>
       <c r="C12" s="6">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="E13" s="20" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>1200</v>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="E16" s="20" t="n">
-        <v>90</v>
+        <v>45.72</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>4500</v>
@@ -4757,7 +4757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5049,25 +5049,25 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="20" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>Gübre Çukuru</t>
+          <t>Yağmur Suyu Deposu</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>15.120.1101</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Makine ile her derinlik ve her genişlikte yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="F11" s="20" t="n">
-        <v>11.934</v>
+        <v>88.75</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2750.454</v>
+        <v>60.354</v>
       </c>
       <c r="H11" s="5">
         <f>F11*G11</f>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>Ölü Atma Çukuru</t>
+          <t>Gübre Çukuru</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="F12" s="20" t="n">
-        <v>1.984</v>
+        <v>11.934</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>2750.454</v>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Foseptik</t>
+          <t>Ölü Atma Çukuru</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>0.484</v>
+        <v>1.984</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>2750.454</v>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
+          <t>Foseptik</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="F14" s="20" t="n">
-        <v>1.922</v>
+        <v>0.484</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>2750.454</v>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Su Deposu</t>
+          <t>Yem Silosu Betonarme Kaideleri</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>1.344</v>
+        <v>1.922</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>2750.454</v>
@@ -5237,22 +5237,22 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Gübre Çukuru</t>
+          <t>Su Deposu</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="F16" s="20" t="n">
-        <v>93.19</v>
+        <v>1.344</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2960.454</v>
+        <v>2750.454</v>
       </c>
       <c r="H16" s="5">
         <f>F16*G16</f>
@@ -5274,22 +5274,22 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Ölü Atma Çukuru</t>
+          <t>Yağmur Suyu Deposu</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="F17" s="20" t="n">
-        <v>20.85</v>
+        <v>1.024</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>2960.454</v>
+        <v>2750.454</v>
       </c>
       <c r="H17" s="5">
         <f>F17*G17</f>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Su Deposu</t>
+          <t>Gübre Çukuru</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="F18" s="20" t="n">
-        <v>15.15</v>
+        <v>93.19</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>2960.454</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Foseptik</t>
+          <t>Ölü Atma Çukuru</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="F19" s="20" t="n">
-        <v>6.175</v>
+        <v>20.85</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>2960.454</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
+          <t>Su Deposu</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="F20" s="20" t="n">
-        <v>8.41</v>
+        <v>15.15</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>2960.454</v>
@@ -5419,111 +5419,111 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="14" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Gübre Çukuru</t>
+          <t>Yağmur Suyu Deposu</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>363.26</v>
+        <v>12.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>863.7972</v>
+        <v>2960.454</v>
       </c>
       <c r="H21" s="5">
         <f>F21*G21</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="14" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Ölü Atma Çukuru</t>
+          <t>Foseptik</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F22" s="20" t="n">
-        <v>127.2</v>
+        <v>6.175</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>863.7972</v>
+        <v>2960.454</v>
       </c>
       <c r="H22" s="5">
         <f>F22*G22</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="14" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Su Deposu</t>
+          <t>Yem Silosu Betonarme Kaideleri</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F23" s="20" t="n">
-        <v>95.59999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>863.7972</v>
+        <v>2960.454</v>
       </c>
       <c r="H23" s="5">
         <f>F23*G23</f>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>Foseptik</t>
+          <t>Gübre Çukuru</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="F24" s="20" t="n">
-        <v>41.4</v>
+        <v>363.26</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>863.7972</v>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
+          <t>Ölü Atma Çukuru</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="F25" s="20" t="n">
-        <v>11.6</v>
+        <v>127.2</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>863.7972</v>
@@ -5604,148 +5604,148 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26" ht="14" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>Gübre Çukuru</t>
+          <t>Su Deposu</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F26" s="20" t="n">
-        <v>7.599</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>39045.2412</v>
+        <v>863.7972</v>
       </c>
       <c r="H26" s="5">
         <f>F26*G26</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
+    <row r="27" ht="14" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Gübre Çukuru</t>
+          <t>Yağmur Suyu Deposu</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F27" s="20" t="n">
-        <v>0.5639999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>37532.1912</v>
+        <v>863.7972</v>
       </c>
       <c r="H27" s="5">
         <f>F27*G27</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
+    <row r="28" ht="14" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>Ölü Atma Çukuru</t>
+          <t>Foseptik</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F28" s="20" t="n">
-        <v>1.657</v>
+        <v>41.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>39045.2412</v>
+        <v>863.7972</v>
       </c>
       <c r="H28" s="5">
         <f>F28*G28</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
+    <row r="29" ht="14" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Foseptik</t>
+          <t>Yem Silosu Betonarme Kaideleri</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F29" s="20" t="n">
-        <v>0.587</v>
+        <v>11.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>39045.2412</v>
+        <v>863.7972</v>
       </c>
       <c r="H29" s="5">
         <f>F29*G29</f>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
+          <t>Gübre Çukuru</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="F30" s="20" t="n">
-        <v>0.757</v>
+        <v>7.599</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>39045.2412</v>
@@ -5797,17 +5797,17 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Su Deposu</t>
+          <t>Gübre Çukuru</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
@@ -5816,121 +5816,121 @@
         </is>
       </c>
       <c r="F31" s="20" t="n">
-        <v>1.232</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>39045.2412</v>
+        <v>37532.1912</v>
       </c>
       <c r="H31" s="5">
         <f>F31*G31</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="20" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Ölü Atma Çukuru</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0042</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F32" s="20" t="n">
-        <v>1204.98</v>
+        <v>1.657</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>1364.7228</v>
+        <v>39045.2412</v>
       </c>
       <c r="H32" s="5">
         <f>F32*G32</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" ht="20" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Foseptik</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0042</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>1204.98</v>
+        <v>0.587</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1364.7228</v>
+        <v>39045.2412</v>
       </c>
       <c r="H33" s="5">
         <f>F33*G33</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="14" customHeight="1">
+    <row r="34" ht="20" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>Çevre düzenlemesi ve çit işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+          <t>Yem Silosu Betonarme Kaideleri</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>361.04</v>
+        <v>0.757</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>940.842</v>
+        <v>39045.2412</v>
       </c>
       <c r="H34" s="5">
         <f>F34*G34</f>
@@ -5940,96 +5940,96 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+          <t>Su Deposu</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F35" s="20" t="n">
-        <v>50</v>
+        <v>1.232</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>330.6996</v>
+        <v>39045.2412</v>
       </c>
       <c r="H35" s="5">
         <f>F35*G35</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="20" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+          <t>Yağmur Suyu Deposu</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F36" s="20" t="n">
-        <v>1.566</v>
+        <v>1.23</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>2960.454</v>
+        <v>39045.2412</v>
       </c>
       <c r="H36" s="5">
         <f>F36*G36</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="14" customHeight="1">
+    <row r="37" ht="30" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>TKDK-0042</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
@@ -6038,47 +6038,47 @@
         </is>
       </c>
       <c r="F37" s="20" t="n">
-        <v>14.4</v>
+        <v>1204.98</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>863.7972</v>
+        <v>1364.7228</v>
       </c>
       <c r="H37" s="5">
         <f>F37*G37</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>TKDK-0042</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F38" s="20" t="n">
-        <v>0.141</v>
+        <v>1204.98</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>39045.2412</v>
+        <v>1364.7228</v>
       </c>
       <c r="H38" s="5">
         <f>F38*G38</f>
@@ -6088,7 +6088,7 @@
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Çevre düzenlemesi ve çit işleri</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
@@ -6098,24 +6098,24 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>15.560.1003</t>
+          <t>TKDK-0091</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
+          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F39" s="20" t="n">
-        <v>4</v>
+        <v>361.04</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>3744.3</v>
+        <v>940.842</v>
       </c>
       <c r="H39" s="5">
         <f>F39*G39</f>
@@ -6125,7 +6125,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
@@ -6135,34 +6135,34 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>30.100.1104</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>41783.1288</v>
+        <v>330.6996</v>
       </c>
       <c r="H40" s="5">
         <f>F40*G40</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="14" customHeight="1">
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
@@ -6172,34 +6172,34 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>30.100.2106</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>1</v>
+        <v>1.566</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>11631.648</v>
+        <v>2960.454</v>
       </c>
       <c r="H41" s="5">
         <f>F41*G41</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
+    <row r="42" ht="14" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B42" s="17" t="inlineStr">
@@ -6209,34 +6209,34 @@
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>30.135.3201</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1</v>
+        <v>14.4</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>2218.1544</v>
+        <v>863.7972</v>
       </c>
       <c r="H42" s="5">
         <f>F42*G42</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
+    <row r="43" ht="20" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
@@ -6246,24 +6246,24 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>30.110.1104</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>1</v>
+        <v>0.141</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>5920.7568</v>
+        <v>39045.2412</v>
       </c>
       <c r="H43" s="5">
         <f>F43*G43</f>
@@ -6273,7 +6273,7 @@
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>15.560.1003</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1436.1984</v>
+        <v>3744.3</v>
       </c>
       <c r="H44" s="5">
         <f>F44*G44</f>
@@ -6320,31 +6320,31 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>30.140.3105</t>
+          <t>30.100.1104</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>332.1696</v>
+        <v>41783.1288</v>
       </c>
       <c r="H45" s="5">
         <f>F45*G45</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
+    <row r="46" ht="14" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6357,24 +6357,24 @@
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>30.140.3101</t>
+          <t>30.100.2106</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>71.3244</v>
+        <v>11631.648</v>
       </c>
       <c r="H46" s="5">
         <f>F46*G46</f>
@@ -6394,12 +6394,12 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>30.172.1706</t>
+          <t>30.135.3201</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
@@ -6408,10 +6408,10 @@
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>7783.1208</v>
+        <v>2218.1544</v>
       </c>
       <c r="H47" s="5">
         <f>F47*G47</f>
@@ -6431,12 +6431,12 @@
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>30.170.4002</t>
+          <t>30.110.1104</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>LED projektör, ışık akısı en az 5100 lm</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>8313.1608</v>
+        <v>5920.7568</v>
       </c>
       <c r="H48" s="5">
         <f>F48*G48</f>
@@ -6463,17 +6463,17 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>30.120.2016</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
@@ -6482,17 +6482,17 @@
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>44709.8148</v>
+        <v>1436.1984</v>
       </c>
       <c r="H49" s="5">
         <f>F49*G49</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="14" customHeight="1">
+    <row r="50" ht="20" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6500,49 +6500,234 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>30.120.2016</t>
+          <t>30.140.3105</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>44709.8148</v>
+        <v>332.1696</v>
       </c>
       <c r="H50" s="5">
         <f>F50*G50</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="21" t="n"/>
-      <c r="B51" s="21" t="n"/>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="22" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>30.140.3101</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>71.3244</v>
+      </c>
+      <c r="H51" s="5">
+        <f>F51*G51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>30.172.1706</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F52" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>7783.1208</v>
+      </c>
+      <c r="H52" s="5">
+        <f>F52*G52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>30.170.4002</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>LED projektör, ışık akısı en az 5100 lm</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>8313.1608</v>
+      </c>
+      <c r="H53" s="5">
+        <f>F53*G53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>30.120.2016</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>Otomatik transfer şalteri 4 x 200 A</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F54" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>44709.8148</v>
+      </c>
+      <c r="H54" s="5">
+        <f>F54*G54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>30.120.2016</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>Otomatik transfer şalteri 4 x 200 A</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>44709.8148</v>
+      </c>
+      <c r="H55" s="5">
+        <f>F55*G55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="n"/>
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="22" t="inlineStr">
         <is>
           <t>HİBE DIŞI YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E51" s="21" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
-      <c r="H51" s="9">
-        <f>SUM(H5:H50)</f>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="9">
+        <f>SUM(H5:H55)</f>
         <v/>
       </c>
     </row>
@@ -6915,7 +7100,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24879695.26</v>
+        <v>24817978.39</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -6953,7 +7138,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5497755.42</v>
+        <v>5659298.55</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -6972,7 +7157,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3095220</v>
+        <v>2871960</v>
       </c>
       <c r="C8" s="6">
         <f>B8/52.7585</f>
@@ -7010,7 +7195,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9302975.42</v>
+        <v>9241258.550000001</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7048,7 +7233,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4975939.05</v>
+        <v>4963595.68</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -1907,7 +1907,7 @@
         <v>1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>10082.96</v>
+        <v>7084.16</v>
       </c>
       <c r="H32" s="5">
         <f>F32*G32</f>
@@ -1944,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>4435.25</v>
+        <v>3528.05</v>
       </c>
       <c r="H33" s="5">
         <f>F33*G33</f>
@@ -1981,7 +1981,7 @@
         <v>2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1436.2</v>
+        <v>1079.2</v>
       </c>
       <c r="H34" s="5">
         <f>F34*G34</f>
@@ -2018,7 +2018,7 @@
         <v>300</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>244.02</v>
+        <v>200</v>
       </c>
       <c r="H35" s="5">
         <f>F35*G35</f>
@@ -2055,7 +2055,7 @@
         <v>30</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>2222.88</v>
+        <v>1996.08</v>
       </c>
       <c r="H36" s="5">
         <f>F36*G36</f>
@@ -2092,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1552.4</v>
+        <v>1370.96</v>
       </c>
       <c r="H37" s="5">
         <f>F37*G37</f>
@@ -2129,7 +2129,7 @@
         <v>500</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>74.42</v>
+        <v>29.06</v>
       </c>
       <c r="H38" s="5">
         <f>F38*G38</f>
@@ -2166,7 +2166,7 @@
         <v>2000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>33.1</v>
+        <v>19.5</v>
       </c>
       <c r="H39" s="5">
         <f>F39*G39</f>
@@ -2203,7 +2203,7 @@
         <v>600</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>23.56</v>
+        <v>12.22</v>
       </c>
       <c r="H40" s="5">
         <f>F40*G40</f>
@@ -2240,7 +2240,7 @@
         <v>100</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>188.13</v>
+        <v>157.05</v>
       </c>
       <c r="H41" s="5">
         <f>F41*G41</f>
@@ -2277,7 +2277,7 @@
         <v>186</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>156.11</v>
+        <v>115.96</v>
       </c>
       <c r="H42" s="5">
         <f>F42*G42</f>
@@ -2314,7 +2314,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>17410.01</v>
+        <v>15595.61</v>
       </c>
       <c r="H43" s="5">
         <f>F43*G43</f>
@@ -2351,7 +2351,7 @@
         <v>16</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>481.15</v>
+        <v>426.72</v>
       </c>
       <c r="H44" s="5">
         <f>F44*G44</f>
@@ -2388,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>484082.09</v>
+        <v>467349.29</v>
       </c>
       <c r="H45" s="5">
         <f>F45*G45</f>
@@ -2425,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>83282.35000000001</v>
+        <v>79653.55</v>
       </c>
       <c r="H46" s="5">
         <f>F46*G46</f>
@@ -3461,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>10082.96</v>
+        <v>7084.16</v>
       </c>
       <c r="H74" s="5">
         <f>F74*G74</f>
@@ -3498,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>4435.25</v>
+        <v>3528.05</v>
       </c>
       <c r="H75" s="5">
         <f>F75*G75</f>
@@ -3535,7 +3535,7 @@
         <v>2</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1436.2</v>
+        <v>1079.2</v>
       </c>
       <c r="H76" s="5">
         <f>F76*G76</f>
@@ -3572,7 +3572,7 @@
         <v>300</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>244.02</v>
+        <v>200</v>
       </c>
       <c r="H77" s="5">
         <f>F77*G77</f>
@@ -3609,7 +3609,7 @@
         <v>30</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>2222.88</v>
+        <v>1996.08</v>
       </c>
       <c r="H78" s="5">
         <f>F78*G78</f>
@@ -3646,7 +3646,7 @@
         <v>2</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1552.4</v>
+        <v>1370.96</v>
       </c>
       <c r="H79" s="5">
         <f>F79*G79</f>
@@ -3683,7 +3683,7 @@
         <v>500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>74.42</v>
+        <v>29.06</v>
       </c>
       <c r="H80" s="5">
         <f>F80*G80</f>
@@ -3720,7 +3720,7 @@
         <v>2000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>33.1</v>
+        <v>19.5</v>
       </c>
       <c r="H81" s="5">
         <f>F81*G81</f>
@@ -3757,7 +3757,7 @@
         <v>600</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>23.56</v>
+        <v>12.22</v>
       </c>
       <c r="H82" s="5">
         <f>F82*G82</f>
@@ -3794,7 +3794,7 @@
         <v>100</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>188.13</v>
+        <v>157.05</v>
       </c>
       <c r="H83" s="5">
         <f>F83*G83</f>
@@ -3831,7 +3831,7 @@
         <v>186</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>156.11</v>
+        <v>115.96</v>
       </c>
       <c r="H84" s="5">
         <f>F84*G84</f>
@@ -3868,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>17410.01</v>
+        <v>15595.61</v>
       </c>
       <c r="H85" s="5">
         <f>F85*G85</f>
@@ -3905,7 +3905,7 @@
         <v>16</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>481.15</v>
+        <v>426.72</v>
       </c>
       <c r="H86" s="5">
         <f>F86*G86</f>
@@ -3942,7 +3942,7 @@
         <v>1</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>484082.09</v>
+        <v>467349.29</v>
       </c>
       <c r="H87" s="5">
         <f>F87*G87</f>
@@ -3979,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>83282.35000000001</v>
+        <v>79653.55</v>
       </c>
       <c r="H88" s="5">
         <f>F88*G88</f>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik)</t>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -6337,14 +6337,14 @@
         <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>41783.1288</v>
+        <v>31602.3288</v>
       </c>
       <c r="H45" s="5">
         <f>F45*G45</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="14" customHeight="1">
+    <row r="46" ht="20" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²)</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
@@ -6374,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>11631.648</v>
+        <v>8179.248</v>
       </c>
       <c r="H46" s="5">
         <f>F46*G46</f>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
@@ -6411,14 +6411,14 @@
         <v>1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>2218.1544</v>
+        <v>1504.1544</v>
       </c>
       <c r="H47" s="5">
         <f>F47*G47</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
+    <row r="48" ht="20" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
@@ -6448,14 +6448,14 @@
         <v>1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>5920.7568</v>
+        <v>4753.1568</v>
       </c>
       <c r="H48" s="5">
         <f>F48*G48</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="14" customHeight="1">
+    <row r="49" ht="20" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
@@ -6485,7 +6485,7 @@
         <v>2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1436.1984</v>
+        <v>1079.1984</v>
       </c>
       <c r="H49" s="5">
         <f>F49*G49</f>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm²</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
@@ -6522,7 +6522,7 @@
         <v>50</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>332.1696</v>
+        <v>277.1496</v>
       </c>
       <c r="H50" s="5">
         <f>F50*G50</f>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm²</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
@@ -6559,7 +6559,7 @@
         <v>50</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>71.3244</v>
+        <v>51.2484</v>
       </c>
       <c r="H51" s="5">
         <f>F51*G51</f>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m</t>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
@@ -6596,14 +6596,14 @@
         <v>4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>7783.1208</v>
+        <v>6229.1208</v>
       </c>
       <c r="H52" s="5">
         <f>F52*G52</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="14" customHeight="1">
+    <row r="53" ht="20" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>LED projektör, ışık akısı en az 5100 lm</t>
+          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -6633,14 +6633,14 @@
         <v>4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>8313.1608</v>
+        <v>7632.7608</v>
       </c>
       <c r="H53" s="5">
         <f>F53*G53</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="14" customHeight="1">
+    <row r="54" ht="20" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
@@ -6670,14 +6670,14 @@
         <v>1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>44709.8148</v>
+        <v>38544.2148</v>
       </c>
       <c r="H54" s="5">
         <f>F54*G54</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="14" customHeight="1">
+    <row r="55" ht="20" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
@@ -6707,7 +6707,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>44709.8148</v>
+        <v>38544.2148</v>
       </c>
       <c r="H55" s="5">
         <f>F55*G55</f>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24817978.39</v>
+        <v>24546126.67</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15576719.84</v>
+        <v>15346120.52</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5659298.55</v>
+        <v>5618046.15</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9241258.550000001</v>
+        <v>9200006.15</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4963595.68</v>
+        <v>4909225.33</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -1520,24 +1520,24 @@
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan iniş borusu yapılması — ø100</t>
+          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F22" s="20" t="n">
-        <v>40.96</v>
+        <v>51.2</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>227.85</v>
+        <v>174.22</v>
       </c>
       <c r="H22" s="5">
         <f>F22*G22</f>
@@ -3074,24 +3074,24 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan iniş borusu yapılması — ø100</t>
+          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>40.96</v>
+        <v>51.2</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>227.85</v>
+        <v>174.22</v>
       </c>
       <c r="H64" s="5">
         <f>F64*G64</f>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24546126.67</v>
+        <v>24545301.31</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15346120.52</v>
+        <v>15345295.16</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4909225.33</v>
+        <v>4909060.26</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -4780,7 +4780,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kümes A ve B blokları dışındaki yapılar ile bu iki bloktan hibe kapsamı dışına çıkarılan pozlar. Bu imalatlar yapılmaya devam eder; teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir ve tamamı öz kaynaktan karşılanır.</t>
+          <t>Kümes A ve B blokları dışındaki yapılar ile bu iki bloktan hibe kapsamı dışına çıkarılan pozlar. Bu imalatlar yapılmaya devam eder; teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir ve tamamı öz kaynaktan karşılanır. Birim fiyatlar kitabın kendi fiyatlarıdır; %16 tenzilat uygulanmaz, çünkü tenzilat idarenin yaklaşık maliyet beklentisidir, satıcının fiyatı değildir.</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
         <v>260.942</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>52.374</v>
+        <v>62.35</v>
       </c>
       <c r="H5" s="5">
         <f>F5*G5</f>
@@ -4894,7 +4894,7 @@
         <v>542.7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>60.354</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H6" s="5">
         <f>F6*G6</f>
@@ -4931,7 +4931,7 @@
         <v>142</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>60.354</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H7" s="5">
         <f>F7*G7</f>
@@ -4968,7 +4968,7 @@
         <v>48.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>60.354</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H8" s="5">
         <f>F8*G8</f>
@@ -5005,7 +5005,7 @@
         <v>48.02</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>60.354</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H9" s="5">
         <f>F9*G9</f>
@@ -5042,7 +5042,7 @@
         <v>106.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>60.354</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H10" s="5">
         <f>F10*G10</f>
@@ -5079,7 +5079,7 @@
         <v>88.75</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>60.354</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H11" s="5">
         <f>F11*G11</f>
@@ -5116,7 +5116,7 @@
         <v>11.934</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2750.454</v>
+        <v>3274.35</v>
       </c>
       <c r="H12" s="5">
         <f>F12*G12</f>
@@ -5153,7 +5153,7 @@
         <v>1.984</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>2750.454</v>
+        <v>3274.35</v>
       </c>
       <c r="H13" s="5">
         <f>F13*G13</f>
@@ -5190,7 +5190,7 @@
         <v>0.484</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2750.454</v>
+        <v>3274.35</v>
       </c>
       <c r="H14" s="5">
         <f>F14*G14</f>
@@ -5227,7 +5227,7 @@
         <v>1.922</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>2750.454</v>
+        <v>3274.35</v>
       </c>
       <c r="H15" s="5">
         <f>F15*G15</f>
@@ -5264,7 +5264,7 @@
         <v>1.344</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>2750.454</v>
+        <v>3274.35</v>
       </c>
       <c r="H16" s="5">
         <f>F16*G16</f>
@@ -5301,7 +5301,7 @@
         <v>1.024</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>2750.454</v>
+        <v>3274.35</v>
       </c>
       <c r="H17" s="5">
         <f>F17*G17</f>
@@ -5338,7 +5338,7 @@
         <v>93.19</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>2960.454</v>
+        <v>3524.35</v>
       </c>
       <c r="H18" s="5">
         <f>F18*G18</f>
@@ -5375,7 +5375,7 @@
         <v>20.85</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2960.454</v>
+        <v>3524.35</v>
       </c>
       <c r="H19" s="5">
         <f>F19*G19</f>
@@ -5412,7 +5412,7 @@
         <v>15.15</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>2960.454</v>
+        <v>3524.35</v>
       </c>
       <c r="H20" s="5">
         <f>F20*G20</f>
@@ -5449,7 +5449,7 @@
         <v>12.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>2960.454</v>
+        <v>3524.35</v>
       </c>
       <c r="H21" s="5">
         <f>F21*G21</f>
@@ -5486,7 +5486,7 @@
         <v>6.175</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>2960.454</v>
+        <v>3524.35</v>
       </c>
       <c r="H22" s="5">
         <f>F22*G22</f>
@@ -5523,7 +5523,7 @@
         <v>8.41</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>2960.454</v>
+        <v>3524.35</v>
       </c>
       <c r="H23" s="5">
         <f>F23*G23</f>
@@ -5560,7 +5560,7 @@
         <v>363.26</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>863.7972</v>
+        <v>1028.33</v>
       </c>
       <c r="H24" s="5">
         <f>F24*G24</f>
@@ -5597,7 +5597,7 @@
         <v>127.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>863.7972</v>
+        <v>1028.33</v>
       </c>
       <c r="H25" s="5">
         <f>F25*G25</f>
@@ -5634,7 +5634,7 @@
         <v>95.59999999999999</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>863.7972</v>
+        <v>1028.33</v>
       </c>
       <c r="H26" s="5">
         <f>F26*G26</f>
@@ -5671,7 +5671,7 @@
         <v>79.8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>863.7972</v>
+        <v>1028.33</v>
       </c>
       <c r="H27" s="5">
         <f>F27*G27</f>
@@ -5708,7 +5708,7 @@
         <v>41.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>863.7972</v>
+        <v>1028.33</v>
       </c>
       <c r="H28" s="5">
         <f>F28*G28</f>
@@ -5745,7 +5745,7 @@
         <v>11.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>863.7972</v>
+        <v>1028.33</v>
       </c>
       <c r="H29" s="5">
         <f>F29*G29</f>
@@ -5782,7 +5782,7 @@
         <v>7.599</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>39045.2412</v>
+        <v>46482.43</v>
       </c>
       <c r="H30" s="5">
         <f>F30*G30</f>
@@ -5819,7 +5819,7 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>37532.1912</v>
+        <v>44681.18</v>
       </c>
       <c r="H31" s="5">
         <f>F31*G31</f>
@@ -5856,7 +5856,7 @@
         <v>1.657</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>39045.2412</v>
+        <v>46482.43</v>
       </c>
       <c r="H32" s="5">
         <f>F32*G32</f>
@@ -5893,7 +5893,7 @@
         <v>0.587</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>39045.2412</v>
+        <v>46482.43</v>
       </c>
       <c r="H33" s="5">
         <f>F33*G33</f>
@@ -5930,7 +5930,7 @@
         <v>0.757</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>39045.2412</v>
+        <v>46482.43</v>
       </c>
       <c r="H34" s="5">
         <f>F34*G34</f>
@@ -5967,7 +5967,7 @@
         <v>1.232</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>39045.2412</v>
+        <v>46482.43</v>
       </c>
       <c r="H35" s="5">
         <f>F35*G35</f>
@@ -6004,7 +6004,7 @@
         <v>1.23</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>39045.2412</v>
+        <v>46482.43</v>
       </c>
       <c r="H36" s="5">
         <f>F36*G36</f>
@@ -6041,7 +6041,7 @@
         <v>1204.98</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1364.7228</v>
+        <v>1624.67</v>
       </c>
       <c r="H37" s="5">
         <f>F37*G37</f>
@@ -6078,7 +6078,7 @@
         <v>1204.98</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1364.7228</v>
+        <v>1624.67</v>
       </c>
       <c r="H38" s="5">
         <f>F38*G38</f>
@@ -6115,7 +6115,7 @@
         <v>361.04</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>940.842</v>
+        <v>1120.05</v>
       </c>
       <c r="H39" s="5">
         <f>F39*G39</f>
@@ -6152,7 +6152,7 @@
         <v>50</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>330.6996</v>
+        <v>393.69</v>
       </c>
       <c r="H40" s="5">
         <f>F40*G40</f>
@@ -6189,7 +6189,7 @@
         <v>1.566</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>2960.454</v>
+        <v>3524.35</v>
       </c>
       <c r="H41" s="5">
         <f>F41*G41</f>
@@ -6226,7 +6226,7 @@
         <v>14.4</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>863.7972</v>
+        <v>1028.33</v>
       </c>
       <c r="H42" s="5">
         <f>F42*G42</f>
@@ -6263,7 +6263,7 @@
         <v>0.141</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>39045.2412</v>
+        <v>46482.43</v>
       </c>
       <c r="H43" s="5">
         <f>F43*G43</f>
@@ -6300,7 +6300,7 @@
         <v>4</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>3744.3</v>
+        <v>4457.5</v>
       </c>
       <c r="H44" s="5">
         <f>F44*G44</f>
@@ -6337,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>31602.3288</v>
+        <v>37621.82</v>
       </c>
       <c r="H45" s="5">
         <f>F45*G45</f>
@@ -6374,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>8179.248</v>
+        <v>9737.200000000001</v>
       </c>
       <c r="H46" s="5">
         <f>F46*G46</f>
@@ -6411,7 +6411,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1504.1544</v>
+        <v>1790.66</v>
       </c>
       <c r="H47" s="5">
         <f>F47*G47</f>
@@ -6448,7 +6448,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>4753.1568</v>
+        <v>5658.52</v>
       </c>
       <c r="H48" s="5">
         <f>F48*G48</f>
@@ -6485,7 +6485,7 @@
         <v>2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1079.1984</v>
+        <v>1284.76</v>
       </c>
       <c r="H49" s="5">
         <f>F49*G49</f>
@@ -6522,7 +6522,7 @@
         <v>50</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>277.1496</v>
+        <v>329.94</v>
       </c>
       <c r="H50" s="5">
         <f>F50*G50</f>
@@ -6559,7 +6559,7 @@
         <v>50</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>51.2484</v>
+        <v>61.01</v>
       </c>
       <c r="H51" s="5">
         <f>F51*G51</f>
@@ -6596,7 +6596,7 @@
         <v>4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>6229.1208</v>
+        <v>7415.62</v>
       </c>
       <c r="H52" s="5">
         <f>F52*G52</f>
@@ -6633,7 +6633,7 @@
         <v>4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>7632.7608</v>
+        <v>9086.620000000001</v>
       </c>
       <c r="H53" s="5">
         <f>F53*G53</f>
@@ -6670,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>38544.2148</v>
+        <v>45885.97</v>
       </c>
       <c r="H54" s="5">
         <f>F54*G54</f>
@@ -6707,7 +6707,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>38544.2148</v>
+        <v>45885.97</v>
       </c>
       <c r="H55" s="5">
         <f>F55*G55</f>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24545301.31</v>
+        <v>25615426.2</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5618046.15</v>
+        <v>6688171.04</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9200006.15</v>
+        <v>10270131.04</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4909060.26</v>
+        <v>5123085.24</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -4780,7 +4780,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kümes A ve B blokları dışındaki yapılar ile bu iki bloktan hibe kapsamı dışına çıkarılan pozlar. Bu imalatlar yapılmaya devam eder; teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir ve tamamı öz kaynaktan karşılanır. Birim fiyatlar kitabın kendi fiyatlarıdır; %16 tenzilat uygulanmaz, çünkü tenzilat idarenin yaklaşık maliyet beklentisidir, satıcının fiyatı değildir.</t>
+          <t>Kümes A ve B blokları dışındaki yapılar ile bu iki bloktan hibe kapsamı dışına çıkarılan pozlar. Bu imalatlar yapılmaya devam eder; teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir ve tamamı öz kaynaktan karşılanır. Birim fiyatlar, hibe kapsamındaki işlerle aynı esasa göre kurulmuştur: ÇŞB 2026 ve TKDK 17.02.2026 kitap fiyatlarına %16 tenzilat uygulanmıştır.</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
         <v>260.942</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>62.35</v>
+        <v>52.37</v>
       </c>
       <c r="H5" s="5">
         <f>F5*G5</f>
@@ -4894,7 +4894,7 @@
         <v>542.7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>71.84999999999999</v>
+        <v>60.35</v>
       </c>
       <c r="H6" s="5">
         <f>F6*G6</f>
@@ -4931,7 +4931,7 @@
         <v>142</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>71.84999999999999</v>
+        <v>60.35</v>
       </c>
       <c r="H7" s="5">
         <f>F7*G7</f>
@@ -4968,7 +4968,7 @@
         <v>48.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>71.84999999999999</v>
+        <v>60.35</v>
       </c>
       <c r="H8" s="5">
         <f>F8*G8</f>
@@ -5005,7 +5005,7 @@
         <v>48.02</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>71.84999999999999</v>
+        <v>60.35</v>
       </c>
       <c r="H9" s="5">
         <f>F9*G9</f>
@@ -5042,7 +5042,7 @@
         <v>106.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>71.84999999999999</v>
+        <v>60.35</v>
       </c>
       <c r="H10" s="5">
         <f>F10*G10</f>
@@ -5079,7 +5079,7 @@
         <v>88.75</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>71.84999999999999</v>
+        <v>60.35</v>
       </c>
       <c r="H11" s="5">
         <f>F11*G11</f>
@@ -5116,7 +5116,7 @@
         <v>11.934</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>3274.35</v>
+        <v>2750.45</v>
       </c>
       <c r="H12" s="5">
         <f>F12*G12</f>
@@ -5153,7 +5153,7 @@
         <v>1.984</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>3274.35</v>
+        <v>2750.45</v>
       </c>
       <c r="H13" s="5">
         <f>F13*G13</f>
@@ -5190,7 +5190,7 @@
         <v>0.484</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>3274.35</v>
+        <v>2750.45</v>
       </c>
       <c r="H14" s="5">
         <f>F14*G14</f>
@@ -5227,7 +5227,7 @@
         <v>1.922</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>3274.35</v>
+        <v>2750.45</v>
       </c>
       <c r="H15" s="5">
         <f>F15*G15</f>
@@ -5264,7 +5264,7 @@
         <v>1.344</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>3274.35</v>
+        <v>2750.45</v>
       </c>
       <c r="H16" s="5">
         <f>F16*G16</f>
@@ -5301,7 +5301,7 @@
         <v>1.024</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3274.35</v>
+        <v>2750.45</v>
       </c>
       <c r="H17" s="5">
         <f>F17*G17</f>
@@ -5338,7 +5338,7 @@
         <v>93.19</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>3524.35</v>
+        <v>2960.45</v>
       </c>
       <c r="H18" s="5">
         <f>F18*G18</f>
@@ -5375,7 +5375,7 @@
         <v>20.85</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3524.35</v>
+        <v>2960.45</v>
       </c>
       <c r="H19" s="5">
         <f>F19*G19</f>
@@ -5412,7 +5412,7 @@
         <v>15.15</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>3524.35</v>
+        <v>2960.45</v>
       </c>
       <c r="H20" s="5">
         <f>F20*G20</f>
@@ -5449,7 +5449,7 @@
         <v>12.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>3524.35</v>
+        <v>2960.45</v>
       </c>
       <c r="H21" s="5">
         <f>F21*G21</f>
@@ -5486,7 +5486,7 @@
         <v>6.175</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>3524.35</v>
+        <v>2960.45</v>
       </c>
       <c r="H22" s="5">
         <f>F22*G22</f>
@@ -5523,7 +5523,7 @@
         <v>8.41</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>3524.35</v>
+        <v>2960.45</v>
       </c>
       <c r="H23" s="5">
         <f>F23*G23</f>
@@ -5560,7 +5560,7 @@
         <v>363.26</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1028.33</v>
+        <v>863.8</v>
       </c>
       <c r="H24" s="5">
         <f>F24*G24</f>
@@ -5597,7 +5597,7 @@
         <v>127.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1028.33</v>
+        <v>863.8</v>
       </c>
       <c r="H25" s="5">
         <f>F25*G25</f>
@@ -5634,7 +5634,7 @@
         <v>95.59999999999999</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1028.33</v>
+        <v>863.8</v>
       </c>
       <c r="H26" s="5">
         <f>F26*G26</f>
@@ -5671,7 +5671,7 @@
         <v>79.8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1028.33</v>
+        <v>863.8</v>
       </c>
       <c r="H27" s="5">
         <f>F27*G27</f>
@@ -5708,7 +5708,7 @@
         <v>41.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1028.33</v>
+        <v>863.8</v>
       </c>
       <c r="H28" s="5">
         <f>F28*G28</f>
@@ -5745,7 +5745,7 @@
         <v>11.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1028.33</v>
+        <v>863.8</v>
       </c>
       <c r="H29" s="5">
         <f>F29*G29</f>
@@ -5782,7 +5782,7 @@
         <v>7.599</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>46482.43</v>
+        <v>39045.24</v>
       </c>
       <c r="H30" s="5">
         <f>F30*G30</f>
@@ -5819,7 +5819,7 @@
         <v>0.5639999999999999</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>44681.18</v>
+        <v>37532.19</v>
       </c>
       <c r="H31" s="5">
         <f>F31*G31</f>
@@ -5856,7 +5856,7 @@
         <v>1.657</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>46482.43</v>
+        <v>39045.24</v>
       </c>
       <c r="H32" s="5">
         <f>F32*G32</f>
@@ -5893,7 +5893,7 @@
         <v>0.587</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>46482.43</v>
+        <v>39045.24</v>
       </c>
       <c r="H33" s="5">
         <f>F33*G33</f>
@@ -5930,7 +5930,7 @@
         <v>0.757</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>46482.43</v>
+        <v>39045.24</v>
       </c>
       <c r="H34" s="5">
         <f>F34*G34</f>
@@ -5967,7 +5967,7 @@
         <v>1.232</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>46482.43</v>
+        <v>39045.24</v>
       </c>
       <c r="H35" s="5">
         <f>F35*G35</f>
@@ -6004,7 +6004,7 @@
         <v>1.23</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>46482.43</v>
+        <v>39045.24</v>
       </c>
       <c r="H36" s="5">
         <f>F36*G36</f>
@@ -6041,7 +6041,7 @@
         <v>1204.98</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1624.67</v>
+        <v>1364.72</v>
       </c>
       <c r="H37" s="5">
         <f>F37*G37</f>
@@ -6078,7 +6078,7 @@
         <v>1204.98</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1624.67</v>
+        <v>1364.72</v>
       </c>
       <c r="H38" s="5">
         <f>F38*G38</f>
@@ -6115,7 +6115,7 @@
         <v>361.04</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1120.05</v>
+        <v>940.84</v>
       </c>
       <c r="H39" s="5">
         <f>F39*G39</f>
@@ -6152,7 +6152,7 @@
         <v>50</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>393.69</v>
+        <v>330.7</v>
       </c>
       <c r="H40" s="5">
         <f>F40*G40</f>
@@ -6189,7 +6189,7 @@
         <v>1.566</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>3524.35</v>
+        <v>2960.45</v>
       </c>
       <c r="H41" s="5">
         <f>F41*G41</f>
@@ -6226,7 +6226,7 @@
         <v>14.4</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1028.33</v>
+        <v>863.8</v>
       </c>
       <c r="H42" s="5">
         <f>F42*G42</f>
@@ -6263,7 +6263,7 @@
         <v>0.141</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>46482.43</v>
+        <v>39045.24</v>
       </c>
       <c r="H43" s="5">
         <f>F43*G43</f>
@@ -6300,7 +6300,7 @@
         <v>4</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>4457.5</v>
+        <v>3744.3</v>
       </c>
       <c r="H44" s="5">
         <f>F44*G44</f>
@@ -6337,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>37621.82</v>
+        <v>31602.33</v>
       </c>
       <c r="H45" s="5">
         <f>F45*G45</f>
@@ -6374,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>9737.200000000001</v>
+        <v>8179.25</v>
       </c>
       <c r="H46" s="5">
         <f>F46*G46</f>
@@ -6411,7 +6411,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1790.66</v>
+        <v>1504.15</v>
       </c>
       <c r="H47" s="5">
         <f>F47*G47</f>
@@ -6448,7 +6448,7 @@
         <v>1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>5658.52</v>
+        <v>4753.16</v>
       </c>
       <c r="H48" s="5">
         <f>F48*G48</f>
@@ -6485,7 +6485,7 @@
         <v>2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1284.76</v>
+        <v>1079.2</v>
       </c>
       <c r="H49" s="5">
         <f>F49*G49</f>
@@ -6522,7 +6522,7 @@
         <v>50</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>329.94</v>
+        <v>277.15</v>
       </c>
       <c r="H50" s="5">
         <f>F50*G50</f>
@@ -6559,7 +6559,7 @@
         <v>50</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>61.01</v>
+        <v>51.25</v>
       </c>
       <c r="H51" s="5">
         <f>F51*G51</f>
@@ -6596,7 +6596,7 @@
         <v>4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>7415.62</v>
+        <v>6229.12</v>
       </c>
       <c r="H52" s="5">
         <f>F52*G52</f>
@@ -6633,7 +6633,7 @@
         <v>4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>9086.620000000001</v>
+        <v>7632.76</v>
       </c>
       <c r="H53" s="5">
         <f>F53*G53</f>
@@ -6670,7 +6670,7 @@
         <v>1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>45885.97</v>
+        <v>38544.21</v>
       </c>
       <c r="H54" s="5">
         <f>F54*G54</f>
@@ -6707,7 +6707,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>45885.97</v>
+        <v>38544.21</v>
       </c>
       <c r="H55" s="5">
         <f>F55*G55</f>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25615426.2</v>
+        <v>24545307.86</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6688171.04</v>
+        <v>5618052.7</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>10270131.04</v>
+        <v>9200012.699999999</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>5123085.24</v>
+        <v>4909061.57</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H89</f>
+        <f>'A3.1.1 Yapım İşleri'!H85</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>'A3.4-EK Yapım'!H56</f>
+        <f>'A3.4-EK Yapım'!H60</f>
         <v/>
       </c>
       <c r="C12" s="6">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2358,37 +2358,37 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="14" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>1</v>
+        <v>1684.38</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>467349.29</v>
+        <v>52.37</v>
       </c>
       <c r="H45" s="5">
         <f>F45*G45</f>
@@ -2398,44 +2398,44 @@
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>1</v>
+        <v>31.4285</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>79653.55</v>
+        <v>2750.45</v>
       </c>
       <c r="H46" s="5">
         <f>F46*G46</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1">
+    <row r="47" ht="20" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
@@ -2459,20 +2459,20 @@
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>1684.38</v>
+        <v>115.71</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>52.37</v>
+        <v>2960.45</v>
       </c>
       <c r="H47" s="5">
         <f>F47*G47</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
+    <row r="48" ht="20" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
@@ -2496,20 +2496,20 @@
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>31.4285</v>
+        <v>162.63</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2750.45</v>
+        <v>2960.45</v>
       </c>
       <c r="H48" s="5">
         <f>F48*G48</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
+    <row r="49" ht="14" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
@@ -2519,34 +2519,34 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>115.71</v>
+        <v>551.26</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2960.45</v>
+        <v>863.8</v>
       </c>
       <c r="H49" s="5">
         <f>F49*G49</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
+    <row r="50" ht="14" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
@@ -2556,24 +2556,24 @@
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
+          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>162.63</v>
+        <v>4.1599</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2960.45</v>
+        <v>39045.24</v>
       </c>
       <c r="H50" s="5">
         <f>F50*G50</f>
@@ -2583,7 +2583,7 @@
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
+          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>551.26</v>
+        <v>7.2875</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>863.8</v>
+        <v>37532.19</v>
       </c>
       <c r="H51" s="5">
         <f>F51*G51</f>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
@@ -2644,20 +2644,20 @@
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>4.1599</v>
+        <v>3.6375</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>39045.24</v>
+        <v>36949.5</v>
       </c>
       <c r="H52" s="5">
         <f>F52*G52</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="14" customHeight="1">
+    <row r="53" ht="20" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -2681,20 +2681,20 @@
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>7.2875</v>
+        <v>44.0481</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>37532.19</v>
+        <v>72192.55</v>
       </c>
       <c r="H53" s="5">
         <f>F53*G53</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="14" customHeight="1">
+    <row r="54" ht="20" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
@@ -2704,24 +2704,24 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F54" s="20" t="n">
-        <v>3.6375</v>
+        <v>507.91</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>36949.5</v>
+        <v>929.28</v>
       </c>
       <c r="H54" s="5">
         <f>F54*G54</f>
@@ -2731,7 +2731,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2741,24 +2741,24 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>44.0481</v>
+        <v>49.85</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>72192.55</v>
+        <v>1777.52</v>
       </c>
       <c r="H55" s="5">
         <f>F55*G55</f>
@@ -2768,7 +2768,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>507.91</v>
+        <v>557.76</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>929.28</v>
+        <v>372.55</v>
       </c>
       <c r="H56" s="5">
         <f>F56*G56</f>
@@ -2805,7 +2805,7 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>49.85</v>
+        <v>557.76</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1777.52</v>
+        <v>381.49</v>
       </c>
       <c r="H57" s="5">
         <f>F57*G57</f>
@@ -2842,7 +2842,7 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
@@ -2869,7 +2869,7 @@
         <v>557.76</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>372.55</v>
+        <v>324.27</v>
       </c>
       <c r="H58" s="5">
         <f>F58*G58</f>
@@ -2879,7 +2879,7 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
@@ -2906,7 +2906,7 @@
         <v>557.76</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>381.49</v>
+        <v>248.75</v>
       </c>
       <c r="H59" s="5">
         <f>F59*G59</f>
@@ -2916,7 +2916,7 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,34 +2926,34 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>557.76</v>
+        <v>674</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>324.27</v>
+        <v>147.67</v>
       </c>
       <c r="H60" s="5">
         <f>F60*G60</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
+    <row r="61" ht="14" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,34 +2963,34 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F61" s="20" t="n">
-        <v>557.76</v>
+        <v>319.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>248.75</v>
+        <v>227.85</v>
       </c>
       <c r="H61" s="5">
         <f>F61*G61</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
+    <row r="62" ht="14" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -3000,34 +3000,34 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
+          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>674</v>
+        <v>51.2</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>147.67</v>
+        <v>174.22</v>
       </c>
       <c r="H62" s="5">
         <f>F62*G62</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="14" customHeight="1">
+    <row r="63" ht="20" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,34 +3037,34 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>319.2</v>
+        <v>4.4</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>227.85</v>
+        <v>870.14</v>
       </c>
       <c r="H63" s="5">
         <f>F63*G63</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="14" customHeight="1">
+    <row r="64" ht="20" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>51.2</v>
+        <v>9</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>174.22</v>
+        <v>870.14</v>
       </c>
       <c r="H64" s="5">
         <f>F64*G64</f>
@@ -3101,7 +3101,7 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>4.4</v>
+        <v>45</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>870.14</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H65" s="5">
         <f>F65*G65</f>
@@ -3138,7 +3138,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>870.14</v>
+        <v>381.49</v>
       </c>
       <c r="H66" s="5">
         <f>F66*G66</f>
@@ -3175,7 +3175,7 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
+          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>701.48</v>
       </c>
       <c r="H67" s="5">
         <f>F67*G67</f>
@@ -3212,7 +3212,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>381.49</v>
+        <v>248.75</v>
       </c>
       <c r="H68" s="5">
         <f>F68*G68</f>
@@ -3249,7 +3249,7 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
+          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>60</v>
+        <v>5.67</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>701.48</v>
+        <v>2687.73</v>
       </c>
       <c r="H69" s="5">
         <f>F69*G69</f>
@@ -3286,7 +3286,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
+          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>55</v>
+        <v>54.315</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>248.75</v>
+        <v>183.57</v>
       </c>
       <c r="H70" s="5">
         <f>F70*G70</f>
@@ -3323,7 +3323,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -3333,24 +3333,24 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
+          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>5.67</v>
+        <v>25</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>2687.73</v>
+        <v>330.7</v>
       </c>
       <c r="H71" s="5">
         <f>F71*G71</f>
@@ -3360,7 +3360,7 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>54.315</v>
+        <v>1</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>183.57</v>
+        <v>7084.16</v>
       </c>
       <c r="H72" s="5">
         <f>F72*G72</f>
@@ -3397,7 +3397,7 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -3407,31 +3407,31 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>330.7</v>
+        <v>3528.05</v>
       </c>
       <c r="H73" s="5">
         <f>F73*G73</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
+    <row r="74" ht="14" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3444,12 +3444,12 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>7084.16</v>
+        <v>1079.2</v>
       </c>
       <c r="H74" s="5">
         <f>F74*G74</f>
@@ -3481,31 +3481,31 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>3528.05</v>
+        <v>200</v>
       </c>
       <c r="H75" s="5">
         <f>F75*G75</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="14" customHeight="1">
+    <row r="76" ht="20" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1079.2</v>
+        <v>1996.08</v>
       </c>
       <c r="H76" s="5">
         <f>F76*G76</f>
@@ -3555,31 +3555,31 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F77" s="20" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>200</v>
+        <v>1370.96</v>
       </c>
       <c r="H77" s="5">
         <f>F77*G77</f>
         <v/>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
+    <row r="78" ht="14" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3592,31 +3592,31 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F78" s="20" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1996.08</v>
+        <v>29.06</v>
       </c>
       <c r="H78" s="5">
         <f>F78*G78</f>
         <v/>
       </c>
     </row>
-    <row r="79" ht="20" customHeight="1">
+    <row r="79" ht="14" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3629,24 +3629,24 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F79" s="20" t="n">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1370.96</v>
+        <v>19.5</v>
       </c>
       <c r="H79" s="5">
         <f>F79*G79</f>
@@ -3666,12 +3666,12 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
@@ -3680,17 +3680,17 @@
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>29.06</v>
+        <v>12.22</v>
       </c>
       <c r="H80" s="5">
         <f>F80*G80</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="14" customHeight="1">
+    <row r="81" ht="20" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3717,17 +3717,17 @@
         </is>
       </c>
       <c r="F81" s="20" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>19.5</v>
+        <v>157.05</v>
       </c>
       <c r="H81" s="5">
         <f>F81*G81</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="14" customHeight="1">
+    <row r="82" ht="20" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3740,12 +3740,12 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
@@ -3754,17 +3754,17 @@
         </is>
       </c>
       <c r="F82" s="20" t="n">
-        <v>600</v>
+        <v>186</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>12.22</v>
+        <v>115.96</v>
       </c>
       <c r="H82" s="5">
         <f>F82*G82</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="20" customHeight="1">
+    <row r="83" ht="14" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F83" s="20" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>157.05</v>
+        <v>15595.61</v>
       </c>
       <c r="H83" s="5">
         <f>F83*G83</f>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
@@ -3828,178 +3828,30 @@
         </is>
       </c>
       <c r="F84" s="20" t="n">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>115.96</v>
+        <v>426.72</v>
       </c>
       <c r="H84" s="5">
         <f>F84*G84</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="14" customHeight="1">
-      <c r="A85" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C85" s="18" t="inlineStr">
-        <is>
-          <t>30.750.1502</t>
-        </is>
-      </c>
-      <c r="D85" s="16" t="inlineStr">
-        <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
-        </is>
-      </c>
-      <c r="E85" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F85" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>15595.61</v>
-      </c>
-      <c r="H85" s="5">
-        <f>F85*G85</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C86" s="18" t="inlineStr">
-        <is>
-          <t>30.750.2001</t>
-        </is>
-      </c>
-      <c r="D86" s="16" t="inlineStr">
-        <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
-        </is>
-      </c>
-      <c r="E86" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F86" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>426.72</v>
-      </c>
-      <c r="H86" s="5">
-        <f>F86*G86</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="inlineStr">
-        <is>
-          <t>30.740.1106</t>
-        </is>
-      </c>
-      <c r="D87" s="16" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
-        </is>
-      </c>
-      <c r="E87" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F87" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>467349.29</v>
-      </c>
-      <c r="H87" s="5">
-        <f>F87*G87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="14" customHeight="1">
-      <c r="A88" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C88" s="18" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="D88" s="16" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
-        </is>
-      </c>
-      <c r="E88" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F88" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>79653.55</v>
-      </c>
-      <c r="H88" s="5">
-        <f>F88*G88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="21" t="n"/>
-      <c r="B89" s="21" t="n"/>
-      <c r="C89" s="21" t="n"/>
-      <c r="D89" s="22" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="21" t="n"/>
+      <c r="B85" s="21" t="n"/>
+      <c r="C85" s="21" t="n"/>
+      <c r="D85" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E89" s="21" t="n"/>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="n"/>
-      <c r="H89" s="9">
-        <f>SUM(H5:H88)</f>
+      <c r="E85" s="21" t="n"/>
+      <c r="F85" s="21" t="n"/>
+      <c r="G85" s="21" t="n"/>
+      <c r="H85" s="9">
+        <f>SUM(H5:H84)</f>
         <v/>
       </c>
     </row>
@@ -4757,7 +4609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6640,7 +6492,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
+    <row r="54" ht="30" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6653,12 +6505,12 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>30.120.2016</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
@@ -6670,14 +6522,14 @@
         <v>1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>38544.21</v>
+        <v>467349.29</v>
       </c>
       <c r="H54" s="5">
         <f>F54*G54</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
+    <row r="55" ht="30" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6690,12 +6542,12 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>30.120.2016</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
@@ -6707,27 +6559,175 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>38544.21</v>
+        <v>467349.29</v>
       </c>
       <c r="H55" s="5">
         <f>F55*G55</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="21" t="n"/>
-      <c r="B56" s="21" t="n"/>
-      <c r="C56" s="21" t="n"/>
-      <c r="D56" s="22" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>30.740.5406</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>79653.55</v>
+      </c>
+      <c r="H56" s="5">
+        <f>F56*G56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>30.740.5406</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>79653.55</v>
+      </c>
+      <c r="H57" s="5">
+        <f>F57*G57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>30.120.2016</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>38544.21</v>
+      </c>
+      <c r="H58" s="5">
+        <f>F58*G58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>30.120.2016</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F59" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>38544.21</v>
+      </c>
+      <c r="H59" s="5">
+        <f>F59*G59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="n"/>
+      <c r="B60" s="21" t="n"/>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="22" t="inlineStr">
         <is>
           <t>HİBE DIŞI YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E56" s="21" t="n"/>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="n"/>
-      <c r="H56" s="9">
-        <f>SUM(H5:H55)</f>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="9">
+        <f>SUM(H5:H59)</f>
         <v/>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15345295.16</v>
+        <v>14251289.48</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5618052.7</v>
+        <v>6712058.38</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9200012.699999999</v>
+        <v>10294018.38</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -4057,7 +4057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Miktarlar kümes mekanik projesinden; birim fiyatlar Mert Veterinerlik 21.08.2026 tarih ve 1300 numaralı teklifinden. Hibe kapsamı dışında olduğundan teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir; iki kümes bloğu için.</t>
+          <t>Miktarlar kümes mekanik projesinden; birim fiyatlar piyasa araştırmasına dayanan tahmindir — proforma 37 numaralı istek listesiyle alındığında yerine yazılır. Hibe kapsamı dışında olduğundan teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir; iki kümes bloğu için.</t>
         </is>
       </c>
     </row>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="F6" s="20" t="n">
-        <v>31.4285</v>
+        <v>31.428</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>2750.45</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="F10" s="20" t="n">
-        <v>4.1599</v>
+        <v>4.16</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>39045.24</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="F11" s="20" t="n">
-        <v>7.2875</v>
+        <v>7.287</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>37532.19</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="F12" s="20" t="n">
-        <v>3.6375</v>
+        <v>3.637</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>36949.5</v>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>44.0481</v>
+        <v>44.048</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>72192.55</v>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>31.4285</v>
+        <v>31.428</v>
       </c>
       <c r="G46" s="5" t="n">
         <v>2750.45</v>
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>4.1599</v>
+        <v>4.16</v>
       </c>
       <c r="G50" s="5" t="n">
         <v>39045.24</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>7.2875</v>
+        <v>7.287</v>
       </c>
       <c r="G51" s="5" t="n">
         <v>37532.19</v>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>3.6375</v>
+        <v>3.637</v>
       </c>
       <c r="G52" s="5" t="n">
         <v>36949.5</v>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>44.0481</v>
+        <v>44.048</v>
       </c>
       <c r="G53" s="5" t="n">
         <v>72192.55</v>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24545307.86</v>
+        <v>24545224</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>14251289.48</v>
+        <v>14251205.62</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4909061.57</v>
+        <v>4909044.8</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H85</f>
+        <f>'A3.1.1 Yapım İşleri'!H89</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>'A3.4-EK Yapım'!H60</f>
+        <f>'A3.4-EK Yapım'!H56</f>
         <v/>
       </c>
       <c r="C12" s="6">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2358,37 +2358,37 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="14" customHeight="1">
+    <row r="45" ht="20" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>1684.38</v>
+        <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>52.37</v>
+        <v>467349.29</v>
       </c>
       <c r="H45" s="5">
         <f>F45*G45</f>
@@ -2398,44 +2398,44 @@
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>31.428</v>
+        <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>2750.45</v>
+        <v>79653.55</v>
       </c>
       <c r="H46" s="5">
         <f>F46*G46</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
+    <row r="47" ht="14" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
+          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
@@ -2459,20 +2459,20 @@
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>115.71</v>
+        <v>1684.38</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>2960.45</v>
+        <v>52.37</v>
       </c>
       <c r="H47" s="5">
         <f>F47*G47</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
+    <row r="48" ht="14" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
+          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
@@ -2496,20 +2496,20 @@
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>162.63</v>
+        <v>31.428</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2960.45</v>
+        <v>2750.45</v>
       </c>
       <c r="H48" s="5">
         <f>F48*G48</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="14" customHeight="1">
+    <row r="49" ht="20" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
@@ -2519,34 +2519,34 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>551.26</v>
+        <v>115.71</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>863.8</v>
+        <v>2960.45</v>
       </c>
       <c r="H49" s="5">
         <f>F49*G49</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="14" customHeight="1">
+    <row r="50" ht="20" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
@@ -2556,24 +2556,24 @@
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>4.16</v>
+        <v>162.63</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>39045.24</v>
+        <v>2960.45</v>
       </c>
       <c r="H50" s="5">
         <f>F50*G50</f>
@@ -2583,7 +2583,7 @@
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>7.287</v>
+        <v>551.26</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>37532.19</v>
+        <v>863.8</v>
       </c>
       <c r="H51" s="5">
         <f>F51*G51</f>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
+          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
@@ -2644,20 +2644,20 @@
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>3.637</v>
+        <v>4.16</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>36949.5</v>
+        <v>39045.24</v>
       </c>
       <c r="H52" s="5">
         <f>F52*G52</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
+    <row r="53" ht="14" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
+          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -2681,20 +2681,20 @@
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>44.048</v>
+        <v>7.287</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>72192.55</v>
+        <v>37532.19</v>
       </c>
       <c r="H53" s="5">
         <f>F53*G53</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
+    <row r="54" ht="14" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
@@ -2704,24 +2704,24 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
+          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F54" s="20" t="n">
-        <v>507.91</v>
+        <v>3.637</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>929.28</v>
+        <v>36949.5</v>
       </c>
       <c r="H54" s="5">
         <f>F54*G54</f>
@@ -2731,7 +2731,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2741,24 +2741,24 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
+          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>49.85</v>
+        <v>44.048</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1777.52</v>
+        <v>72192.55</v>
       </c>
       <c r="H55" s="5">
         <f>F55*G55</f>
@@ -2768,7 +2768,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>557.76</v>
+        <v>507.91</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>372.55</v>
+        <v>929.28</v>
       </c>
       <c r="H56" s="5">
         <f>F56*G56</f>
@@ -2805,7 +2805,7 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>557.76</v>
+        <v>49.85</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>381.49</v>
+        <v>1777.52</v>
       </c>
       <c r="H57" s="5">
         <f>F57*G57</f>
@@ -2842,7 +2842,7 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
@@ -2869,7 +2869,7 @@
         <v>557.76</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>324.27</v>
+        <v>372.55</v>
       </c>
       <c r="H58" s="5">
         <f>F58*G58</f>
@@ -2879,7 +2879,7 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
@@ -2906,7 +2906,7 @@
         <v>557.76</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>248.75</v>
+        <v>381.49</v>
       </c>
       <c r="H59" s="5">
         <f>F59*G59</f>
@@ -2916,7 +2916,7 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,34 +2926,34 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>674</v>
+        <v>557.76</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>147.67</v>
+        <v>324.27</v>
       </c>
       <c r="H60" s="5">
         <f>F60*G60</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="14" customHeight="1">
+    <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,34 +2963,34 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F61" s="20" t="n">
-        <v>319.2</v>
+        <v>557.76</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>227.85</v>
+        <v>248.75</v>
       </c>
       <c r="H61" s="5">
         <f>F61*G61</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="14" customHeight="1">
+    <row r="62" ht="20" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -3000,34 +3000,34 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
+          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>51.2</v>
+        <v>674</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>174.22</v>
+        <v>147.67</v>
       </c>
       <c r="H62" s="5">
         <f>F62*G62</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
+    <row r="63" ht="14" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,34 +3037,34 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
+          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>4.4</v>
+        <v>319.2</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>870.14</v>
+        <v>227.85</v>
       </c>
       <c r="H63" s="5">
         <f>F63*G63</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
+    <row r="64" ht="14" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
+          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>9</v>
+        <v>51.2</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>870.14</v>
+        <v>174.22</v>
       </c>
       <c r="H64" s="5">
         <f>F64*G64</f>
@@ -3101,7 +3101,7 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>45</v>
+        <v>4.4</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>870.14</v>
       </c>
       <c r="H65" s="5">
         <f>F65*G65</f>
@@ -3138,7 +3138,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>381.49</v>
+        <v>870.14</v>
       </c>
       <c r="H66" s="5">
         <f>F66*G66</f>
@@ -3175,7 +3175,7 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>701.48</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H67" s="5">
         <f>F67*G67</f>
@@ -3212,7 +3212,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>248.75</v>
+        <v>381.49</v>
       </c>
       <c r="H68" s="5">
         <f>F68*G68</f>
@@ -3249,7 +3249,7 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
+          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>5.67</v>
+        <v>60</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>2687.73</v>
+        <v>701.48</v>
       </c>
       <c r="H69" s="5">
         <f>F69*G69</f>
@@ -3286,7 +3286,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>54.315</v>
+        <v>55</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>183.57</v>
+        <v>248.75</v>
       </c>
       <c r="H70" s="5">
         <f>F70*G70</f>
@@ -3323,7 +3323,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -3333,24 +3333,24 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>25</v>
+        <v>5.67</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>330.7</v>
+        <v>2687.73</v>
       </c>
       <c r="H71" s="5">
         <f>F71*G71</f>
@@ -3360,7 +3360,7 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>1</v>
+        <v>54.315</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>7084.16</v>
+        <v>183.57</v>
       </c>
       <c r="H72" s="5">
         <f>F72*G72</f>
@@ -3397,7 +3397,7 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -3407,31 +3407,31 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>3528.05</v>
+        <v>330.7</v>
       </c>
       <c r="H73" s="5">
         <f>F73*G73</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="14" customHeight="1">
+    <row r="74" ht="20" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3444,12 +3444,12 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
@@ -3458,10 +3458,10 @@
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1079.2</v>
+        <v>7084.16</v>
       </c>
       <c r="H74" s="5">
         <f>F74*G74</f>
@@ -3481,31 +3481,31 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>200</v>
+        <v>3528.05</v>
       </c>
       <c r="H75" s="5">
         <f>F75*G75</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
+    <row r="76" ht="14" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1996.08</v>
+        <v>1079.2</v>
       </c>
       <c r="H76" s="5">
         <f>F76*G76</f>
@@ -3555,31 +3555,31 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F77" s="20" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>1370.96</v>
+        <v>200</v>
       </c>
       <c r="H77" s="5">
         <f>F77*G77</f>
         <v/>
       </c>
     </row>
-    <row r="78" ht="14" customHeight="1">
+    <row r="78" ht="20" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3592,31 +3592,31 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F78" s="20" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>29.06</v>
+        <v>1996.08</v>
       </c>
       <c r="H78" s="5">
         <f>F78*G78</f>
         <v/>
       </c>
     </row>
-    <row r="79" ht="14" customHeight="1">
+    <row r="79" ht="20" customHeight="1">
       <c r="A79" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3629,24 +3629,24 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F79" s="20" t="n">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>19.5</v>
+        <v>1370.96</v>
       </c>
       <c r="H79" s="5">
         <f>F79*G79</f>
@@ -3666,12 +3666,12 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
@@ -3680,17 +3680,17 @@
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>12.22</v>
+        <v>29.06</v>
       </c>
       <c r="H80" s="5">
         <f>F80*G80</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="20" customHeight="1">
+    <row r="81" ht="14" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3717,17 +3717,17 @@
         </is>
       </c>
       <c r="F81" s="20" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>157.05</v>
+        <v>19.5</v>
       </c>
       <c r="H81" s="5">
         <f>F81*G81</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
+    <row r="82" ht="14" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3740,12 +3740,12 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
@@ -3754,17 +3754,17 @@
         </is>
       </c>
       <c r="F82" s="20" t="n">
-        <v>186</v>
+        <v>600</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>115.96</v>
+        <v>12.22</v>
       </c>
       <c r="H82" s="5">
         <f>F82*G82</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="14" customHeight="1">
+    <row r="83" ht="20" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F83" s="20" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>15595.61</v>
+        <v>157.05</v>
       </c>
       <c r="H83" s="5">
         <f>F83*G83</f>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
@@ -3828,30 +3828,178 @@
         </is>
       </c>
       <c r="F84" s="20" t="n">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>426.72</v>
+        <v>115.96</v>
       </c>
       <c r="H84" s="5">
         <f>F84*G84</f>
         <v/>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="21" t="n"/>
-      <c r="B85" s="21" t="n"/>
-      <c r="C85" s="21" t="n"/>
-      <c r="D85" s="22" t="inlineStr">
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>30.750.1502</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="inlineStr">
+        <is>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+        </is>
+      </c>
+      <c r="E85" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F85" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>15595.61</v>
+      </c>
+      <c r="H85" s="5">
+        <f>F85*G85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>30.750.2001</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+        </is>
+      </c>
+      <c r="E86" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F86" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>426.72</v>
+      </c>
+      <c r="H86" s="5">
+        <f>F86*G86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>30.740.1106</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+        </is>
+      </c>
+      <c r="E87" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F87" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>467349.29</v>
+      </c>
+      <c r="H87" s="5">
+        <f>F87*G87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>30.740.5406</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+        </is>
+      </c>
+      <c r="E88" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F88" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>79653.55</v>
+      </c>
+      <c r="H88" s="5">
+        <f>F88*G88</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="n"/>
+      <c r="B89" s="21" t="n"/>
+      <c r="C89" s="21" t="n"/>
+      <c r="D89" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E85" s="21" t="n"/>
-      <c r="F85" s="21" t="n"/>
-      <c r="G85" s="21" t="n"/>
-      <c r="H85" s="9">
-        <f>SUM(H5:H84)</f>
+      <c r="E89" s="21" t="n"/>
+      <c r="F89" s="21" t="n"/>
+      <c r="G89" s="21" t="n"/>
+      <c r="H89" s="9">
+        <f>SUM(H5:H88)</f>
         <v/>
       </c>
     </row>
@@ -4609,7 +4757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6492,7 +6640,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
+    <row r="54" ht="20" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6505,12 +6653,12 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.120.2016</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
@@ -6522,14 +6670,14 @@
         <v>1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>467349.29</v>
+        <v>38544.21</v>
       </c>
       <c r="H54" s="5">
         <f>F54*G54</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
+    <row r="55" ht="20" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -6542,12 +6690,12 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.120.2016</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
@@ -6559,175 +6707,27 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>467349.29</v>
+        <v>38544.21</v>
       </c>
       <c r="H55" s="5">
         <f>F55*G55</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E56" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F56" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>79653.55</v>
-      </c>
-      <c r="H56" s="5">
-        <f>F56*G56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E57" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F57" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>79653.55</v>
-      </c>
-      <c r="H57" s="5">
-        <f>F57*G57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="inlineStr">
-        <is>
-          <t>30.120.2016</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E58" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F58" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>38544.21</v>
-      </c>
-      <c r="H58" s="5">
-        <f>F58*G58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="inlineStr">
-        <is>
-          <t>30.120.2016</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="inlineStr">
-        <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E59" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F59" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>38544.21</v>
-      </c>
-      <c r="H59" s="5">
-        <f>F59*G59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="21" t="n"/>
-      <c r="B60" s="21" t="n"/>
-      <c r="C60" s="21" t="n"/>
-      <c r="D60" s="22" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="21" t="n"/>
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="22" t="inlineStr">
         <is>
           <t>HİBE DIŞI YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E60" s="21" t="n"/>
-      <c r="F60" s="21" t="n"/>
-      <c r="G60" s="21" t="n"/>
-      <c r="H60" s="9">
-        <f>SUM(H5:H59)</f>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="9">
+        <f>SUM(H5:H55)</f>
         <v/>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>14251205.62</v>
+        <v>15345211.3</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6712058.38</v>
+        <v>5618052.7</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>10294018.38</v>
+        <v>9200012.699999999</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="F6" s="20" t="n">
-        <v>31.428</v>
+        <v>31.429</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>2750.45</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="F11" s="20" t="n">
-        <v>7.287</v>
+        <v>7.288</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>37532.19</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>31.428</v>
+        <v>31.429</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>2750.45</v>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>7.287</v>
+        <v>7.288</v>
       </c>
       <c r="G53" s="5" t="n">
         <v>37532.19</v>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="F5" s="20" t="n">
-        <v>260.942</v>
+        <v>260.943</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>52.37</v>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24545224</v>
+        <v>24545304.61</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15345211.3</v>
+        <v>15345291.86</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5618052.7</v>
+        <v>5618052.75</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9200012.699999999</v>
+        <v>9200012.75</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4909044.8</v>
+        <v>4909060.92</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H89</f>
+        <f>'A3.1.1 Yapım İşleri'!H93</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2432,37 +2432,37 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1">
+    <row r="47" ht="20" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
+          <t>Kablo tava sistemi — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme)</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>1684.38</v>
+        <v>502</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>52.37</v>
+        <v>199.42</v>
       </c>
       <c r="H47" s="5">
         <f>F47*G47</f>
@@ -2472,44 +2472,44 @@
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
+          <t>Kablo tava sisteminin montajı — askı ve konsollarla tespiti</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>31.429</v>
+        <v>502</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2750.45</v>
+        <v>38.72</v>
       </c>
       <c r="H48" s="5">
         <f>F48*G48</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
+    <row r="49" ht="14" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
+          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
@@ -2533,20 +2533,20 @@
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>115.71</v>
+        <v>1684.38</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2960.45</v>
+        <v>52.37</v>
       </c>
       <c r="H49" s="5">
         <f>F49*G49</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
+    <row r="50" ht="14" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
+          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
@@ -2570,20 +2570,20 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>162.63</v>
+        <v>31.429</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2960.45</v>
+        <v>2750.45</v>
       </c>
       <c r="H50" s="5">
         <f>F50*G50</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="14" customHeight="1">
+    <row r="51" ht="20" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
@@ -2593,34 +2593,34 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>551.26</v>
+        <v>115.71</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>863.8</v>
+        <v>2960.45</v>
       </c>
       <c r="H51" s="5">
         <f>F51*G51</f>
         <v/>
       </c>
     </row>
-    <row r="52" ht="14" customHeight="1">
+    <row r="52" ht="20" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
@@ -2630,24 +2630,24 @@
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>4.16</v>
+        <v>162.63</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>39045.24</v>
+        <v>2960.45</v>
       </c>
       <c r="H52" s="5">
         <f>F52*G52</f>
@@ -2657,7 +2657,7 @@
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2667,24 +2667,24 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>7.288</v>
+        <v>551.26</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>37532.19</v>
+        <v>863.8</v>
       </c>
       <c r="H53" s="5">
         <f>F53*G53</f>
@@ -2704,12 +2704,12 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
+          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
@@ -2718,20 +2718,20 @@
         </is>
       </c>
       <c r="F54" s="20" t="n">
-        <v>3.637</v>
+        <v>4.16</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>36949.5</v>
+        <v>39045.24</v>
       </c>
       <c r="H54" s="5">
         <f>F54*G54</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
+    <row r="55" ht="14" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
+          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
@@ -2755,20 +2755,20 @@
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>44.048</v>
+        <v>7.288</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>72192.55</v>
+        <v>37532.19</v>
       </c>
       <c r="H55" s="5">
         <f>F55*G55</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
+    <row r="56" ht="14" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
+          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>507.91</v>
+        <v>3.637</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>929.28</v>
+        <v>36949.5</v>
       </c>
       <c r="H56" s="5">
         <f>F56*G56</f>
@@ -2805,7 +2805,7 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -2815,24 +2815,24 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
+          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>49.85</v>
+        <v>44.048</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1777.52</v>
+        <v>72192.55</v>
       </c>
       <c r="H57" s="5">
         <f>F57*G57</f>
@@ -2842,7 +2842,7 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>557.76</v>
+        <v>507.91</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>372.55</v>
+        <v>929.28</v>
       </c>
       <c r="H58" s="5">
         <f>F58*G58</f>
@@ -2879,7 +2879,7 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="F59" s="20" t="n">
-        <v>557.76</v>
+        <v>49.85</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>381.49</v>
+        <v>1777.52</v>
       </c>
       <c r="H59" s="5">
         <f>F59*G59</f>
@@ -2916,7 +2916,7 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
@@ -2943,7 +2943,7 @@
         <v>557.76</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>324.27</v>
+        <v>372.55</v>
       </c>
       <c r="H60" s="5">
         <f>F60*G60</f>
@@ -2953,7 +2953,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -2980,7 +2980,7 @@
         <v>557.76</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>248.75</v>
+        <v>381.49</v>
       </c>
       <c r="H61" s="5">
         <f>F61*G61</f>
@@ -2990,7 +2990,7 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -3000,34 +3000,34 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>674</v>
+        <v>557.76</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>147.67</v>
+        <v>324.27</v>
       </c>
       <c r="H62" s="5">
         <f>F62*G62</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="14" customHeight="1">
+    <row r="63" ht="20" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,34 +3037,34 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>319.2</v>
+        <v>557.76</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>227.85</v>
+        <v>248.75</v>
       </c>
       <c r="H63" s="5">
         <f>F63*G63</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="14" customHeight="1">
+    <row r="64" ht="20" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -3074,34 +3074,34 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
+          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>51.2</v>
+        <v>674</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>174.22</v>
+        <v>147.67</v>
       </c>
       <c r="H64" s="5">
         <f>F64*G64</f>
         <v/>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
+    <row r="65" ht="14" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
+          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>4.4</v>
+        <v>319.2</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>870.14</v>
+        <v>227.85</v>
       </c>
       <c r="H65" s="5">
         <f>F65*G65</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
+    <row r="66" ht="14" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3148,24 +3148,24 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
+          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>9</v>
+        <v>51.2</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>870.14</v>
+        <v>174.22</v>
       </c>
       <c r="H66" s="5">
         <f>F66*G66</f>
@@ -3175,7 +3175,7 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>45</v>
+        <v>4.4</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>870.14</v>
       </c>
       <c r="H67" s="5">
         <f>F67*G67</f>
@@ -3212,7 +3212,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
@@ -3236,10 +3236,10 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>381.49</v>
+        <v>870.14</v>
       </c>
       <c r="H68" s="5">
         <f>F68*G68</f>
@@ -3249,7 +3249,7 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>701.48</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H69" s="5">
         <f>F69*G69</f>
@@ -3286,7 +3286,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>248.75</v>
+        <v>381.49</v>
       </c>
       <c r="H70" s="5">
         <f>F70*G70</f>
@@ -3323,7 +3323,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
+          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>5.67</v>
+        <v>60</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>2687.73</v>
+        <v>701.48</v>
       </c>
       <c r="H71" s="5">
         <f>F71*G71</f>
@@ -3360,7 +3360,7 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>54.315</v>
+        <v>55</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>183.57</v>
+        <v>248.75</v>
       </c>
       <c r="H72" s="5">
         <f>F72*G72</f>
@@ -3397,7 +3397,7 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -3407,24 +3407,24 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>25</v>
+        <v>5.67</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>330.7</v>
+        <v>2687.73</v>
       </c>
       <c r="H73" s="5">
         <f>F73*G73</f>
@@ -3434,7 +3434,7 @@
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
@@ -3444,24 +3444,24 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>1</v>
+        <v>54.315</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>7084.16</v>
+        <v>183.57</v>
       </c>
       <c r="H74" s="5">
         <f>F74*G74</f>
@@ -3471,7 +3471,7 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -3481,31 +3481,31 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>3528.05</v>
+        <v>330.7</v>
       </c>
       <c r="H75" s="5">
         <f>F75*G75</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="14" customHeight="1">
+    <row r="76" ht="20" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1079.2</v>
+        <v>7084.16</v>
       </c>
       <c r="H76" s="5">
         <f>F76*G76</f>
@@ -3555,31 +3555,31 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F77" s="20" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>200</v>
+        <v>3528.05</v>
       </c>
       <c r="H77" s="5">
         <f>F77*G77</f>
         <v/>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
+    <row r="78" ht="14" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="F78" s="20" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1996.08</v>
+        <v>1079.2</v>
       </c>
       <c r="H78" s="5">
         <f>F78*G78</f>
@@ -3629,31 +3629,31 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F79" s="20" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1370.96</v>
+        <v>200</v>
       </c>
       <c r="H79" s="5">
         <f>F79*G79</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="14" customHeight="1">
+    <row r="80" ht="20" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3666,31 +3666,31 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>29.06</v>
+        <v>1996.08</v>
       </c>
       <c r="H80" s="5">
         <f>F80*G80</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="14" customHeight="1">
+    <row r="81" ht="20" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3703,24 +3703,24 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F81" s="20" t="n">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>19.5</v>
+        <v>1370.96</v>
       </c>
       <c r="H81" s="5">
         <f>F81*G81</f>
@@ -3740,12 +3740,12 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
@@ -3754,17 +3754,17 @@
         </is>
       </c>
       <c r="F82" s="20" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>12.22</v>
+        <v>29.06</v>
       </c>
       <c r="H82" s="5">
         <f>F82*G82</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="20" customHeight="1">
+    <row r="83" ht="14" customHeight="1">
       <c r="A83" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3777,12 +3777,12 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -3791,17 +3791,17 @@
         </is>
       </c>
       <c r="F83" s="20" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>157.05</v>
+        <v>19.5</v>
       </c>
       <c r="H83" s="5">
         <f>F83*G83</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="20" customHeight="1">
+    <row r="84" ht="14" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
@@ -3828,17 +3828,17 @@
         </is>
       </c>
       <c r="F84" s="20" t="n">
-        <v>186</v>
+        <v>600</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>115.96</v>
+        <v>12.22</v>
       </c>
       <c r="H84" s="5">
         <f>F84*G84</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="14" customHeight="1">
+    <row r="85" ht="20" customHeight="1">
       <c r="A85" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3851,24 +3851,24 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F85" s="20" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>15595.61</v>
+        <v>157.05</v>
       </c>
       <c r="H85" s="5">
         <f>F85*G85</f>
@@ -3888,12 +3888,12 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
@@ -3902,17 +3902,17 @@
         </is>
       </c>
       <c r="F86" s="20" t="n">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>426.72</v>
+        <v>115.96</v>
       </c>
       <c r="H86" s="5">
         <f>F86*G86</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
+    <row r="87" ht="14" customHeight="1">
       <c r="A87" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="C87" s="18" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
@@ -3942,14 +3942,14 @@
         <v>1</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>467349.29</v>
+        <v>15595.61</v>
       </c>
       <c r="H87" s="5">
         <f>F87*G87</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="14" customHeight="1">
+    <row r="88" ht="20" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3962,44 +3962,192 @@
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F88" s="20" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>79653.55</v>
+        <v>426.72</v>
       </c>
       <c r="H88" s="5">
         <f>F88*G88</f>
         <v/>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="21" t="n"/>
-      <c r="B89" s="21" t="n"/>
-      <c r="C89" s="21" t="n"/>
-      <c r="D89" s="22" t="inlineStr">
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>30.740.1106</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+        </is>
+      </c>
+      <c r="E89" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>467349.29</v>
+      </c>
+      <c r="H89" s="5">
+        <f>F89*G89</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>30.740.5406</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+        </is>
+      </c>
+      <c r="E90" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F90" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>79653.55</v>
+      </c>
+      <c r="H90" s="5">
+        <f>F90*G90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemi — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme)</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F91" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>199.42</v>
+      </c>
+      <c r="H91" s="5">
+        <f>F91*G91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sisteminin montajı — askı ve konsollarla tespiti</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F92" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="H92" s="5">
+        <f>F92*G92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="21" t="n"/>
+      <c r="B93" s="21" t="n"/>
+      <c r="C93" s="21" t="n"/>
+      <c r="D93" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E89" s="21" t="n"/>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="n"/>
-      <c r="H89" s="9">
-        <f>SUM(H5:H88)</f>
+      <c r="E93" s="21" t="n"/>
+      <c r="F93" s="21" t="n"/>
+      <c r="G93" s="21" t="n"/>
+      <c r="H93" s="9">
+        <f>SUM(H5:H92)</f>
         <v/>
       </c>
     </row>
@@ -7100,7 +7248,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24545304.61</v>
+        <v>24784397.17</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7119,7 +7267,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15345291.86</v>
+        <v>15584384.42</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7233,7 +7381,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4909060.92</v>
+        <v>4956879.43</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H93</f>
+        <f>'A3.1.1 Yapım İşleri'!H97</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -911,7 +911,7 @@
         <v>52.37</v>
       </c>
       <c r="H5" s="5">
-        <f>F5*G5</f>
+        <f>ROUND(F5*G5,2)</f>
         <v/>
       </c>
     </row>
@@ -948,7 +948,7 @@
         <v>2750.45</v>
       </c>
       <c r="H6" s="5">
-        <f>F6*G6</f>
+        <f>ROUND(F6*G6,2)</f>
         <v/>
       </c>
     </row>
@@ -985,7 +985,7 @@
         <v>2960.45</v>
       </c>
       <c r="H7" s="5">
-        <f>F7*G7</f>
+        <f>ROUND(F7*G7,2)</f>
         <v/>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
         <v>2960.45</v>
       </c>
       <c r="H8" s="5">
-        <f>F8*G8</f>
+        <f>ROUND(F8*G8,2)</f>
         <v/>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
         <v>863.8</v>
       </c>
       <c r="H9" s="5">
-        <f>F9*G9</f>
+        <f>ROUND(F9*G9,2)</f>
         <v/>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
         <v>39045.24</v>
       </c>
       <c r="H10" s="5">
-        <f>F10*G10</f>
+        <f>ROUND(F10*G10,2)</f>
         <v/>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         <v>37532.19</v>
       </c>
       <c r="H11" s="5">
-        <f>F11*G11</f>
+        <f>ROUND(F11*G11,2)</f>
         <v/>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
         <v>36949.5</v>
       </c>
       <c r="H12" s="5">
-        <f>F12*G12</f>
+        <f>ROUND(F12*G12,2)</f>
         <v/>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
         <v>72192.55</v>
       </c>
       <c r="H13" s="5">
-        <f>F13*G13</f>
+        <f>ROUND(F13*G13,2)</f>
         <v/>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         <v>929.28</v>
       </c>
       <c r="H14" s="5">
-        <f>F14*G14</f>
+        <f>ROUND(F14*G14,2)</f>
         <v/>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
         <v>1777.52</v>
       </c>
       <c r="H15" s="5">
-        <f>F15*G15</f>
+        <f>ROUND(F15*G15,2)</f>
         <v/>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
         <v>372.55</v>
       </c>
       <c r="H16" s="5">
-        <f>F16*G16</f>
+        <f>ROUND(F16*G16,2)</f>
         <v/>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
         <v>381.49</v>
       </c>
       <c r="H17" s="5">
-        <f>F17*G17</f>
+        <f>ROUND(F17*G17,2)</f>
         <v/>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
         <v>324.27</v>
       </c>
       <c r="H18" s="5">
-        <f>F18*G18</f>
+        <f>ROUND(F18*G18,2)</f>
         <v/>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
         <v>248.75</v>
       </c>
       <c r="H19" s="5">
-        <f>F19*G19</f>
+        <f>ROUND(F19*G19,2)</f>
         <v/>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
         <v>147.67</v>
       </c>
       <c r="H20" s="5">
-        <f>F20*G20</f>
+        <f>ROUND(F20*G20,2)</f>
         <v/>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         <v>227.85</v>
       </c>
       <c r="H21" s="5">
-        <f>F21*G21</f>
+        <f>ROUND(F21*G21,2)</f>
         <v/>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
         <v>174.22</v>
       </c>
       <c r="H22" s="5">
-        <f>F22*G22</f>
+        <f>ROUND(F22*G22,2)</f>
         <v/>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
         <v>870.14</v>
       </c>
       <c r="H23" s="5">
-        <f>F23*G23</f>
+        <f>ROUND(F23*G23,2)</f>
         <v/>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
         <v>870.14</v>
       </c>
       <c r="H24" s="5">
-        <f>F24*G24</f>
+        <f>ROUND(F24*G24,2)</f>
         <v/>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
         <v>607.9299999999999</v>
       </c>
       <c r="H25" s="5">
-        <f>F25*G25</f>
+        <f>ROUND(F25*G25,2)</f>
         <v/>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
         <v>381.49</v>
       </c>
       <c r="H26" s="5">
-        <f>F26*G26</f>
+        <f>ROUND(F26*G26,2)</f>
         <v/>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
         <v>701.48</v>
       </c>
       <c r="H27" s="5">
-        <f>F27*G27</f>
+        <f>ROUND(F27*G27,2)</f>
         <v/>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
         <v>248.75</v>
       </c>
       <c r="H28" s="5">
-        <f>F28*G28</f>
+        <f>ROUND(F28*G28,2)</f>
         <v/>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
         <v>2687.73</v>
       </c>
       <c r="H29" s="5">
-        <f>F29*G29</f>
+        <f>ROUND(F29*G29,2)</f>
         <v/>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
         <v>183.57</v>
       </c>
       <c r="H30" s="5">
-        <f>F30*G30</f>
+        <f>ROUND(F30*G30,2)</f>
         <v/>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         <v>330.7</v>
       </c>
       <c r="H31" s="5">
-        <f>F31*G31</f>
+        <f>ROUND(F31*G31,2)</f>
         <v/>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
         <v>7084.16</v>
       </c>
       <c r="H32" s="5">
-        <f>F32*G32</f>
+        <f>ROUND(F32*G32,2)</f>
         <v/>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
         <v>3528.05</v>
       </c>
       <c r="H33" s="5">
-        <f>F33*G33</f>
+        <f>ROUND(F33*G33,2)</f>
         <v/>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
         <v>1079.2</v>
       </c>
       <c r="H34" s="5">
-        <f>F34*G34</f>
+        <f>ROUND(F34*G34,2)</f>
         <v/>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
         <v>200</v>
       </c>
       <c r="H35" s="5">
-        <f>F35*G35</f>
+        <f>ROUND(F35*G35,2)</f>
         <v/>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
         <v>1996.08</v>
       </c>
       <c r="H36" s="5">
-        <f>F36*G36</f>
+        <f>ROUND(F36*G36,2)</f>
         <v/>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
         <v>1370.96</v>
       </c>
       <c r="H37" s="5">
-        <f>F37*G37</f>
+        <f>ROUND(F37*G37,2)</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v>29.06</v>
       </c>
       <c r="H38" s="5">
-        <f>F38*G38</f>
+        <f>ROUND(F38*G38,2)</f>
         <v/>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
         <v>19.5</v>
       </c>
       <c r="H39" s="5">
-        <f>F39*G39</f>
+        <f>ROUND(F39*G39,2)</f>
         <v/>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
         <v>12.22</v>
       </c>
       <c r="H40" s="5">
-        <f>F40*G40</f>
+        <f>ROUND(F40*G40,2)</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>157.05</v>
       </c>
       <c r="H41" s="5">
-        <f>F41*G41</f>
+        <f>ROUND(F41*G41,2)</f>
         <v/>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
         <v>115.96</v>
       </c>
       <c r="H42" s="5">
-        <f>F42*G42</f>
+        <f>ROUND(F42*G42,2)</f>
         <v/>
       </c>
     </row>
@@ -2317,7 +2317,7 @@
         <v>15595.61</v>
       </c>
       <c r="H43" s="5">
-        <f>F43*G43</f>
+        <f>ROUND(F43*G43,2)</f>
         <v/>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         <v>426.72</v>
       </c>
       <c r="H44" s="5">
-        <f>F44*G44</f>
+        <f>ROUND(F44*G44,2)</f>
         <v/>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
         <v>467349.29</v>
       </c>
       <c r="H45" s="5">
-        <f>F45*G45</f>
+        <f>ROUND(F45*G45,2)</f>
         <v/>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
         <v>79653.55</v>
       </c>
       <c r="H46" s="5">
-        <f>F46*G46</f>
+        <f>ROUND(F46*G46,2)</f>
         <v/>
       </c>
     </row>
@@ -2465,11 +2465,11 @@
         <v>199.42</v>
       </c>
       <c r="H47" s="5">
-        <f>F47*G47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="14" customHeight="1">
+        <f>ROUND(F47*G47,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sisteminin montajı — askı ve konsollarla tespiti</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
@@ -2502,236 +2502,236 @@
         <v>38.72</v>
       </c>
       <c r="H48" s="5">
-        <f>F48*G48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="14" customHeight="1">
+        <f>ROUND(F48*G48,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemi kapak sacı — 1,0 mm sıcak daldırma galvanizli (malzeme)</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>162.37</v>
+      </c>
+      <c r="H49" s="5">
+        <f>ROUND(F49*G49,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F50" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H50" s="5">
+        <f>ROUND(F50*G50,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
           <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>15.120.1001</t>
         </is>
       </c>
-      <c r="D49" s="16" t="inlineStr">
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>Makine ile kazı yapılması — kümes A ve B blok</t>
         </is>
       </c>
-      <c r="E49" s="19" t="inlineStr">
+      <c r="E51" s="19" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F49" s="20" t="n">
+      <c r="F51" s="20" t="n">
         <v>1684.38</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="G51" s="5" t="n">
         <v>52.37</v>
       </c>
-      <c r="H49" s="5">
-        <f>F49*G49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="H51" s="5">
+        <f>ROUND(F51*G51,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Beton işleri</t>
         </is>
       </c>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C52" s="18" t="inlineStr">
         <is>
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
         </is>
       </c>
-      <c r="E50" s="19" t="inlineStr">
+      <c r="E52" s="19" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F50" s="20" t="n">
+      <c r="F52" s="20" t="n">
         <v>31.429</v>
       </c>
-      <c r="G50" s="5" t="n">
+      <c r="G52" s="5" t="n">
         <v>2750.45</v>
       </c>
-      <c r="H50" s="5">
-        <f>F50*G50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="H52" s="5">
+        <f>ROUND(F52*G52,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B53" s="17" t="inlineStr">
         <is>
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C53" s="18" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="D53" s="16" t="inlineStr">
         <is>
           <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
         </is>
       </c>
-      <c r="E51" s="19" t="inlineStr">
+      <c r="E53" s="19" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F51" s="20" t="n">
+      <c r="F53" s="20" t="n">
         <v>115.71</v>
       </c>
-      <c r="G51" s="5" t="n">
+      <c r="G53" s="5" t="n">
         <v>2960.45</v>
       </c>
-      <c r="H51" s="5">
-        <f>F51*G51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="H53" s="5">
+        <f>ROUND(F53*G53,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
         </is>
       </c>
-      <c r="B52" s="17" t="inlineStr">
+      <c r="B54" s="17" t="inlineStr">
         <is>
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C54" s="18" t="inlineStr">
         <is>
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="D54" s="16" t="inlineStr">
         <is>
           <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
         </is>
       </c>
-      <c r="E52" s="19" t="inlineStr">
+      <c r="E54" s="19" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="F52" s="20" t="n">
+      <c r="F54" s="20" t="n">
         <v>162.63</v>
       </c>
-      <c r="G52" s="5" t="n">
+      <c r="G54" s="5" t="n">
         <v>2960.45</v>
       </c>
-      <c r="H52" s="5">
-        <f>F52*G52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="14" customHeight="1">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
-        </is>
-      </c>
-      <c r="E53" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F53" s="20" t="n">
-        <v>551.26</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>863.8</v>
-      </c>
-      <c r="H53" s="5">
-        <f>F53*G53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>Demir-inşaat işleri</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="inlineStr">
-        <is>
-          <t>15.160.1003</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
-        </is>
-      </c>
-      <c r="E54" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F54" s="20" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>39045.24</v>
-      </c>
       <c r="H54" s="5">
-        <f>F54*G54</f>
+        <f>ROUND(F54*G54,2)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2741,27 +2741,27 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>7.288</v>
+        <v>551.26</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>37532.19</v>
+        <v>863.8</v>
       </c>
       <c r="H55" s="5">
-        <f>F55*G55</f>
+        <f>ROUND(F55*G55,2)</f>
         <v/>
       </c>
     </row>
@@ -2778,108 +2778,108 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
+          <t>15.160.1003</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>39045.24</v>
+      </c>
+      <c r="H56" s="5">
+        <f>ROUND(F56*G56,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>15.160.1004</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>ton</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="n">
+        <v>7.288</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>37532.19</v>
+      </c>
+      <c r="H57" s="5">
+        <f>ROUND(F57*G57,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>Demir-inşaat işleri</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
           <t>15.160.1002</t>
         </is>
       </c>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
         </is>
       </c>
-      <c r="E56" s="19" t="inlineStr">
+      <c r="E58" s="19" t="inlineStr">
         <is>
           <t>ton</t>
         </is>
       </c>
-      <c r="F56" s="20" t="n">
+      <c r="F58" s="20" t="n">
         <v>3.637</v>
       </c>
-      <c r="G56" s="5" t="n">
+      <c r="G58" s="5" t="n">
         <v>36949.5</v>
       </c>
-      <c r="H56" s="5">
-        <f>F56*G56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>Çelik yapım-imalat işleri</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
-        <is>
-          <t>15.165.1003</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr">
-        <is>
-          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
-        </is>
-      </c>
-      <c r="E57" s="19" t="inlineStr">
-        <is>
-          <t>ton</t>
-        </is>
-      </c>
-      <c r="F57" s="20" t="n">
-        <v>44.048</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>72192.55</v>
-      </c>
-      <c r="H57" s="5">
-        <f>F57*G57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>Tuğla ve duvar işleri</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="inlineStr">
-        <is>
-          <t>15.225.1010</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
-        </is>
-      </c>
-      <c r="E58" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F58" s="20" t="n">
-        <v>507.91</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>929.28</v>
-      </c>
       <c r="H58" s="5">
-        <f>F58*G58</f>
+        <f>ROUND(F58*G58,2)</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,34 +2889,34 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
+          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F59" s="20" t="n">
-        <v>49.85</v>
+        <v>44.048</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1777.52</v>
+        <v>72192.55</v>
       </c>
       <c r="H59" s="5">
-        <f>F59*G59</f>
+        <f>ROUND(F59*G59,2)</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
@@ -2940,20 +2940,20 @@
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>557.76</v>
+        <v>507.91</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>372.55</v>
+        <v>929.28</v>
       </c>
       <c r="H60" s="5">
-        <f>F60*G60</f>
+        <f>ROUND(F60*G60,2)</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -2977,20 +2977,20 @@
         </is>
       </c>
       <c r="F61" s="20" t="n">
-        <v>557.76</v>
+        <v>49.85</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>381.49</v>
+        <v>1777.52</v>
       </c>
       <c r="H61" s="5">
-        <f>F61*G61</f>
+        <f>ROUND(F61*G61,2)</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
@@ -3017,17 +3017,17 @@
         <v>557.76</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>324.27</v>
+        <v>372.55</v>
       </c>
       <c r="H62" s="5">
-        <f>F62*G62</f>
+        <f>ROUND(F62*G62,2)</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -3054,202 +3054,202 @@
         <v>557.76</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>248.75</v>
+        <v>381.49</v>
       </c>
       <c r="H63" s="5">
-        <f>F63*G63</f>
+        <f>ROUND(F63*G63,2)</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
+          <t>Boya, badana ve cila işleri</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>15.540.1606</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F64" s="20" t="n">
+        <v>557.76</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>324.27</v>
+      </c>
+      <c r="H64" s="5">
+        <f>ROUND(F64*G64,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>Boya, badana ve cila işleri</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>15.540.1537</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F65" s="20" t="n">
+        <v>557.76</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>248.75</v>
+      </c>
+      <c r="H65" s="5">
+        <f>ROUND(F65*G65,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
           <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
         <is>
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C64" s="18" t="inlineStr">
+      <c r="C66" s="18" t="inlineStr">
         <is>
           <t>15.550.1202</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
         </is>
       </c>
-      <c r="E64" s="19" t="inlineStr">
+      <c r="E66" s="19" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F64" s="20" t="n">
+      <c r="F66" s="20" t="n">
         <v>674</v>
       </c>
-      <c r="G64" s="5" t="n">
+      <c r="G66" s="5" t="n">
         <v>147.67</v>
       </c>
-      <c r="H64" s="5">
-        <f>F64*G64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="H66" s="5">
+        <f>ROUND(F66*G66,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
-      <c r="B65" s="17" t="inlineStr">
+      <c r="B67" s="17" t="inlineStr">
         <is>
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C65" s="18" t="inlineStr">
+      <c r="C67" s="18" t="inlineStr">
         <is>
           <t>TKDK-0115</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D67" s="16" t="inlineStr">
         <is>
           <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
         </is>
       </c>
-      <c r="E65" s="19" t="inlineStr">
+      <c r="E67" s="19" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F65" s="20" t="n">
+      <c r="F67" s="20" t="n">
         <v>319.2</v>
       </c>
-      <c r="G65" s="5" t="n">
+      <c r="G67" s="5" t="n">
         <v>227.85</v>
       </c>
-      <c r="H65" s="5">
-        <f>F65*G65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="H67" s="5">
+        <f>ROUND(F67*G67,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
         <is>
           <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C66" s="18" t="inlineStr">
+      <c r="C68" s="18" t="inlineStr">
         <is>
           <t>15.315.1001</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
         </is>
       </c>
-      <c r="E66" s="19" t="inlineStr">
+      <c r="E68" s="19" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F66" s="20" t="n">
+      <c r="F68" s="20" t="n">
         <v>51.2</v>
       </c>
-      <c r="G66" s="5" t="n">
+      <c r="G68" s="5" t="n">
         <v>174.22</v>
       </c>
-      <c r="H66" s="5">
-        <f>F66*G66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
-        </is>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="inlineStr">
-        <is>
-          <t>TKDK-0151</t>
-        </is>
-      </c>
-      <c r="D67" s="16" t="inlineStr">
-        <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
-        </is>
-      </c>
-      <c r="E67" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F67" s="20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>870.14</v>
-      </c>
-      <c r="H67" s="5">
-        <f>F67*G67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="inlineStr">
-        <is>
-          <t>TKDK-0151</t>
-        </is>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
-        </is>
-      </c>
-      <c r="E68" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="F68" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>870.14</v>
-      </c>
       <c r="H68" s="5">
-        <f>F68*G68</f>
+        <f>ROUND(F68*G68,2)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3273,20 +3273,20 @@
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>45</v>
+        <v>4.4</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>870.14</v>
       </c>
       <c r="H69" s="5">
-        <f>F69*G69</f>
+        <f>ROUND(F69*G69,2)</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
@@ -3310,20 +3310,20 @@
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>381.49</v>
+        <v>870.14</v>
       </c>
       <c r="H70" s="5">
-        <f>F70*G70</f>
+        <f>ROUND(F70*G70,2)</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3347,20 +3347,20 @@
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>701.48</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H71" s="5">
-        <f>F71*G71</f>
+        <f>ROUND(F71*G71,2)</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
@@ -3384,20 +3384,20 @@
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>248.75</v>
+        <v>381.49</v>
       </c>
       <c r="H72" s="5">
-        <f>F72*G72</f>
+        <f>ROUND(F72*G72,2)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
+          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
@@ -3421,20 +3421,20 @@
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>5.67</v>
+        <v>60</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>2687.73</v>
+        <v>701.48</v>
       </c>
       <c r="H73" s="5">
-        <f>F73*G73</f>
+        <f>ROUND(F73*G73,2)</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
@@ -3444,34 +3444,34 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>54.315</v>
+        <v>55</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>183.57</v>
+        <v>248.75</v>
       </c>
       <c r="H74" s="5">
-        <f>F74*G74</f>
+        <f>ROUND(F74*G74,2)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -3481,34 +3481,34 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>25</v>
+        <v>5.67</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>330.7</v>
+        <v>2687.73</v>
       </c>
       <c r="H75" s="5">
-        <f>F75*G75</f>
+        <f>ROUND(F75*G75,2)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B76" s="17" t="inlineStr">
@@ -3518,101 +3518,101 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>1</v>
+        <v>54.315</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>7084.16</v>
+        <v>183.57</v>
       </c>
       <c r="H76" s="5">
-        <f>F76*G76</f>
+        <f>ROUND(F76*G76,2)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
+          <t>Kanalizasyon işleri</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="D77" s="16" t="inlineStr">
+        <is>
+          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+        </is>
+      </c>
+      <c r="E77" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>330.7</v>
+      </c>
+      <c r="H77" s="5">
+        <f>ROUND(F77*G77,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
-      <c r="B77" s="17" t="inlineStr">
+      <c r="B78" s="17" t="inlineStr">
         <is>
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
-        <is>
-          <t>30.110.1102</t>
-        </is>
-      </c>
-      <c r="D77" s="16" t="inlineStr">
-        <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
-        </is>
-      </c>
-      <c r="E77" s="19" t="inlineStr">
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>30.100.2105</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+        </is>
+      </c>
+      <c r="E78" s="19" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F77" s="20" t="n">
+      <c r="F78" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G77" s="5" t="n">
-        <v>3528.05</v>
-      </c>
-      <c r="H77" s="5">
-        <f>F77*G77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
-        <is>
-          <t>30.115.1003</t>
-        </is>
-      </c>
-      <c r="D78" s="16" t="inlineStr">
-        <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
-        </is>
-      </c>
-      <c r="E78" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F78" s="20" t="n">
-        <v>2</v>
-      </c>
       <c r="G78" s="5" t="n">
-        <v>1079.2</v>
+        <v>7084.16</v>
       </c>
       <c r="H78" s="5">
-        <f>F78*G78</f>
+        <f>ROUND(F78*G78,2)</f>
         <v/>
       </c>
     </row>
@@ -3629,31 +3629,31 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F79" s="20" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>200</v>
+        <v>3528.05</v>
       </c>
       <c r="H79" s="5">
-        <f>F79*G79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
+        <f>ROUND(F79*G79,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="14" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3666,12 +3666,12 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1996.08</v>
+        <v>1079.2</v>
       </c>
       <c r="H80" s="5">
-        <f>F80*G80</f>
+        <f>ROUND(F80*G80,2)</f>
         <v/>
       </c>
     </row>
@@ -3703,101 +3703,101 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
+          <t>30.140.3104</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="inlineStr">
+        <is>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F81" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="H81" s="5">
+        <f>ROUND(F81*G81,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>30.170.1602</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+        </is>
+      </c>
+      <c r="E82" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>1996.08</v>
+      </c>
+      <c r="H82" s="5">
+        <f>ROUND(F82*G82,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
           <t>30.170.1601</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
+      <c r="D83" s="16" t="inlineStr">
         <is>
           <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
-      <c r="E81" s="19" t="inlineStr">
+      <c r="E83" s="19" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="F81" s="20" t="n">
+      <c r="F83" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="G81" s="5" t="n">
+      <c r="G83" s="5" t="n">
         <v>1370.96</v>
       </c>
-      <c r="H81" s="5">
-        <f>F81*G81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" ht="14" customHeight="1">
-      <c r="A82" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B82" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C82" s="18" t="inlineStr">
-        <is>
-          <t>30.160.6102</t>
-        </is>
-      </c>
-      <c r="D82" s="16" t="inlineStr">
-        <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
-        </is>
-      </c>
-      <c r="E82" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F82" s="20" t="n">
-        <v>500</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>29.06</v>
-      </c>
-      <c r="H82" s="5">
-        <f>F82*G82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="14" customHeight="1">
-      <c r="A83" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C83" s="18" t="inlineStr">
-        <is>
-          <t>30.150.1402</t>
-        </is>
-      </c>
-      <c r="D83" s="16" t="inlineStr">
-        <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
-        </is>
-      </c>
-      <c r="E83" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F83" s="20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>19.5</v>
-      </c>
       <c r="H83" s="5">
-        <f>F83*G83</f>
+        <f>ROUND(F83*G83,2)</f>
         <v/>
       </c>
     </row>
@@ -3814,138 +3814,138 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
+          <t>30.160.6102</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+        </is>
+      </c>
+      <c r="E84" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F84" s="20" t="n">
+        <v>500</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="H84" s="5">
+        <f>ROUND(F84*G84,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>30.150.1402</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="inlineStr">
+        <is>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+        </is>
+      </c>
+      <c r="E85" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F85" s="20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H85" s="5">
+        <f>ROUND(F85*G85,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
           <t>30.150.1401</t>
         </is>
       </c>
-      <c r="D84" s="16" t="inlineStr">
+      <c r="D86" s="16" t="inlineStr">
         <is>
           <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
-      <c r="E84" s="19" t="inlineStr">
+      <c r="E86" s="19" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F84" s="20" t="n">
+      <c r="F86" s="20" t="n">
         <v>600</v>
       </c>
-      <c r="G84" s="5" t="n">
+      <c r="G86" s="5" t="n">
         <v>12.22</v>
       </c>
-      <c r="H84" s="5">
-        <f>F84*G84</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="16" t="inlineStr">
+      <c r="H86" s="5">
+        <f>ROUND(F86*G86,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
-      <c r="B85" s="17" t="inlineStr">
+      <c r="B87" s="17" t="inlineStr">
         <is>
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C85" s="18" t="inlineStr">
+      <c r="C87" s="18" t="inlineStr">
         <is>
           <t>30.140.1105</t>
         </is>
       </c>
-      <c r="D85" s="16" t="inlineStr">
+      <c r="D87" s="16" t="inlineStr">
         <is>
           <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
-      <c r="E85" s="19" t="inlineStr">
+      <c r="E87" s="19" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="F85" s="20" t="n">
+      <c r="F87" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="G85" s="5" t="n">
+      <c r="G87" s="5" t="n">
         <v>157.05</v>
       </c>
-      <c r="H85" s="5">
-        <f>F85*G85</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C86" s="18" t="inlineStr">
-        <is>
-          <t>30.750.3002</t>
-        </is>
-      </c>
-      <c r="D86" s="16" t="inlineStr">
-        <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
-        </is>
-      </c>
-      <c r="E86" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F86" s="20" t="n">
-        <v>186</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>115.96</v>
-      </c>
-      <c r="H86" s="5">
-        <f>F86*G86</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="14" customHeight="1">
-      <c r="A87" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="inlineStr">
-        <is>
-          <t>30.750.1502</t>
-        </is>
-      </c>
-      <c r="D87" s="16" t="inlineStr">
-        <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
-        </is>
-      </c>
-      <c r="E87" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F87" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>15595.61</v>
-      </c>
       <c r="H87" s="5">
-        <f>F87*G87</f>
+        <f>ROUND(F87*G87,2)</f>
         <v/>
       </c>
     </row>
@@ -3962,12 +3962,12 @@
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
@@ -3976,17 +3976,17 @@
         </is>
       </c>
       <c r="F88" s="20" t="n">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>426.72</v>
+        <v>115.96</v>
       </c>
       <c r="H88" s="5">
-        <f>F88*G88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
+        <f>ROUND(F88*G88,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="14" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3999,12 +3999,12 @@
       </c>
       <c r="C89" s="18" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
@@ -4016,14 +4016,14 @@
         <v>1</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>467349.29</v>
+        <v>15595.61</v>
       </c>
       <c r="H89" s="5">
-        <f>F89*G89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="14" customHeight="1">
+        <f>ROUND(F89*G89,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
       <c r="A90" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -4036,27 +4036,27 @@
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F90" s="20" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>79653.55</v>
+        <v>426.72</v>
       </c>
       <c r="H90" s="5">
-        <f>F90*G90</f>
+        <f>ROUND(F90*G90,2)</f>
         <v/>
       </c>
     </row>
@@ -4073,27 +4073,27 @@
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemi — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F91" s="20" t="n">
-        <v>502</v>
+        <v>1</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>199.42</v>
+        <v>467349.29</v>
       </c>
       <c r="H91" s="5">
-        <f>F91*G91</f>
+        <f>ROUND(F91*G91,2)</f>
         <v/>
       </c>
     </row>
@@ -4108,46 +4108,194 @@
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C92" s="19" t="inlineStr">
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>30.740.5406</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F92" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>79653.55</v>
+      </c>
+      <c r="H92" s="5">
+        <f>ROUND(F92*G92,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemi — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme)</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>199.42</v>
+      </c>
+      <c r="H93" s="5">
+        <f>ROUND(F93*G93,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C94" s="19" t="inlineStr">
         <is>
           <t>35.190.1100 (montaj)</t>
         </is>
       </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sisteminin montajı — askı ve konsollarla tespiti</t>
-        </is>
-      </c>
-      <c r="E92" s="19" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="E94" s="19" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="F92" s="20" t="n">
+      <c r="F94" s="20" t="n">
         <v>502</v>
       </c>
-      <c r="G92" s="5" t="n">
+      <c r="G94" s="5" t="n">
         <v>38.72</v>
       </c>
-      <c r="H92" s="5">
-        <f>F92*G92</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="21" t="n"/>
-      <c r="B93" s="21" t="n"/>
-      <c r="C93" s="21" t="n"/>
-      <c r="D93" s="22" t="inlineStr">
+      <c r="H94" s="5">
+        <f>ROUND(F94*G94,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemi kapak sacı — 1,0 mm sıcak daldırma galvanizli (malzeme)</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F95" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>162.37</v>
+      </c>
+      <c r="H95" s="5">
+        <f>ROUND(F95*G95,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C96" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="E96" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F96" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H96" s="5">
+        <f>ROUND(F96*G96,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="21" t="n"/>
+      <c r="B97" s="21" t="n"/>
+      <c r="C97" s="21" t="n"/>
+      <c r="D97" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E93" s="21" t="n"/>
-      <c r="F93" s="21" t="n"/>
-      <c r="G93" s="21" t="n"/>
-      <c r="H93" s="9">
-        <f>SUM(H5:H92)</f>
+      <c r="E97" s="21" t="n"/>
+      <c r="F97" s="21" t="n"/>
+      <c r="G97" s="21" t="n"/>
+      <c r="H97" s="9">
+        <f>SUM(H5:H96)</f>
         <v/>
       </c>
     </row>
@@ -4421,7 +4569,7 @@
         <v>22000</v>
       </c>
       <c r="G5" s="5">
-        <f>E5*F5</f>
+        <f>ROUND(E5*F5,2)</f>
         <v/>
       </c>
     </row>
@@ -4451,7 +4599,7 @@
         <v>510</v>
       </c>
       <c r="G6" s="5">
-        <f>E6*F6</f>
+        <f>ROUND(E6*F6,2)</f>
         <v/>
       </c>
     </row>
@@ -4481,7 +4629,7 @@
         <v>285</v>
       </c>
       <c r="G7" s="5">
-        <f>E7*F7</f>
+        <f>ROUND(E7*F7,2)</f>
         <v/>
       </c>
     </row>
@@ -4511,7 +4659,7 @@
         <v>1800</v>
       </c>
       <c r="G8" s="5">
-        <f>E8*F8</f>
+        <f>ROUND(E8*F8,2)</f>
         <v/>
       </c>
     </row>
@@ -4541,7 +4689,7 @@
         <v>55</v>
       </c>
       <c r="G9" s="5">
-        <f>E9*F9</f>
+        <f>ROUND(E9*F9,2)</f>
         <v/>
       </c>
     </row>
@@ -4571,7 +4719,7 @@
         <v>50000</v>
       </c>
       <c r="G10" s="5">
-        <f>E10*F10</f>
+        <f>ROUND(E10*F10,2)</f>
         <v/>
       </c>
     </row>
@@ -4601,7 +4749,7 @@
         <v>50000</v>
       </c>
       <c r="G11" s="5">
-        <f>E11*F11</f>
+        <f>ROUND(E11*F11,2)</f>
         <v/>
       </c>
     </row>
@@ -4631,7 +4779,7 @@
         <v>25500</v>
       </c>
       <c r="G12" s="5">
-        <f>E12*F12</f>
+        <f>ROUND(E12*F12,2)</f>
         <v/>
       </c>
     </row>
@@ -4661,7 +4809,7 @@
         <v>1200</v>
       </c>
       <c r="G13" s="5">
-        <f>E13*F13</f>
+        <f>ROUND(E13*F13,2)</f>
         <v/>
       </c>
     </row>
@@ -4691,7 +4839,7 @@
         <v>11000</v>
       </c>
       <c r="G14" s="5">
-        <f>E14*F14</f>
+        <f>ROUND(E14*F14,2)</f>
         <v/>
       </c>
     </row>
@@ -4721,7 +4869,7 @@
         <v>210000</v>
       </c>
       <c r="G15" s="5">
-        <f>E15*F15</f>
+        <f>ROUND(E15*F15,2)</f>
         <v/>
       </c>
     </row>
@@ -4751,7 +4899,7 @@
         <v>4500</v>
       </c>
       <c r="G16" s="5">
-        <f>E16*F16</f>
+        <f>ROUND(E16*F16,2)</f>
         <v/>
       </c>
     </row>
@@ -4781,7 +4929,7 @@
         <v>11000</v>
       </c>
       <c r="G17" s="5">
-        <f>E17*F17</f>
+        <f>ROUND(E17*F17,2)</f>
         <v/>
       </c>
     </row>
@@ -4811,7 +4959,7 @@
         <v>6000</v>
       </c>
       <c r="G18" s="5">
-        <f>E18*F18</f>
+        <f>ROUND(E18*F18,2)</f>
         <v/>
       </c>
     </row>
@@ -4841,7 +4989,7 @@
         <v>155000</v>
       </c>
       <c r="G19" s="5">
-        <f>E19*F19</f>
+        <f>ROUND(E19*F19,2)</f>
         <v/>
       </c>
     </row>
@@ -4871,7 +5019,7 @@
         <v>250000</v>
       </c>
       <c r="G20" s="5">
-        <f>E20*F20</f>
+        <f>ROUND(E20*F20,2)</f>
         <v/>
       </c>
     </row>
@@ -5008,7 +5156,7 @@
         <v>52.37</v>
       </c>
       <c r="H5" s="5">
-        <f>F5*G5</f>
+        <f>ROUND(F5*G5,2)</f>
         <v/>
       </c>
     </row>
@@ -5045,7 +5193,7 @@
         <v>60.35</v>
       </c>
       <c r="H6" s="5">
-        <f>F6*G6</f>
+        <f>ROUND(F6*G6,2)</f>
         <v/>
       </c>
     </row>
@@ -5082,7 +5230,7 @@
         <v>60.35</v>
       </c>
       <c r="H7" s="5">
-        <f>F7*G7</f>
+        <f>ROUND(F7*G7,2)</f>
         <v/>
       </c>
     </row>
@@ -5119,7 +5267,7 @@
         <v>60.35</v>
       </c>
       <c r="H8" s="5">
-        <f>F8*G8</f>
+        <f>ROUND(F8*G8,2)</f>
         <v/>
       </c>
     </row>
@@ -5156,7 +5304,7 @@
         <v>60.35</v>
       </c>
       <c r="H9" s="5">
-        <f>F9*G9</f>
+        <f>ROUND(F9*G9,2)</f>
         <v/>
       </c>
     </row>
@@ -5193,7 +5341,7 @@
         <v>60.35</v>
       </c>
       <c r="H10" s="5">
-        <f>F10*G10</f>
+        <f>ROUND(F10*G10,2)</f>
         <v/>
       </c>
     </row>
@@ -5230,7 +5378,7 @@
         <v>60.35</v>
       </c>
       <c r="H11" s="5">
-        <f>F11*G11</f>
+        <f>ROUND(F11*G11,2)</f>
         <v/>
       </c>
     </row>
@@ -5267,7 +5415,7 @@
         <v>2750.45</v>
       </c>
       <c r="H12" s="5">
-        <f>F12*G12</f>
+        <f>ROUND(F12*G12,2)</f>
         <v/>
       </c>
     </row>
@@ -5304,7 +5452,7 @@
         <v>2750.45</v>
       </c>
       <c r="H13" s="5">
-        <f>F13*G13</f>
+        <f>ROUND(F13*G13,2)</f>
         <v/>
       </c>
     </row>
@@ -5341,7 +5489,7 @@
         <v>2750.45</v>
       </c>
       <c r="H14" s="5">
-        <f>F14*G14</f>
+        <f>ROUND(F14*G14,2)</f>
         <v/>
       </c>
     </row>
@@ -5378,7 +5526,7 @@
         <v>2750.45</v>
       </c>
       <c r="H15" s="5">
-        <f>F15*G15</f>
+        <f>ROUND(F15*G15,2)</f>
         <v/>
       </c>
     </row>
@@ -5415,7 +5563,7 @@
         <v>2750.45</v>
       </c>
       <c r="H16" s="5">
-        <f>F16*G16</f>
+        <f>ROUND(F16*G16,2)</f>
         <v/>
       </c>
     </row>
@@ -5452,7 +5600,7 @@
         <v>2750.45</v>
       </c>
       <c r="H17" s="5">
-        <f>F17*G17</f>
+        <f>ROUND(F17*G17,2)</f>
         <v/>
       </c>
     </row>
@@ -5489,7 +5637,7 @@
         <v>2960.45</v>
       </c>
       <c r="H18" s="5">
-        <f>F18*G18</f>
+        <f>ROUND(F18*G18,2)</f>
         <v/>
       </c>
     </row>
@@ -5526,7 +5674,7 @@
         <v>2960.45</v>
       </c>
       <c r="H19" s="5">
-        <f>F19*G19</f>
+        <f>ROUND(F19*G19,2)</f>
         <v/>
       </c>
     </row>
@@ -5563,7 +5711,7 @@
         <v>2960.45</v>
       </c>
       <c r="H20" s="5">
-        <f>F20*G20</f>
+        <f>ROUND(F20*G20,2)</f>
         <v/>
       </c>
     </row>
@@ -5600,7 +5748,7 @@
         <v>2960.45</v>
       </c>
       <c r="H21" s="5">
-        <f>F21*G21</f>
+        <f>ROUND(F21*G21,2)</f>
         <v/>
       </c>
     </row>
@@ -5637,7 +5785,7 @@
         <v>2960.45</v>
       </c>
       <c r="H22" s="5">
-        <f>F22*G22</f>
+        <f>ROUND(F22*G22,2)</f>
         <v/>
       </c>
     </row>
@@ -5674,7 +5822,7 @@
         <v>2960.45</v>
       </c>
       <c r="H23" s="5">
-        <f>F23*G23</f>
+        <f>ROUND(F23*G23,2)</f>
         <v/>
       </c>
     </row>
@@ -5711,7 +5859,7 @@
         <v>863.8</v>
       </c>
       <c r="H24" s="5">
-        <f>F24*G24</f>
+        <f>ROUND(F24*G24,2)</f>
         <v/>
       </c>
     </row>
@@ -5748,7 +5896,7 @@
         <v>863.8</v>
       </c>
       <c r="H25" s="5">
-        <f>F25*G25</f>
+        <f>ROUND(F25*G25,2)</f>
         <v/>
       </c>
     </row>
@@ -5785,7 +5933,7 @@
         <v>863.8</v>
       </c>
       <c r="H26" s="5">
-        <f>F26*G26</f>
+        <f>ROUND(F26*G26,2)</f>
         <v/>
       </c>
     </row>
@@ -5822,7 +5970,7 @@
         <v>863.8</v>
       </c>
       <c r="H27" s="5">
-        <f>F27*G27</f>
+        <f>ROUND(F27*G27,2)</f>
         <v/>
       </c>
     </row>
@@ -5859,7 +6007,7 @@
         <v>863.8</v>
       </c>
       <c r="H28" s="5">
-        <f>F28*G28</f>
+        <f>ROUND(F28*G28,2)</f>
         <v/>
       </c>
     </row>
@@ -5896,7 +6044,7 @@
         <v>863.8</v>
       </c>
       <c r="H29" s="5">
-        <f>F29*G29</f>
+        <f>ROUND(F29*G29,2)</f>
         <v/>
       </c>
     </row>
@@ -5933,7 +6081,7 @@
         <v>39045.24</v>
       </c>
       <c r="H30" s="5">
-        <f>F30*G30</f>
+        <f>ROUND(F30*G30,2)</f>
         <v/>
       </c>
     </row>
@@ -5970,7 +6118,7 @@
         <v>37532.19</v>
       </c>
       <c r="H31" s="5">
-        <f>F31*G31</f>
+        <f>ROUND(F31*G31,2)</f>
         <v/>
       </c>
     </row>
@@ -6007,7 +6155,7 @@
         <v>39045.24</v>
       </c>
       <c r="H32" s="5">
-        <f>F32*G32</f>
+        <f>ROUND(F32*G32,2)</f>
         <v/>
       </c>
     </row>
@@ -6044,7 +6192,7 @@
         <v>39045.24</v>
       </c>
       <c r="H33" s="5">
-        <f>F33*G33</f>
+        <f>ROUND(F33*G33,2)</f>
         <v/>
       </c>
     </row>
@@ -6081,7 +6229,7 @@
         <v>39045.24</v>
       </c>
       <c r="H34" s="5">
-        <f>F34*G34</f>
+        <f>ROUND(F34*G34,2)</f>
         <v/>
       </c>
     </row>
@@ -6118,7 +6266,7 @@
         <v>39045.24</v>
       </c>
       <c r="H35" s="5">
-        <f>F35*G35</f>
+        <f>ROUND(F35*G35,2)</f>
         <v/>
       </c>
     </row>
@@ -6155,7 +6303,7 @@
         <v>39045.24</v>
       </c>
       <c r="H36" s="5">
-        <f>F36*G36</f>
+        <f>ROUND(F36*G36,2)</f>
         <v/>
       </c>
     </row>
@@ -6192,7 +6340,7 @@
         <v>1364.72</v>
       </c>
       <c r="H37" s="5">
-        <f>F37*G37</f>
+        <f>ROUND(F37*G37,2)</f>
         <v/>
       </c>
     </row>
@@ -6229,7 +6377,7 @@
         <v>1364.72</v>
       </c>
       <c r="H38" s="5">
-        <f>F38*G38</f>
+        <f>ROUND(F38*G38,2)</f>
         <v/>
       </c>
     </row>
@@ -6266,7 +6414,7 @@
         <v>940.84</v>
       </c>
       <c r="H39" s="5">
-        <f>F39*G39</f>
+        <f>ROUND(F39*G39,2)</f>
         <v/>
       </c>
     </row>
@@ -6303,7 +6451,7 @@
         <v>330.7</v>
       </c>
       <c r="H40" s="5">
-        <f>F40*G40</f>
+        <f>ROUND(F40*G40,2)</f>
         <v/>
       </c>
     </row>
@@ -6340,7 +6488,7 @@
         <v>2960.45</v>
       </c>
       <c r="H41" s="5">
-        <f>F41*G41</f>
+        <f>ROUND(F41*G41,2)</f>
         <v/>
       </c>
     </row>
@@ -6377,7 +6525,7 @@
         <v>863.8</v>
       </c>
       <c r="H42" s="5">
-        <f>F42*G42</f>
+        <f>ROUND(F42*G42,2)</f>
         <v/>
       </c>
     </row>
@@ -6414,7 +6562,7 @@
         <v>39045.24</v>
       </c>
       <c r="H43" s="5">
-        <f>F43*G43</f>
+        <f>ROUND(F43*G43,2)</f>
         <v/>
       </c>
     </row>
@@ -6451,7 +6599,7 @@
         <v>3744.3</v>
       </c>
       <c r="H44" s="5">
-        <f>F44*G44</f>
+        <f>ROUND(F44*G44,2)</f>
         <v/>
       </c>
     </row>
@@ -6488,7 +6636,7 @@
         <v>31602.33</v>
       </c>
       <c r="H45" s="5">
-        <f>F45*G45</f>
+        <f>ROUND(F45*G45,2)</f>
         <v/>
       </c>
     </row>
@@ -6525,7 +6673,7 @@
         <v>8179.25</v>
       </c>
       <c r="H46" s="5">
-        <f>F46*G46</f>
+        <f>ROUND(F46*G46,2)</f>
         <v/>
       </c>
     </row>
@@ -6562,7 +6710,7 @@
         <v>1504.15</v>
       </c>
       <c r="H47" s="5">
-        <f>F47*G47</f>
+        <f>ROUND(F47*G47,2)</f>
         <v/>
       </c>
     </row>
@@ -6599,7 +6747,7 @@
         <v>4753.16</v>
       </c>
       <c r="H48" s="5">
-        <f>F48*G48</f>
+        <f>ROUND(F48*G48,2)</f>
         <v/>
       </c>
     </row>
@@ -6636,7 +6784,7 @@
         <v>1079.2</v>
       </c>
       <c r="H49" s="5">
-        <f>F49*G49</f>
+        <f>ROUND(F49*G49,2)</f>
         <v/>
       </c>
     </row>
@@ -6673,7 +6821,7 @@
         <v>277.15</v>
       </c>
       <c r="H50" s="5">
-        <f>F50*G50</f>
+        <f>ROUND(F50*G50,2)</f>
         <v/>
       </c>
     </row>
@@ -6710,7 +6858,7 @@
         <v>51.25</v>
       </c>
       <c r="H51" s="5">
-        <f>F51*G51</f>
+        <f>ROUND(F51*G51,2)</f>
         <v/>
       </c>
     </row>
@@ -6747,7 +6895,7 @@
         <v>6229.12</v>
       </c>
       <c r="H52" s="5">
-        <f>F52*G52</f>
+        <f>ROUND(F52*G52,2)</f>
         <v/>
       </c>
     </row>
@@ -6784,7 +6932,7 @@
         <v>7632.76</v>
       </c>
       <c r="H53" s="5">
-        <f>F53*G53</f>
+        <f>ROUND(F53*G53,2)</f>
         <v/>
       </c>
     </row>
@@ -6821,7 +6969,7 @@
         <v>38544.21</v>
       </c>
       <c r="H54" s="5">
-        <f>F54*G54</f>
+        <f>ROUND(F54*G54,2)</f>
         <v/>
       </c>
     </row>
@@ -6858,7 +7006,7 @@
         <v>38544.21</v>
       </c>
       <c r="H55" s="5">
-        <f>F55*G55</f>
+        <f>ROUND(F55*G55,2)</f>
         <v/>
       </c>
     </row>
@@ -7248,7 +7396,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24784397.17</v>
+        <v>24917080.37</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7267,7 +7415,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15584384.42</v>
+        <v>15717067.62</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7381,7 +7529,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4956879.43</v>
+        <v>4983416.07</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H97</f>
+        <f>'A3.1.1 Yapım İşleri'!H89</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>'A3.4-EK Yapım'!H56</f>
+        <f>'A3.4-EK Yapım'!H64</f>
         <v/>
       </c>
       <c r="C12" s="6">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2432,74 +2432,74 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
+    <row r="47" ht="14" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemi — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme)</t>
+          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>502</v>
+        <v>1684.38</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>199.42</v>
+        <v>52.37</v>
       </c>
       <c r="H47" s="5">
         <f>ROUND(F47*G47,2)</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="14" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>502</v>
+        <v>31.429</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>38.72</v>
+        <v>2750.45</v>
       </c>
       <c r="H48" s="5">
         <f>ROUND(F48*G48,2)</f>
@@ -2509,71 +2509,71 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemi kapak sacı — 1,0 mm sıcak daldırma galvanizli (malzeme)</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>361.2</v>
+        <v>115.71</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>162.37</v>
+        <v>2960.45</v>
       </c>
       <c r="H49" s="5">
         <f>ROUND(F49*G49,2)</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="20" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>361.2</v>
+        <v>162.63</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>21.3</v>
+        <v>2960.45</v>
       </c>
       <c r="H50" s="5">
         <f>ROUND(F50*G50,2)</f>
@@ -2583,7 +2583,7 @@
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>1684.38</v>
+        <v>551.26</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>52.37</v>
+        <v>863.8</v>
       </c>
       <c r="H51" s="5">
         <f>ROUND(F51*G51,2)</f>
@@ -2620,7 +2620,7 @@
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
@@ -2630,34 +2630,34 @@
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
+          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>31.429</v>
+        <v>4.16</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>2750.45</v>
+        <v>39045.24</v>
       </c>
       <c r="H52" s="5">
         <f>ROUND(F52*G52,2)</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
+    <row r="53" ht="14" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2667,34 +2667,34 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
+          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>115.71</v>
+        <v>7.288</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>2960.45</v>
+        <v>37532.19</v>
       </c>
       <c r="H53" s="5">
         <f>ROUND(F53*G53,2)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
+    <row r="54" ht="14" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
@@ -2704,34 +2704,34 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
+          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F54" s="20" t="n">
-        <v>162.63</v>
+        <v>3.637</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>2960.45</v>
+        <v>36949.5</v>
       </c>
       <c r="H54" s="5">
         <f>ROUND(F54*G54,2)</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="14" customHeight="1">
+    <row r="55" ht="20" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2741,34 +2741,34 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
+          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>551.26</v>
+        <v>44.048</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>863.8</v>
+        <v>72192.55</v>
       </c>
       <c r="H55" s="5">
         <f>ROUND(F55*G55,2)</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="14" customHeight="1">
+    <row r="56" ht="20" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2778,34 +2778,34 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>4.16</v>
+        <v>507.91</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>39045.24</v>
+        <v>929.28</v>
       </c>
       <c r="H56" s="5">
         <f>ROUND(F56*G56,2)</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
+    <row r="57" ht="20" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -2815,34 +2815,34 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>7.288</v>
+        <v>49.85</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>37532.19</v>
+        <v>1777.52</v>
       </c>
       <c r="H57" s="5">
         <f>ROUND(F57*G57,2)</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="14" customHeight="1">
+    <row r="58" ht="20" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2852,24 +2852,24 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>3.637</v>
+        <v>557.76</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>36949.5</v>
+        <v>372.55</v>
       </c>
       <c r="H58" s="5">
         <f>ROUND(F58*G58,2)</f>
@@ -2879,7 +2879,7 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,24 +2889,24 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F59" s="20" t="n">
-        <v>44.048</v>
+        <v>557.76</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>72192.55</v>
+        <v>381.49</v>
       </c>
       <c r="H59" s="5">
         <f>ROUND(F59*G59,2)</f>
@@ -2916,7 +2916,7 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
@@ -2940,10 +2940,10 @@
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>507.91</v>
+        <v>557.76</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>929.28</v>
+        <v>324.27</v>
       </c>
       <c r="H60" s="5">
         <f>ROUND(F60*G60,2)</f>
@@ -2953,7 +2953,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="F61" s="20" t="n">
-        <v>49.85</v>
+        <v>557.76</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>1777.52</v>
+        <v>248.75</v>
       </c>
       <c r="H61" s="5">
         <f>ROUND(F61*G61,2)</f>
@@ -2990,7 +2990,7 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -3000,34 +3000,34 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
+          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>557.76</v>
+        <v>674</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>372.55</v>
+        <v>147.67</v>
       </c>
       <c r="H62" s="5">
         <f>ROUND(F62*G62,2)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
+    <row r="63" ht="14" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,34 +3037,34 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
+          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>557.76</v>
+        <v>319.2</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>381.49</v>
+        <v>227.85</v>
       </c>
       <c r="H63" s="5">
         <f>ROUND(F63*G63,2)</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
+    <row r="64" ht="14" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>557.76</v>
+        <v>51.2</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>324.27</v>
+        <v>174.22</v>
       </c>
       <c r="H64" s="5">
         <f>ROUND(F64*G64,2)</f>
@@ -3101,7 +3101,7 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>557.76</v>
+        <v>4.4</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>248.75</v>
+        <v>870.14</v>
       </c>
       <c r="H65" s="5">
         <f>ROUND(F65*G65,2)</f>
@@ -3138,7 +3138,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3148,34 +3148,34 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>674</v>
+        <v>9</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>147.67</v>
+        <v>870.14</v>
       </c>
       <c r="H66" s="5">
         <f>ROUND(F66*G66,2)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="14" customHeight="1">
+    <row r="67" ht="20" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3185,34 +3185,34 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>319.2</v>
+        <v>45</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>227.85</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H67" s="5">
         <f>ROUND(F67*G67,2)</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="14" customHeight="1">
+    <row r="68" ht="20" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3222,24 +3222,24 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>51.2</v>
+        <v>90</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>174.22</v>
+        <v>381.49</v>
       </c>
       <c r="H68" s="5">
         <f>ROUND(F68*G68,2)</f>
@@ -3249,7 +3249,7 @@
     <row r="69" ht="20" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
+          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
@@ -3273,10 +3273,10 @@
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>4.4</v>
+        <v>60</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>870.14</v>
+        <v>701.48</v>
       </c>
       <c r="H69" s="5">
         <f>ROUND(F69*G69,2)</f>
@@ -3286,7 +3286,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>870.14</v>
+        <v>248.75</v>
       </c>
       <c r="H70" s="5">
         <f>ROUND(F70*G70,2)</f>
@@ -3323,7 +3323,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -3333,12 +3333,12 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
+          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>45</v>
+        <v>5.67</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>2687.73</v>
       </c>
       <c r="H71" s="5">
         <f>ROUND(F71*G71,2)</f>
@@ -3360,7 +3360,7 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
+          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>90</v>
+        <v>54.315</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>381.49</v>
+        <v>183.57</v>
       </c>
       <c r="H72" s="5">
         <f>ROUND(F72*G72,2)</f>
@@ -3397,7 +3397,7 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -3407,24 +3407,24 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
+          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>701.48</v>
+        <v>330.7</v>
       </c>
       <c r="H73" s="5">
         <f>ROUND(F73*G73,2)</f>
@@ -3434,7 +3434,7 @@
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
@@ -3444,24 +3444,24 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>248.75</v>
+        <v>7084.16</v>
       </c>
       <c r="H74" s="5">
         <f>ROUND(F74*G74,2)</f>
@@ -3471,7 +3471,7 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -3481,34 +3481,34 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>5.67</v>
+        <v>1</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>2687.73</v>
+        <v>3528.05</v>
       </c>
       <c r="H75" s="5">
         <f>ROUND(F75*G75,2)</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="20" customHeight="1">
+    <row r="76" ht="14" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B76" s="17" t="inlineStr">
@@ -3518,24 +3518,24 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>54.315</v>
+        <v>2</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>183.57</v>
+        <v>1079.2</v>
       </c>
       <c r="H76" s="5">
         <f>ROUND(F76*G76,2)</f>
@@ -3545,7 +3545,7 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="F77" s="20" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>330.7</v>
+        <v>200</v>
       </c>
       <c r="H77" s="5">
         <f>ROUND(F77*G77,2)</f>
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="F78" s="20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>7084.16</v>
+        <v>1996.08</v>
       </c>
       <c r="H78" s="5">
         <f>ROUND(F78*G78,2)</f>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="F79" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>3528.05</v>
+        <v>1370.96</v>
       </c>
       <c r="H79" s="5">
         <f>ROUND(F79*G79,2)</f>
@@ -3666,31 +3666,31 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1079.2</v>
+        <v>29.06</v>
       </c>
       <c r="H80" s="5">
         <f>ROUND(F80*G80,2)</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="20" customHeight="1">
+    <row r="81" ht="14" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3717,17 +3717,17 @@
         </is>
       </c>
       <c r="F81" s="20" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>200</v>
+        <v>19.5</v>
       </c>
       <c r="H81" s="5">
         <f>ROUND(F81*G81,2)</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
+    <row r="82" ht="14" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3740,24 +3740,24 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F82" s="20" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1996.08</v>
+        <v>12.22</v>
       </c>
       <c r="H82" s="5">
         <f>ROUND(F82*G82,2)</f>
@@ -3777,31 +3777,31 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F83" s="20" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1370.96</v>
+        <v>157.05</v>
       </c>
       <c r="H83" s="5">
         <f>ROUND(F83*G83,2)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
+    <row r="84" ht="20" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="F84" s="20" t="n">
-        <v>500</v>
+        <v>186</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>29.06</v>
+        <v>115.96</v>
       </c>
       <c r="H84" s="5">
         <f>ROUND(F84*G84,2)</f>
@@ -3851,31 +3851,31 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F85" s="20" t="n">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>19.5</v>
+        <v>15595.61</v>
       </c>
       <c r="H85" s="5">
         <f>ROUND(F85*G85,2)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="14" customHeight="1">
+    <row r="86" ht="20" customHeight="1">
       <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3888,12 +3888,12 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F86" s="20" t="n">
-        <v>600</v>
+        <v>16</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>12.22</v>
+        <v>426.72</v>
       </c>
       <c r="H86" s="5">
         <f>ROUND(F86*G86,2)</f>
@@ -3925,31 +3925,31 @@
       </c>
       <c r="C87" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F87" s="20" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>157.05</v>
+        <v>467349.29</v>
       </c>
       <c r="H87" s="5">
         <f>ROUND(F87*G87,2)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
+    <row r="88" ht="14" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3962,340 +3962,44 @@
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F88" s="20" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>115.96</v>
+        <v>79653.55</v>
       </c>
       <c r="H88" s="5">
         <f>ROUND(F88*G88,2)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>30.750.1502</t>
-        </is>
-      </c>
-      <c r="D89" s="16" t="inlineStr">
-        <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
-        </is>
-      </c>
-      <c r="E89" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F89" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>15595.61</v>
-      </c>
-      <c r="H89" s="5">
-        <f>ROUND(F89*G89,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>30.750.2001</t>
-        </is>
-      </c>
-      <c r="D90" s="16" t="inlineStr">
-        <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
-        </is>
-      </c>
-      <c r="E90" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F90" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>426.72</v>
-      </c>
-      <c r="H90" s="5">
-        <f>ROUND(F90*G90,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="inlineStr">
-        <is>
-          <t>30.740.1106</t>
-        </is>
-      </c>
-      <c r="D91" s="16" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
-        </is>
-      </c>
-      <c r="E91" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F91" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>467349.29</v>
-      </c>
-      <c r="H91" s="5">
-        <f>ROUND(F91*G91,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="14" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
-        </is>
-      </c>
-      <c r="E92" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F92" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>79653.55</v>
-      </c>
-      <c r="H92" s="5">
-        <f>ROUND(F92*G92,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C93" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
-        </is>
-      </c>
-      <c r="D93" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemi — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme)</t>
-        </is>
-      </c>
-      <c r="E93" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F93" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>199.42</v>
-      </c>
-      <c r="H93" s="5">
-        <f>ROUND(F93*G93,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C94" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="E94" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F94" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="H94" s="5">
-        <f>ROUND(F94*G94,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C95" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="D95" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemi kapak sacı — 1,0 mm sıcak daldırma galvanizli (malzeme)</t>
-        </is>
-      </c>
-      <c r="E95" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F95" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>162.37</v>
-      </c>
-      <c r="H95" s="5">
-        <f>ROUND(F95*G95,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C96" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="E96" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F96" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H96" s="5">
-        <f>ROUND(F96*G96,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="21" t="n"/>
-      <c r="B97" s="21" t="n"/>
-      <c r="C97" s="21" t="n"/>
-      <c r="D97" s="22" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="21" t="n"/>
+      <c r="B89" s="21" t="n"/>
+      <c r="C89" s="21" t="n"/>
+      <c r="D89" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E97" s="21" t="n"/>
-      <c r="F97" s="21" t="n"/>
-      <c r="G97" s="21" t="n"/>
-      <c r="H97" s="9">
-        <f>SUM(H5:H96)</f>
+      <c r="E89" s="21" t="n"/>
+      <c r="F89" s="21" t="n"/>
+      <c r="G89" s="21" t="n"/>
+      <c r="H89" s="9">
+        <f>SUM(H5:H88)</f>
         <v/>
       </c>
     </row>
@@ -5053,7 +4757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7010,20 +6714,316 @@
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="21" t="n"/>
-      <c r="B56" s="21" t="n"/>
-      <c r="C56" s="21" t="n"/>
-      <c r="D56" s="22" t="inlineStr">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>199.42</v>
+      </c>
+      <c r="H56" s="5">
+        <f>ROUND(F56*G56,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>199.42</v>
+      </c>
+      <c r="H57" s="5">
+        <f>ROUND(F57*G57,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="H58" s="5">
+        <f>ROUND(F58*G58,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F59" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="H59" s="5">
+        <f>ROUND(F59*G59,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F60" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>162.37</v>
+      </c>
+      <c r="H60" s="5">
+        <f>ROUND(F60*G60,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>162.37</v>
+      </c>
+      <c r="H61" s="5">
+        <f>ROUND(F61*G61,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H62" s="5">
+        <f>ROUND(F62*G62,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H63" s="5">
+        <f>ROUND(F63*G63,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="n"/>
+      <c r="B64" s="21" t="n"/>
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="22" t="inlineStr">
         <is>
           <t>HİBE DIŞI YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E56" s="21" t="n"/>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="n"/>
-      <c r="H56" s="9">
-        <f>SUM(H5:H55)</f>
+      <c r="E64" s="21" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="n"/>
+      <c r="H64" s="9">
+        <f>SUM(H5:H63)</f>
         <v/>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15717067.62</v>
+        <v>15345291.86</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5618052.75</v>
+        <v>5989828.51</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9200012.75</v>
+        <v>9571788.51</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H89</f>
+        <f>'A3.1.1 Yapım İşleri'!H99</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>'A3.4-EK Yapım'!H64</f>
+        <f>'A3.4-EK Yapım'!H56</f>
         <v/>
       </c>
       <c r="C12" s="6">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2432,74 +2432,74 @@
         <v/>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1">
+    <row r="47" ht="20" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
+          <t>Kablo tava sistemi — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme)</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>1684.38</v>
+        <v>502</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>52.37</v>
+        <v>199.42</v>
       </c>
       <c r="H47" s="5">
         <f>ROUND(F47*G47,2)</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>31.429</v>
+        <v>502</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>2750.45</v>
+        <v>38.72</v>
       </c>
       <c r="H48" s="5">
         <f>ROUND(F48*G48,2)</f>
@@ -2509,71 +2509,71 @@
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
+          <t>Kablo tava sistemi kapak sacı — 1,0 mm sıcak daldırma galvanizli (malzeme)</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>115.71</v>
+        <v>361.2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2960.45</v>
+        <v>162.37</v>
       </c>
       <c r="H49" s="5">
         <f>ROUND(F49*G49,2)</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>162.63</v>
+        <v>361.2</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2960.45</v>
+        <v>21.3</v>
       </c>
       <c r="H50" s="5">
         <f>ROUND(F50*G50,2)</f>
@@ -2583,34 +2583,34 @@
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>30.190.1304</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>551.26</v>
+        <v>123</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>863.8</v>
+        <v>233.28</v>
       </c>
       <c r="H51" s="5">
         <f>ROUND(F51*G51,2)</f>
@@ -2620,7 +2620,7 @@
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
@@ -2630,24 +2630,24 @@
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>4.16</v>
+        <v>1684.38</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>39045.24</v>
+        <v>52.37</v>
       </c>
       <c r="H52" s="5">
         <f>ROUND(F52*G52,2)</f>
@@ -2657,7 +2657,7 @@
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2667,34 +2667,34 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>7.288</v>
+        <v>31.429</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>37532.19</v>
+        <v>2750.45</v>
       </c>
       <c r="H53" s="5">
         <f>ROUND(F53*G53,2)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="14" customHeight="1">
+    <row r="54" ht="20" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
@@ -2704,24 +2704,24 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F54" s="20" t="n">
-        <v>3.637</v>
+        <v>115.71</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>36949.5</v>
+        <v>2960.45</v>
       </c>
       <c r="H54" s="5">
         <f>ROUND(F54*G54,2)</f>
@@ -2731,7 +2731,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2741,34 +2741,34 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
+          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>44.048</v>
+        <v>162.63</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>72192.55</v>
+        <v>2960.45</v>
       </c>
       <c r="H55" s="5">
         <f>ROUND(F55*G55,2)</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
+    <row r="56" ht="14" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
@@ -2792,20 +2792,20 @@
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>507.91</v>
+        <v>551.26</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>929.28</v>
+        <v>863.8</v>
       </c>
       <c r="H56" s="5">
         <f>ROUND(F56*G56,2)</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
+    <row r="57" ht="14" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -2815,34 +2815,34 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
+          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>49.85</v>
+        <v>4.16</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1777.52</v>
+        <v>39045.24</v>
       </c>
       <c r="H57" s="5">
         <f>ROUND(F57*G57,2)</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
+    <row r="58" ht="14" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2852,34 +2852,34 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
+          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>557.76</v>
+        <v>7.288</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>372.55</v>
+        <v>37532.19</v>
       </c>
       <c r="H58" s="5">
         <f>ROUND(F58*G58,2)</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
+    <row r="59" ht="14" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,24 +2889,24 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
+          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F59" s="20" t="n">
-        <v>557.76</v>
+        <v>3.637</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>381.49</v>
+        <v>36949.5</v>
       </c>
       <c r="H59" s="5">
         <f>ROUND(F59*G59,2)</f>
@@ -2916,7 +2916,7 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,24 +2926,24 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>557.76</v>
+        <v>44.048</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>324.27</v>
+        <v>72192.55</v>
       </c>
       <c r="H60" s="5">
         <f>ROUND(F60*G60,2)</f>
@@ -2953,7 +2953,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="F61" s="20" t="n">
-        <v>557.76</v>
+        <v>507.91</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>248.75</v>
+        <v>929.28</v>
       </c>
       <c r="H61" s="5">
         <f>ROUND(F61*G61,2)</f>
@@ -2990,7 +2990,7 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -3000,34 +3000,34 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>674</v>
+        <v>49.85</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>147.67</v>
+        <v>1777.52</v>
       </c>
       <c r="H62" s="5">
         <f>ROUND(F62*G62,2)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="14" customHeight="1">
+    <row r="63" ht="20" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,34 +3037,34 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>319.2</v>
+        <v>557.76</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>227.85</v>
+        <v>372.55</v>
       </c>
       <c r="H63" s="5">
         <f>ROUND(F63*G63,2)</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="14" customHeight="1">
+    <row r="64" ht="20" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>51.2</v>
+        <v>557.76</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>174.22</v>
+        <v>381.49</v>
       </c>
       <c r="H64" s="5">
         <f>ROUND(F64*G64,2)</f>
@@ -3101,7 +3101,7 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>4.4</v>
+        <v>557.76</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>870.14</v>
+        <v>324.27</v>
       </c>
       <c r="H65" s="5">
         <f>ROUND(F65*G65,2)</f>
@@ -3138,7 +3138,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>9</v>
+        <v>557.76</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>870.14</v>
+        <v>248.75</v>
       </c>
       <c r="H66" s="5">
         <f>ROUND(F66*G66,2)</f>
@@ -3175,7 +3175,7 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3185,34 +3185,34 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
+          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>45</v>
+        <v>674</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>147.67</v>
       </c>
       <c r="H67" s="5">
         <f>ROUND(F67*G67,2)</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
+    <row r="68" ht="14" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3222,34 +3222,34 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
+          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>90</v>
+        <v>319.2</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>381.49</v>
+        <v>227.85</v>
       </c>
       <c r="H68" s="5">
         <f>ROUND(F68*G68,2)</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
+    <row r="69" ht="14" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,24 +3259,24 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
+          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>60</v>
+        <v>51.2</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>701.48</v>
+        <v>174.22</v>
       </c>
       <c r="H69" s="5">
         <f>ROUND(F69*G69,2)</f>
@@ -3286,7 +3286,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>55</v>
+        <v>4.4</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>248.75</v>
+        <v>870.14</v>
       </c>
       <c r="H70" s="5">
         <f>ROUND(F70*G70,2)</f>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
+          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>5.67</v>
+        <v>9</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>2687.73</v>
+        <v>870.14</v>
       </c>
       <c r="H71" s="5">
         <f>ROUND(F71*G71,2)</f>
@@ -3360,7 +3360,7 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>54.315</v>
+        <v>45</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>183.57</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H72" s="5">
         <f>ROUND(F72*G72,2)</f>
@@ -3397,7 +3397,7 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -3407,24 +3407,24 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>330.7</v>
+        <v>381.49</v>
       </c>
       <c r="H73" s="5">
         <f>ROUND(F73*G73,2)</f>
@@ -3434,7 +3434,7 @@
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
@@ -3444,24 +3444,24 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>7084.16</v>
+        <v>701.48</v>
       </c>
       <c r="H74" s="5">
         <f>ROUND(F74*G74,2)</f>
@@ -3471,7 +3471,7 @@
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -3481,34 +3481,34 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>3528.05</v>
+        <v>248.75</v>
       </c>
       <c r="H75" s="5">
         <f>ROUND(F75*G75,2)</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="14" customHeight="1">
+    <row r="76" ht="20" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B76" s="17" t="inlineStr">
@@ -3518,24 +3518,24 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>2</v>
+        <v>5.67</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1079.2</v>
+        <v>2687.73</v>
       </c>
       <c r="H76" s="5">
         <f>ROUND(F76*G76,2)</f>
@@ -3545,7 +3545,7 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
@@ -3555,24 +3555,24 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F77" s="20" t="n">
-        <v>300</v>
+        <v>54.315</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>200</v>
+        <v>183.57</v>
       </c>
       <c r="H77" s="5">
         <f>ROUND(F77*G77,2)</f>
@@ -3582,7 +3582,7 @@
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B78" s="17" t="inlineStr">
@@ -3592,24 +3592,24 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F78" s="20" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1996.08</v>
+        <v>330.7</v>
       </c>
       <c r="H78" s="5">
         <f>ROUND(F78*G78,2)</f>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3643,17 +3643,17 @@
         </is>
       </c>
       <c r="F79" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1370.96</v>
+        <v>7084.16</v>
       </c>
       <c r="H79" s="5">
         <f>ROUND(F79*G79,2)</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="14" customHeight="1">
+    <row r="80" ht="20" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>29.06</v>
+        <v>3528.05</v>
       </c>
       <c r="H80" s="5">
         <f>ROUND(F80*G80,2)</f>
@@ -3703,31 +3703,31 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F81" s="20" t="n">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>19.5</v>
+        <v>1079.2</v>
       </c>
       <c r="H81" s="5">
         <f>ROUND(F81*G81,2)</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="14" customHeight="1">
+    <row r="82" ht="20" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3740,12 +3740,12 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
@@ -3754,10 +3754,10 @@
         </is>
       </c>
       <c r="F82" s="20" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>12.22</v>
+        <v>200</v>
       </c>
       <c r="H82" s="5">
         <f>ROUND(F82*G82,2)</f>
@@ -3777,24 +3777,24 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F83" s="20" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>157.05</v>
+        <v>1996.08</v>
       </c>
       <c r="H83" s="5">
         <f>ROUND(F83*G83,2)</f>
@@ -3814,24 +3814,24 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F84" s="20" t="n">
-        <v>186</v>
+        <v>2</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>115.96</v>
+        <v>1370.96</v>
       </c>
       <c r="H84" s="5">
         <f>ROUND(F84*G84,2)</f>
@@ -3851,31 +3851,31 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F85" s="20" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>15595.61</v>
+        <v>29.06</v>
       </c>
       <c r="H85" s="5">
         <f>ROUND(F85*G85,2)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="20" customHeight="1">
+    <row r="86" ht="14" customHeight="1">
       <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3888,12 +3888,12 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
@@ -3902,17 +3902,17 @@
         </is>
       </c>
       <c r="F86" s="20" t="n">
-        <v>16</v>
+        <v>2000</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>426.72</v>
+        <v>19.5</v>
       </c>
       <c r="H86" s="5">
         <f>ROUND(F86*G86,2)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
+    <row r="87" ht="14" customHeight="1">
       <c r="A87" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3925,31 +3925,31 @@
       </c>
       <c r="C87" s="18" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F87" s="20" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>467349.29</v>
+        <v>12.22</v>
       </c>
       <c r="H87" s="5">
         <f>ROUND(F87*G87,2)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="14" customHeight="1">
+    <row r="88" ht="20" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3962,44 +3962,414 @@
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F88" s="20" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>79653.55</v>
+        <v>157.05</v>
       </c>
       <c r="H88" s="5">
         <f>ROUND(F88*G88,2)</f>
         <v/>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="21" t="n"/>
-      <c r="B89" s="21" t="n"/>
-      <c r="C89" s="21" t="n"/>
-      <c r="D89" s="22" t="inlineStr">
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>30.750.3002</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+        </is>
+      </c>
+      <c r="E89" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="n">
+        <v>186</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>115.96</v>
+      </c>
+      <c r="H89" s="5">
+        <f>ROUND(F89*G89,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>30.750.1502</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+        </is>
+      </c>
+      <c r="E90" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F90" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>15595.61</v>
+      </c>
+      <c r="H90" s="5">
+        <f>ROUND(F90*G90,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>30.750.2001</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="inlineStr">
+        <is>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F91" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>426.72</v>
+      </c>
+      <c r="H91" s="5">
+        <f>ROUND(F91*G91,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>30.740.1106</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F92" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>467349.29</v>
+      </c>
+      <c r="H92" s="5">
+        <f>ROUND(F92*G92,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="14" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>30.740.5406</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>79653.55</v>
+      </c>
+      <c r="H93" s="5">
+        <f>ROUND(F93*G93,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemi — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme)</t>
+        </is>
+      </c>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F94" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>199.42</v>
+      </c>
+      <c r="H94" s="5">
+        <f>ROUND(F94*G94,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F95" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="H95" s="5">
+        <f>ROUND(F95*G95,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemi kapak sacı — 1,0 mm sıcak daldırma galvanizli (malzeme)</t>
+        </is>
+      </c>
+      <c r="E96" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F96" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>162.37</v>
+      </c>
+      <c r="H96" s="5">
+        <f>ROUND(F96*G96,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F97" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H97" s="5">
+        <f>ROUND(F97*G97,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>30.190.1304</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
+        <is>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli</t>
+        </is>
+      </c>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F98" s="20" t="n">
+        <v>123</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>233.28</v>
+      </c>
+      <c r="H98" s="5">
+        <f>ROUND(F98*G98,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="n"/>
+      <c r="B99" s="21" t="n"/>
+      <c r="C99" s="21" t="n"/>
+      <c r="D99" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E89" s="21" t="n"/>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="n"/>
-      <c r="H89" s="9">
-        <f>SUM(H5:H88)</f>
+      <c r="E99" s="21" t="n"/>
+      <c r="F99" s="21" t="n"/>
+      <c r="G99" s="21" t="n"/>
+      <c r="H99" s="9">
+        <f>SUM(H5:H98)</f>
         <v/>
       </c>
     </row>
@@ -4757,7 +5127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6714,316 +7084,20 @@
         <v/>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E56" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F56" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>199.42</v>
-      </c>
-      <c r="H56" s="5">
-        <f>ROUND(F56*G56,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E57" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F57" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>199.42</v>
-      </c>
-      <c r="H57" s="5">
-        <f>ROUND(F57*G57,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="E58" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F58" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="H58" s="5">
-        <f>ROUND(F58*G58,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C59" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="E59" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F59" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="H59" s="5">
-        <f>ROUND(F59*G59,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E60" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F60" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>162.37</v>
-      </c>
-      <c r="H60" s="5">
-        <f>ROUND(F60*G60,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="D61" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E61" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F61" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>162.37</v>
-      </c>
-      <c r="H61" s="5">
-        <f>ROUND(F61*G61,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C62" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="E62" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F62" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H62" s="5">
-        <f>ROUND(F62*G62,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="E63" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F63" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H63" s="5">
-        <f>ROUND(F63*G63,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="21" t="n"/>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
-      <c r="D64" s="22" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="21" t="n"/>
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="22" t="inlineStr">
         <is>
           <t>HİBE DIŞI YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E64" s="21" t="n"/>
-      <c r="F64" s="21" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="9">
-        <f>SUM(H5:H63)</f>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="9">
+        <f>SUM(H5:H55)</f>
         <v/>
       </c>
     </row>
@@ -7396,7 +7470,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24917080.37</v>
+        <v>24974467.25</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7415,7 +7489,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15345291.86</v>
+        <v>15774454.5</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7434,7 +7508,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5989828.51</v>
+        <v>5618052.75</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7491,7 +7565,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9571788.51</v>
+        <v>9200012.75</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7529,7 +7603,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4983416.07</v>
+        <v>4994893.45</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H99</f>
+        <f>'A3.1.1 Yapım İşleri'!H91</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -896,7 +896,7 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
       <c r="E5" s="19" t="inlineStr">
@@ -915,7 +915,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="14" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Beton işleri</t>
@@ -933,7 +933,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E6" s="19" t="inlineStr">
@@ -952,7 +952,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Betonarme işleri</t>
@@ -970,7 +970,7 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="F7" s="20" t="n">
-        <v>115.71</v>
+        <v>278.34</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>2960.45</v>
@@ -989,10 +989,10 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
@@ -1002,34 +1002,34 @@
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F8" s="20" t="n">
-        <v>162.63</v>
+        <v>551.26</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2960.45</v>
+        <v>863.8</v>
       </c>
       <c r="H8" s="5">
         <f>ROUND(F8*G8,2)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="14" customHeight="1">
+    <row r="9" ht="20" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -1039,31 +1039,31 @@
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F9" s="20" t="n">
-        <v>551.26</v>
+        <v>4.16</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>863.8</v>
+        <v>39045.24</v>
       </c>
       <c r="H9" s="5">
         <f>ROUND(F9*G9,2)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="14" customHeight="1">
+    <row r="10" ht="20" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="F10" s="20" t="n">
-        <v>4.16</v>
+        <v>7.288</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>39045.24</v>
+        <v>37532.19</v>
       </c>
       <c r="H10" s="5">
         <f>ROUND(F10*G10,2)</f>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>Nervürlü çelik hasırın yerine konulması</t>
         </is>
       </c>
       <c r="E11" s="19" t="inlineStr">
@@ -1127,20 +1127,20 @@
         </is>
       </c>
       <c r="F11" s="20" t="n">
-        <v>7.288</v>
+        <v>3.637</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>37532.19</v>
+        <v>36949.5</v>
       </c>
       <c r="H11" s="5">
         <f>ROUND(F11*G11,2)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="14" customHeight="1">
+    <row r="12" ht="20" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
+          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="F12" s="20" t="n">
-        <v>3.637</v>
+        <v>44.048</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>36949.5</v>
+        <v>72192.55</v>
       </c>
       <c r="H12" s="5">
         <f>ROUND(F12*G12,2)</f>
@@ -1177,7 +1177,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
@@ -1187,24 +1187,24 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>44.048</v>
+        <v>507.91</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>72192.55</v>
+        <v>929.28</v>
       </c>
       <c r="H13" s="5">
         <f>ROUND(F13*G13,2)</f>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -1238,20 +1238,20 @@
         </is>
       </c>
       <c r="F14" s="20" t="n">
-        <v>507.91</v>
+        <v>49.85</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>929.28</v>
+        <v>1777.52</v>
       </c>
       <c r="H14" s="5">
         <f>ROUND(F14*G14,2)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>49.85</v>
+        <v>557.76</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1777.52</v>
+        <v>372.55</v>
       </c>
       <c r="H15" s="5">
         <f>ROUND(F15*G15,2)</f>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="F16" s="20" t="n">
-        <v>557.76</v>
+        <v>647.76</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>372.55</v>
+        <v>381.49</v>
       </c>
       <c r="H16" s="5">
         <f>ROUND(F16*G16,2)</f>
@@ -1325,7 +1325,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
@@ -1352,7 +1352,7 @@
         <v>557.76</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>381.49</v>
+        <v>324.27</v>
       </c>
       <c r="H17" s="5">
         <f>ROUND(F17*G17,2)</f>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
@@ -1386,10 +1386,10 @@
         </is>
       </c>
       <c r="F18" s="20" t="n">
-        <v>557.76</v>
+        <v>612.76</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>324.27</v>
+        <v>248.75</v>
       </c>
       <c r="H18" s="5">
         <f>ROUND(F18*G18,2)</f>
@@ -1399,7 +1399,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
@@ -1409,34 +1409,34 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F19" s="20" t="n">
-        <v>557.76</v>
+        <v>674</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>248.75</v>
+        <v>147.67</v>
       </c>
       <c r="H19" s="5">
         <f>ROUND(F19*G19,2)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
@@ -1460,17 +1460,17 @@
         </is>
       </c>
       <c r="F20" s="20" t="n">
-        <v>674</v>
+        <v>319.2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>147.67</v>
+        <v>227.85</v>
       </c>
       <c r="H20" s="5">
         <f>ROUND(F20*G20,2)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="14" customHeight="1">
+    <row r="21" ht="20" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Çatı ve sundurma işleri</t>
@@ -1483,34 +1483,34 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>319.2</v>
+        <v>51.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>227.85</v>
+        <v>174.22</v>
       </c>
       <c r="H21" s="5">
         <f>ROUND(F21*G21,2)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="14" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
@@ -1520,24 +1520,24 @@
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F22" s="20" t="n">
-        <v>51.2</v>
+        <v>13.4</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>174.22</v>
+        <v>870.14</v>
       </c>
       <c r="H22" s="5">
         <f>ROUND(F22*G22,2)</f>
@@ -1547,7 +1547,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
@@ -1571,20 +1571,20 @@
         </is>
       </c>
       <c r="F23" s="20" t="n">
-        <v>4.4</v>
+        <v>45</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>870.14</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H23" s="5">
         <f>ROUND(F23*G23,2)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
+    <row r="24" ht="40" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -1608,20 +1608,20 @@
         </is>
       </c>
       <c r="F24" s="20" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>870.14</v>
+        <v>701.48</v>
       </c>
       <c r="H24" s="5">
         <f>ROUND(F24*G24,2)</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -1645,10 +1645,10 @@
         </is>
       </c>
       <c r="F25" s="20" t="n">
-        <v>45</v>
+        <v>5.67</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>2687.73</v>
       </c>
       <c r="H25" s="5">
         <f>ROUND(F25*G25,2)</f>
@@ -1658,7 +1658,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
@@ -1668,24 +1668,24 @@
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F26" s="20" t="n">
-        <v>90</v>
+        <v>54.315</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>381.49</v>
+        <v>183.57</v>
       </c>
       <c r="H26" s="5">
         <f>ROUND(F26*G26,2)</f>
@@ -1695,7 +1695,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
@@ -1705,24 +1705,24 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E27" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F27" s="20" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>701.48</v>
+        <v>330.7</v>
       </c>
       <c r="H27" s="5">
         <f>ROUND(F27*G27,2)</f>
@@ -1732,7 +1732,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
@@ -1742,24 +1742,24 @@
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F28" s="20" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>248.75</v>
+        <v>7084.16</v>
       </c>
       <c r="H28" s="5">
         <f>ROUND(F28*G28,2)</f>
@@ -1769,7 +1769,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
@@ -1779,24 +1779,24 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F29" s="20" t="n">
-        <v>5.67</v>
+        <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2687.73</v>
+        <v>3528.05</v>
       </c>
       <c r="H29" s="5">
         <f>ROUND(F29*G29,2)</f>
@@ -1806,7 +1806,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
@@ -1816,24 +1816,24 @@
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F30" s="20" t="n">
-        <v>54.315</v>
+        <v>2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>183.57</v>
+        <v>1079.2</v>
       </c>
       <c r="H30" s="5">
         <f>ROUND(F30*G30,2)</f>
@@ -1843,7 +1843,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
@@ -1867,17 +1867,17 @@
         </is>
       </c>
       <c r="F31" s="20" t="n">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>330.7</v>
+        <v>200</v>
       </c>
       <c r="H31" s="5">
         <f>ROUND(F31*G31,2)</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
+    <row r="32" ht="30" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E32" s="19" t="inlineStr">
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F32" s="20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>7084.16</v>
+        <v>1996.08</v>
       </c>
       <c r="H32" s="5">
         <f>ROUND(F32*G32,2)</f>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E33" s="19" t="inlineStr">
@@ -1941,17 +1941,17 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>3528.05</v>
+        <v>1370.96</v>
       </c>
       <c r="H33" s="5">
         <f>ROUND(F33*G33,2)</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="14" customHeight="1">
+    <row r="34" ht="20" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -1964,24 +1964,24 @@
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1079.2</v>
+        <v>29.06</v>
       </c>
       <c r="H34" s="5">
         <f>ROUND(F34*G34,2)</f>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F35" s="20" t="n">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>200</v>
+        <v>19.5</v>
       </c>
       <c r="H35" s="5">
         <f>ROUND(F35*G35,2)</f>
@@ -2038,24 +2038,24 @@
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F36" s="20" t="n">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1996.08</v>
+        <v>12.22</v>
       </c>
       <c r="H36" s="5">
         <f>ROUND(F36*G36,2)</f>
@@ -2075,31 +2075,31 @@
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F37" s="20" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1370.96</v>
+        <v>157.05</v>
       </c>
       <c r="H37" s="5">
         <f>ROUND(F37*G37,2)</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="14" customHeight="1">
+    <row r="38" ht="20" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2112,12 +2112,12 @@
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
@@ -2126,17 +2126,17 @@
         </is>
       </c>
       <c r="F38" s="20" t="n">
-        <v>500</v>
+        <v>186</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>29.06</v>
+        <v>115.96</v>
       </c>
       <c r="H38" s="5">
         <f>ROUND(F38*G38,2)</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="14" customHeight="1">
+    <row r="39" ht="20" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2149,31 +2149,31 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F39" s="20" t="n">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>19.5</v>
+        <v>15595.61</v>
       </c>
       <c r="H39" s="5">
         <f>ROUND(F39*G39,2)</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
+    <row r="40" ht="20" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2186,12 +2186,12 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
@@ -2200,17 +2200,17 @@
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>600</v>
+        <v>16</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>12.22</v>
+        <v>426.72</v>
       </c>
       <c r="H40" s="5">
         <f>ROUND(F40*G40,2)</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2223,24 +2223,24 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>157.05</v>
+        <v>467349.29</v>
       </c>
       <c r="H41" s="5">
         <f>ROUND(F41*G41,2)</f>
@@ -2260,31 +2260,31 @@
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>115.96</v>
+        <v>79653.55</v>
       </c>
       <c r="H42" s="5">
         <f>ROUND(F42*G42,2)</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
+    <row r="43" ht="20" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2297,31 +2297,31 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>1</v>
+        <v>502</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>15595.61</v>
+        <v>199.42</v>
       </c>
       <c r="H43" s="5">
         <f>ROUND(F43*G43,2)</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
+    <row r="44" ht="30" customHeight="1">
       <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2332,33 +2332,33 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>30.750.2001</t>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>426.72</v>
+        <v>38.72</v>
       </c>
       <c r="H44" s="5">
         <f>ROUND(F44*G44,2)</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2371,31 +2371,31 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>467349.29</v>
+        <v>162.37</v>
       </c>
       <c r="H45" s="5">
         <f>ROUND(F45*G45,2)</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="14" customHeight="1">
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2406,26 +2406,26 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>79653.55</v>
+        <v>21.3</v>
       </c>
       <c r="H46" s="5">
         <f>ROUND(F46*G46,2)</f>
@@ -2445,98 +2445,98 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>30.190.1304</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemi — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>502</v>
+        <v>123</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>199.42</v>
+        <v>233.28</v>
       </c>
       <c r="H47" s="5">
         <f>ROUND(F47*G47,2)</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="14" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>502</v>
+        <v>1684.38</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>38.72</v>
+        <v>52.37</v>
       </c>
       <c r="H48" s="5">
         <f>ROUND(F48*G48,2)</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemi kapak sacı — 1,0 mm sıcak daldırma galvanizli (malzeme)</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>361.2</v>
+        <v>31.429</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>162.37</v>
+        <v>2750.45</v>
       </c>
       <c r="H49" s="5">
         <f>ROUND(F49*G49,2)</f>
@@ -2546,34 +2546,34 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>361.2</v>
+        <v>278.34</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>21.3</v>
+        <v>2960.45</v>
       </c>
       <c r="H50" s="5">
         <f>ROUND(F50*G50,2)</f>
@@ -2583,44 +2583,44 @@
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>30.190.1304</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>123</v>
+        <v>551.26</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>233.28</v>
+        <v>863.8</v>
       </c>
       <c r="H51" s="5">
         <f>ROUND(F51*G51,2)</f>
         <v/>
       </c>
     </row>
-    <row r="52" ht="14" customHeight="1">
+    <row r="52" ht="20" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
@@ -2630,34 +2630,34 @@
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Makine ile kazı yapılması — kümes A ve B blok</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>1684.38</v>
+        <v>4.16</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>52.37</v>
+        <v>39045.24</v>
       </c>
       <c r="H52" s="5">
         <f>ROUND(F52*G52,2)</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="14" customHeight="1">
+    <row r="53" ht="20" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2667,34 +2667,34 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>C 16/20 hazır beton dökülmesi — kümes temel altı grobeton</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>31.429</v>
+        <v>7.288</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>2750.45</v>
+        <v>37532.19</v>
       </c>
       <c r="H53" s="5">
         <f>ROUND(F53*G53,2)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
+    <row r="54" ht="14" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
@@ -2704,24 +2704,24 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes şerit temel ve bağ kirişleri</t>
+          <t>Nervürlü çelik hasırın yerine konulması</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F54" s="20" t="n">
-        <v>115.71</v>
+        <v>3.637</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>2960.45</v>
+        <v>36949.5</v>
       </c>
       <c r="H54" s="5">
         <f>ROUND(F54*G54,2)</f>
@@ -2731,7 +2731,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2741,34 +2741,34 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>C 25/30 hazır beton dökülmesi — kümes zemin döşemeleri (15 cm)</t>
+          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>162.63</v>
+        <v>44.048</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2960.45</v>
+        <v>72192.55</v>
       </c>
       <c r="H55" s="5">
         <f>ROUND(F55*G55,2)</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="14" customHeight="1">
+    <row r="56" ht="20" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı — kümes temelleri</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
@@ -2792,20 +2792,20 @@
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>551.26</v>
+        <v>507.91</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>863.8</v>
+        <v>929.28</v>
       </c>
       <c r="H56" s="5">
         <f>ROUND(F56*G56,2)</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
+    <row r="57" ht="20" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -2815,24 +2815,24 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>Ø8-Ø12 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>4.16</v>
+        <v>49.85</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>39045.24</v>
+        <v>1777.52</v>
       </c>
       <c r="H57" s="5">
         <f>ROUND(F57*G57,2)</f>
@@ -2842,7 +2842,7 @@
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2852,34 +2852,34 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>Ø14-Ø28 nervürlü beton çelik çubuğu — kümes temelleri</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>7.288</v>
+        <v>557.76</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>37532.19</v>
+        <v>372.55</v>
       </c>
       <c r="H58" s="5">
         <f>ROUND(F58*G58,2)</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="14" customHeight="1">
+    <row r="59" ht="20" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,24 +2889,24 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması — kümes döşemeleri</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F59" s="20" t="n">
-        <v>3.637</v>
+        <v>647.76</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>36949.5</v>
+        <v>381.49</v>
       </c>
       <c r="H59" s="5">
         <f>ROUND(F59*G59,2)</f>
@@ -2916,7 +2916,7 @@
     <row r="60" ht="20" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,24 +2926,24 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti — kümes çelik taşıyıcı sistemi</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>44.048</v>
+        <v>557.76</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>72192.55</v>
+        <v>324.27</v>
       </c>
       <c r="H60" s="5">
         <f>ROUND(F60*G60,2)</f>
@@ -2953,7 +2953,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile) — cephe duvarı</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -2977,10 +2977,10 @@
         </is>
       </c>
       <c r="F61" s="20" t="n">
-        <v>507.91</v>
+        <v>612.76</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>929.28</v>
+        <v>248.75</v>
       </c>
       <c r="H61" s="5">
         <f>ROUND(F61*G61,2)</f>
@@ -2990,7 +2990,7 @@
     <row r="62" ht="20" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -3000,34 +3000,34 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması — boşluk üstü lento ve yatay hatıl</t>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>49.85</v>
+        <v>674</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1777.52</v>
+        <v>147.67</v>
       </c>
       <c r="H62" s="5">
         <f>ROUND(F62*G62,2)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
+    <row r="63" ht="14" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,24 +3037,24 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması — cephe duvarı dış yüzü</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>557.76</v>
+        <v>319.2</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>372.55</v>
+        <v>227.85</v>
       </c>
       <c r="H63" s="5">
         <f>ROUND(F63*G63,2)</f>
@@ -3064,7 +3064,7 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -3074,34 +3074,34 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe) — cephe duvarı iç yüzü</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>557.76</v>
+        <v>51.2</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>381.49</v>
+        <v>174.22</v>
       </c>
       <c r="H64" s="5">
         <f>ROUND(F64*G64,2)</f>
         <v/>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
+    <row r="65" ht="30" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>557.76</v>
+        <v>13.4</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>324.27</v>
+        <v>870.14</v>
       </c>
       <c r="H65" s="5">
         <f>ROUND(F65*G65,2)</f>
@@ -3138,7 +3138,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
@@ -3162,20 +3162,20 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>557.76</v>
+        <v>45</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>248.75</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H66" s="5">
         <f>ROUND(F66*G66,2)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
+    <row r="67" ht="40" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3185,34 +3185,34 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden mahya, saçak ve köşe kapama profilleri</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>674</v>
+        <v>60</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>147.67</v>
+        <v>701.48</v>
       </c>
       <c r="H67" s="5">
         <f>ROUND(F67*G67,2)</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="14" customHeight="1">
+    <row r="68" ht="30" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3222,34 +3222,34 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu yapılması — dere</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>319.2</v>
+        <v>5.67</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>227.85</v>
+        <v>2687.73</v>
       </c>
       <c r="H68" s="5">
         <f>ROUND(F68*G68,2)</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="14" customHeight="1">
+    <row r="69" ht="20" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,24 +3259,24 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>Ø70 sert PVC yağmur suyu iniş borusu temini ve yerine tesbiti</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>51.2</v>
+        <v>54.315</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>174.22</v>
+        <v>183.57</v>
       </c>
       <c r="H69" s="5">
         <f>ROUND(F69*G69,2)</f>
@@ -3286,7 +3286,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — kümes servis kapısı 100/220</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>4.4</v>
+        <v>25</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>870.14</v>
+        <v>330.7</v>
       </c>
       <c r="H70" s="5">
         <f>ROUND(F70*G70,2)</f>
@@ -3323,7 +3323,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -3333,24 +3333,24 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>30.100.2105</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu panel ile ısı yalıtımlı kapı yapılması — yükleme/temizlik kapısı 300/300 sürgülü</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>870.14</v>
+        <v>7084.16</v>
       </c>
       <c r="H71" s="5">
         <f>ROUND(F71*G71,2)</f>
@@ -3360,7 +3360,7 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>30.110.1102</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile bölme duvar yapılması — servis bölümü</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>3528.05</v>
       </c>
       <c r="H72" s="5">
         <f>ROUND(F72*G72,2)</f>
@@ -3397,7 +3397,7 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -3407,24 +3407,24 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>30.115.1003</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması — servis bölümü bölme duvarları</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>381.49</v>
+        <v>1079.2</v>
       </c>
       <c r="H73" s="5">
         <f>ROUND(F73*G73,2)</f>
@@ -3434,7 +3434,7 @@
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
@@ -3444,34 +3444,34 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>30.140.3104</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>Duvar karosu ile 3 mm derz aralıklı döşeme ve duvar kaplaması yapılması — servis bölümü</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>701.48</v>
+        <v>200</v>
       </c>
       <c r="H74" s="5">
         <f>ROUND(F74*G74,2)</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
+    <row r="75" ht="30" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -3481,24 +3481,24 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>30.170.1602</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel boya — servis bölümü</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>248.75</v>
+        <v>1996.08</v>
       </c>
       <c r="H75" s="5">
         <f>ROUND(F75*G75,2)</f>
@@ -3508,7 +3508,7 @@
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B76" s="17" t="inlineStr">
@@ -3518,24 +3518,24 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>30.170.1601</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı yapılması, yerinde takılması — servis bölümü</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>5.67</v>
+        <v>2</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>2687.73</v>
+        <v>1370.96</v>
       </c>
       <c r="H76" s="5">
         <f>ROUND(F76*G76,2)</f>
@@ -3545,7 +3545,7 @@
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B77" s="17" t="inlineStr">
@@ -3555,24 +3555,24 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>30.160.6102</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm sacdan bükme kapı kasası yapılması ve yerine konulması — servis bölümü iç kapıları</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F77" s="20" t="n">
-        <v>54.315</v>
+        <v>500</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>183.57</v>
+        <v>29.06</v>
       </c>
       <c r="H77" s="5">
         <f>ROUND(F77*G77,2)</f>
@@ -3582,7 +3582,7 @@
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B78" s="17" t="inlineStr">
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>30.150.1402</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>ø150 HDPE koruge boru ile pissu hattı döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="F78" s="20" t="n">
-        <v>25</v>
+        <v>2000</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>330.7</v>
+        <v>19.5</v>
       </c>
       <c r="H78" s="5">
         <f>ROUND(F78*G78,2)</f>
@@ -3629,24 +3629,24 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>30.150.1401</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F79" s="20" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>7084.16</v>
+        <v>12.22</v>
       </c>
       <c r="H79" s="5">
         <f>ROUND(F79*G79,2)</f>
@@ -3666,31 +3666,31 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>30.140.1105</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>3528.05</v>
+        <v>157.05</v>
       </c>
       <c r="H80" s="5">
         <f>ROUND(F80*G80,2)</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="14" customHeight="1">
+    <row r="81" ht="20" customHeight="1">
       <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3703,24 +3703,24 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>30.750.3002</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F81" s="20" t="n">
-        <v>2</v>
+        <v>186</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1079.2</v>
+        <v>115.96</v>
       </c>
       <c r="H81" s="5">
         <f>ROUND(F81*G81,2)</f>
@@ -3740,24 +3740,24 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>30.750.1502</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm²</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F82" s="20" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>200</v>
+        <v>15595.61</v>
       </c>
       <c r="H82" s="5">
         <f>ROUND(F82*G82,2)</f>
@@ -3777,31 +3777,31 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>30.750.2001</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F83" s="20" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>1996.08</v>
+        <v>426.72</v>
       </c>
       <c r="H83" s="5">
         <f>ROUND(F83*G83,2)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="20" customHeight="1">
+    <row r="84" ht="30" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>30.740.1106</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
@@ -3828,17 +3828,17 @@
         </is>
       </c>
       <c r="F84" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>1370.96</v>
+        <v>467349.29</v>
       </c>
       <c r="H84" s="5">
         <f>ROUND(F84*G84,2)</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="14" customHeight="1">
+    <row r="85" ht="20" customHeight="1">
       <c r="A85" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3851,31 +3851,31 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>30.740.5406</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F85" s="20" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>29.06</v>
+        <v>79653.55</v>
       </c>
       <c r="H85" s="5">
         <f>ROUND(F85*G85,2)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="14" customHeight="1">
+    <row r="86" ht="20" customHeight="1">
       <c r="A86" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3888,31 +3888,31 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F86" s="20" t="n">
-        <v>2000</v>
+        <v>502</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>19.5</v>
+        <v>199.42</v>
       </c>
       <c r="H86" s="5">
         <f>ROUND(F86*G86,2)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="14" customHeight="1">
+    <row r="87" ht="30" customHeight="1">
       <c r="A87" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3923,33 +3923,33 @@
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C87" s="18" t="inlineStr">
-        <is>
-          <t>30.150.1401</t>
+      <c r="C87" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F87" s="20" t="n">
-        <v>600</v>
+        <v>502</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>12.22</v>
+        <v>38.72</v>
       </c>
       <c r="H87" s="5">
         <f>ROUND(F87*G87,2)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
+    <row r="88" ht="30" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3962,31 +3962,31 @@
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F88" s="20" t="n">
-        <v>100</v>
+        <v>361.2</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>157.05</v>
+        <v>162.37</v>
       </c>
       <c r="H88" s="5">
         <f>ROUND(F88*G88,2)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
+    <row r="89" ht="30" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3997,33 +3997,33 @@
           <t>Kümes B Blok</t>
         </is>
       </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>30.750.3002</t>
+      <c r="C89" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması)</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F89" s="20" t="n">
-        <v>186</v>
+        <v>361.2</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>115.96</v>
+        <v>21.3</v>
       </c>
       <c r="H89" s="5">
         <f>ROUND(F89*G89,2)</f>
         <v/>
       </c>
     </row>
-    <row r="90" ht="14" customHeight="1">
+    <row r="90" ht="20" customHeight="1">
       <c r="A90" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -4036,340 +4036,44 @@
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>30.190.1304</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F90" s="20" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>15595.61</v>
+        <v>233.28</v>
       </c>
       <c r="H90" s="5">
         <f>ROUND(F90*G90,2)</f>
         <v/>
       </c>
     </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C91" s="18" t="inlineStr">
-        <is>
-          <t>30.750.2001</t>
-        </is>
-      </c>
-      <c r="D91" s="16" t="inlineStr">
-        <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel</t>
-        </is>
-      </c>
-      <c r="E91" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F91" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>426.72</v>
-      </c>
-      <c r="H91" s="5">
-        <f>ROUND(F91*G91,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="inlineStr">
-        <is>
-          <t>30.740.1106</t>
-        </is>
-      </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak</t>
-        </is>
-      </c>
-      <c r="E92" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F92" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>467349.29</v>
-      </c>
-      <c r="H92" s="5">
-        <f>ROUND(F92*G92,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="14" customHeight="1">
-      <c r="A93" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C93" s="18" t="inlineStr">
-        <is>
-          <t>30.740.5406</t>
-        </is>
-      </c>
-      <c r="D93" s="16" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA</t>
-        </is>
-      </c>
-      <c r="E93" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F93" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>79653.55</v>
-      </c>
-      <c r="H93" s="5">
-        <f>ROUND(F93*G93,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
-        </is>
-      </c>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemi — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme)</t>
-        </is>
-      </c>
-      <c r="E94" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F94" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>199.42</v>
-      </c>
-      <c r="H94" s="5">
-        <f>ROUND(F94*G94,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C95" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="D95" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="E95" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F95" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="H95" s="5">
-        <f>ROUND(F95*G95,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C96" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemi kapak sacı — 1,0 mm sıcak daldırma galvanizli (malzeme)</t>
-        </is>
-      </c>
-      <c r="E96" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F96" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>162.37</v>
-      </c>
-      <c r="H96" s="5">
-        <f>ROUND(F96*G96,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B97" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C97" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="D97" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="E97" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F97" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H97" s="5">
-        <f>ROUND(F97*G97,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="14" customHeight="1">
-      <c r="A98" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C98" s="18" t="inlineStr">
-        <is>
-          <t>30.190.1304</t>
-        </is>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli</t>
-        </is>
-      </c>
-      <c r="E98" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F98" s="20" t="n">
-        <v>123</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>233.28</v>
-      </c>
-      <c r="H98" s="5">
-        <f>ROUND(F98*G98,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="21" t="n"/>
-      <c r="B99" s="21" t="n"/>
-      <c r="C99" s="21" t="n"/>
-      <c r="D99" s="22" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="21" t="n"/>
+      <c r="B91" s="21" t="n"/>
+      <c r="C91" s="21" t="n"/>
+      <c r="D91" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E99" s="21" t="n"/>
-      <c r="F99" s="21" t="n"/>
-      <c r="G99" s="21" t="n"/>
-      <c r="H99" s="9">
-        <f>SUM(H5:H98)</f>
+      <c r="E91" s="21" t="n"/>
+      <c r="F91" s="21" t="n"/>
+      <c r="G91" s="21" t="n"/>
+      <c r="H91" s="9">
+        <f>SUM(H5:H90)</f>
         <v/>
       </c>
     </row>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="F5" s="20" t="n">
-        <v>1684.39</v>
+        <v>1684.385</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>52.37</v>
@@ -1177,7 +1177,7 @@
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
@@ -1187,24 +1187,24 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
-        <v>507.91</v>
+        <v>674</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>929.28</v>
+        <v>147.67</v>
       </c>
       <c r="H13" s="5">
         <f>ROUND(F13*G13,2)</f>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
@@ -1238,20 +1238,20 @@
         </is>
       </c>
       <c r="F14" s="20" t="n">
-        <v>49.85</v>
+        <v>507.91</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1777.52</v>
+        <v>929.28</v>
       </c>
       <c r="H14" s="5">
         <f>ROUND(F14*G14,2)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="14" customHeight="1">
+    <row r="15" ht="20" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>557.76</v>
+        <v>49.85</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>372.55</v>
+        <v>1777.52</v>
       </c>
       <c r="H15" s="5">
         <f>ROUND(F15*G15,2)</f>
@@ -1288,7 +1288,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -1312,20 +1312,20 @@
         </is>
       </c>
       <c r="F16" s="20" t="n">
-        <v>647.76</v>
+        <v>45</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>381.49</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H16" s="5">
         <f>ROUND(F16*G16,2)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
+    <row r="17" ht="14" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
@@ -1335,24 +1335,24 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F17" s="20" t="n">
-        <v>557.76</v>
+        <v>319.2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>324.27</v>
+        <v>227.85</v>
       </c>
       <c r="H17" s="5">
         <f>ROUND(F17*G17,2)</f>
@@ -1362,7 +1362,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
@@ -1372,34 +1372,34 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F18" s="20" t="n">
-        <v>612.76</v>
+        <v>51.2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>248.75</v>
+        <v>174.22</v>
       </c>
       <c r="H18" s="5">
         <f>ROUND(F18*G18,2)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
@@ -1409,34 +1409,34 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F19" s="20" t="n">
-        <v>674</v>
+        <v>13.4</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>147.67</v>
+        <v>870.14</v>
       </c>
       <c r="H19" s="5">
         <f>ROUND(F19*G19,2)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="14" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
@@ -1446,24 +1446,24 @@
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F20" s="20" t="n">
-        <v>319.2</v>
+        <v>5.67</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>227.85</v>
+        <v>2687.73</v>
       </c>
       <c r="H20" s="5">
         <f>ROUND(F20*G20,2)</f>
@@ -1473,7 +1473,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
@@ -1483,34 +1483,34 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>51.2</v>
+        <v>54.315</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>174.22</v>
+        <v>183.57</v>
       </c>
       <c r="H21" s="5">
         <f>ROUND(F21*G21,2)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="14" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="E22" s="19" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="F22" s="20" t="n">
-        <v>13.4</v>
+        <v>557.76</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>870.14</v>
+        <v>372.55</v>
       </c>
       <c r="H22" s="5">
         <f>ROUND(F22*G22,2)</f>
@@ -1547,7 +1547,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
@@ -1571,20 +1571,20 @@
         </is>
       </c>
       <c r="F23" s="20" t="n">
-        <v>45</v>
+        <v>647.76</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>381.49</v>
       </c>
       <c r="H23" s="5">
         <f>ROUND(F23*G23,2)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="40" customHeight="1">
+    <row r="24" ht="20" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="C24" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E24" s="19" t="inlineStr">
@@ -1608,20 +1608,20 @@
         </is>
       </c>
       <c r="F24" s="20" t="n">
-        <v>60</v>
+        <v>557.76</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>701.48</v>
+        <v>324.27</v>
       </c>
       <c r="H24" s="5">
         <f>ROUND(F24*G24,2)</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
+    <row r="25" ht="20" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E25" s="19" t="inlineStr">
@@ -1645,20 +1645,20 @@
         </is>
       </c>
       <c r="F25" s="20" t="n">
-        <v>5.67</v>
+        <v>612.76</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>2687.73</v>
+        <v>248.75</v>
       </c>
       <c r="H25" s="5">
         <f>ROUND(F25*G25,2)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26" ht="40" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
@@ -1668,24 +1668,24 @@
       </c>
       <c r="C26" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="E26" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F26" s="20" t="n">
-        <v>54.315</v>
+        <v>60</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>183.57</v>
+        <v>701.48</v>
       </c>
       <c r="H26" s="5">
         <f>ROUND(F26*G26,2)</f>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>1684.38</v>
+        <v>1684.385</v>
       </c>
       <c r="G48" s="5" t="n">
         <v>52.37</v>
@@ -2768,7 +2768,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>507.91</v>
+        <v>674</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>929.28</v>
+        <v>147.67</v>
       </c>
       <c r="H56" s="5">
         <f>ROUND(F56*G56,2)</f>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
@@ -2829,20 +2829,20 @@
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>49.85</v>
+        <v>507.91</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1777.52</v>
+        <v>929.28</v>
       </c>
       <c r="H57" s="5">
         <f>ROUND(F57*G57,2)</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="14" customHeight="1">
+    <row r="58" ht="20" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>557.76</v>
+        <v>49.85</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>372.55</v>
+        <v>1777.52</v>
       </c>
       <c r="H58" s="5">
         <f>ROUND(F58*G58,2)</f>
@@ -2879,7 +2879,7 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
@@ -2903,20 +2903,20 @@
         </is>
       </c>
       <c r="F59" s="20" t="n">
-        <v>647.76</v>
+        <v>45</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>381.49</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H59" s="5">
         <f>ROUND(F59*G59,2)</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
+    <row r="60" ht="14" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,24 +2926,24 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>557.76</v>
+        <v>319.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>324.27</v>
+        <v>227.85</v>
       </c>
       <c r="H60" s="5">
         <f>ROUND(F60*G60,2)</f>
@@ -2953,7 +2953,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,34 +2963,34 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F61" s="20" t="n">
-        <v>612.76</v>
+        <v>51.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>248.75</v>
+        <v>174.22</v>
       </c>
       <c r="H61" s="5">
         <f>ROUND(F61*G61,2)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
+    <row r="62" ht="30" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -3000,34 +3000,34 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>674</v>
+        <v>13.4</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>147.67</v>
+        <v>870.14</v>
       </c>
       <c r="H62" s="5">
         <f>ROUND(F62*G62,2)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="14" customHeight="1">
+    <row r="63" ht="30" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,24 +3037,24 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>319.2</v>
+        <v>5.67</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>227.85</v>
+        <v>2687.73</v>
       </c>
       <c r="H63" s="5">
         <f>ROUND(F63*G63,2)</f>
@@ -3064,7 +3064,7 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -3074,34 +3074,34 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>51.2</v>
+        <v>54.315</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>174.22</v>
+        <v>183.57</v>
       </c>
       <c r="H64" s="5">
         <f>ROUND(F64*G64,2)</f>
         <v/>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
+    <row r="65" ht="14" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3125,10 +3125,10 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>13.4</v>
+        <v>557.76</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>870.14</v>
+        <v>372.55</v>
       </c>
       <c r="H65" s="5">
         <f>ROUND(F65*G65,2)</f>
@@ -3138,7 +3138,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
@@ -3162,20 +3162,20 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>45</v>
+        <v>647.76</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>381.49</v>
       </c>
       <c r="H66" s="5">
         <f>ROUND(F66*G66,2)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="40" customHeight="1">
+    <row r="67" ht="20" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3199,20 +3199,20 @@
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>60</v>
+        <v>557.76</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>701.48</v>
+        <v>324.27</v>
       </c>
       <c r="H67" s="5">
         <f>ROUND(F67*G67,2)</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
+    <row r="68" ht="20" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
@@ -3236,20 +3236,20 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>5.67</v>
+        <v>612.76</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>2687.73</v>
+        <v>248.75</v>
       </c>
       <c r="H68" s="5">
         <f>ROUND(F68*G68,2)</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
+    <row r="69" ht="40" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,24 +3259,24 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>54.315</v>
+        <v>60</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>183.57</v>
+        <v>701.48</v>
       </c>
       <c r="H69" s="5">
         <f>ROUND(F69*G69,2)</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>'A3.4-EK Makine-Ekipman'!G21</f>
+        <f>'A3.4-EK Makine-Ekipman'!G13</f>
         <v/>
       </c>
       <c r="C13" s="6">
@@ -4257,15 +4257,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -4297,22 +4297,22 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Ürün adı</t>
+          <t>Ürün kodu</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Birim</t>
+          <t>Makine-ekipmanın adı ve teknik özeti</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Miktar</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Birim fiyat (TL)</t>
+          <t>Bina başına (TL)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -4321,7 +4321,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
@@ -4330,28 +4330,28 @@
       <c r="B5" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Yemlik depo motor grubu (170 kg yem deposu, milli yemlik motoru, yemlik hat sonu, elektrik kutusu ile)</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="n">
-        <v>6</v>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>HZC-FD-01</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Yemleme sistemi — 3 hat, 243 m hat uzunluğu, 150 kg galvanizli yem deposu x 3, 0,55 kW yemlik motoru x 3, 35 cm çapında 324 plastik yemlik, 1,1 kW çift redüktörlü frenli otomatik kaldırma</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>22000</v>
+        <v>250062.04</v>
       </c>
       <c r="G5" s="5">
         <f>ROUND(E5*F5,2)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="14" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
@@ -4360,21 +4360,21 @@
       <c r="B6" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>Spiral yemleme sistemi (yemlik boru, yemlik tabağı, yay, boru kelepçesi)</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>468</v>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>HZC-COM-004</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Kümes kontrol panosu — HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>510</v>
+        <v>262674.92</v>
       </c>
       <c r="G6" s="5">
         <f>ROUND(E6*F6,2)</f>
@@ -4390,28 +4390,28 @@
       <c r="B7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>15'li nipel sulama sistemi (20 cm'de bir krom nipelli boru, nipel çanağı, muf ve muf teli ile)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>624</v>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>HZC-WNT-012</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Tünel havalandırma fanı — 4 adet, 138 x 138 x 42 cm, 40.000 m³/h, 1,5 kW, galvanizli çelik kanat, ahtapot sistemli otomatik panjur</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>285</v>
+        <v>76982.48</v>
       </c>
       <c r="G7" s="5">
         <f>ROUND(E7*F7,2)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="14" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
@@ -4420,28 +4420,28 @@
       <c r="B8" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>Regülatör takımı</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>8</v>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>HZC-WTR-005</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Sulama sistemi — 4 hat, hat başına 312 m, 22 x 22 mm hat çapı, 1.560 metal 360° nipel suluk, 4 regülatör, 0,75 kW çift redüktörlü frenli otomatik kaldırma</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1800</v>
+        <v>145353.3</v>
       </c>
       <c r="G8" s="5">
         <f>ROUND(E8*F8,2)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
@@ -4450,21 +4450,21 @@
       <c r="B9" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>Yemlik ve suluk kaldırma sistemi (6 ve 5 mm halat, sarı ve beyaz ip, klemens, plastik makara, askı saçı, bilyalı makara)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>1260</v>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>HZC-WNT-024</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Soğutma pedi sistemi — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, 2 x 15 m uzunluk (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>55</v>
+        <v>269272.63</v>
       </c>
       <c r="G9" s="5">
         <f>ROUND(E9*F9,2)</f>
@@ -4480,21 +4480,21 @@
       <c r="B10" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Yemlik motorlu kaldırma sistemi (1,1 kW çift redüktörlü frenli kaldırma motoru, mafsal 50'lik boru, UCP bilya, kontrol panosu dâhil)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="n">
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>HZC-WNT-001</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Klape sistemi — 40 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h, 2 aktüatörlü açma-kapama, 161 m hat</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>50000</v>
+        <v>40581.31</v>
       </c>
       <c r="G10" s="5">
         <f>ROUND(E10*F10,2)</f>
@@ -4510,21 +4510,21 @@
       <c r="B11" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>Nipel motorlu kaldırma sistemi (0,75 kW çift redüktörlü frenli kaldırma motoru, mafsal 50'lik boru, UCP bilya, kontrol panosu dâhil)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="n">
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>HZC-SLO-004</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Yem silosu ve nakil sistemi — En az 17,77 ton galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>50000</v>
+        <v>172996.93</v>
       </c>
       <c r="G11" s="5">
         <f>ROUND(E11*F11,2)</f>
@@ -4538,282 +4538,42 @@
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>140 x 140 cm tünel havalandırma fanı</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Montaj ve nakliye — Kümes montajı ve nakliye bedelleri</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>2</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>25500</v>
+        <v>225000</v>
       </c>
       <c r="G12" s="5">
         <f>ROUND(E12*F12,2)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Makine ve ekipman alımı</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>3 makaralı klape (hava giriş kapağı)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="G13" s="5">
-        <f>ROUND(E13*F13,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Makine ve ekipman alımı</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Klape açma sistemi</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G14" s="5">
-        <f>ROUND(E14*F14,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>Makine ve ekipman alımı</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>7 inç dokunmatik ekran kümes kontrol panosu (uzaktan erişim, karbondioksit, nem ve basınç sensörü, 5 ısı sensörü dâhil)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>210000</v>
-      </c>
-      <c r="G15" s="5">
-        <f>ROUND(E15*F15,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Makine ve ekipman alımı</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>15 m x 1,5 m x 15 cm PVC çerçeveli, kendinden depolu ve su pompalı tüp ped (serinletme) sistemi</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>45.72</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G16" s="5">
-        <f>ROUND(E16*F16,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Makine ve ekipman alımı</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Ped kapağı açma sistemi</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G17" s="5">
-        <f>ROUND(E17*F17,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Makine ve ekipman alımı</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>110 x 150 cm ped kapağı</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G18" s="5">
-        <f>ROUND(E18*F18,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Makine ve ekipman alımı</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>18 ton galvaniz yem silosu ve alt grubu</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>155000</v>
-      </c>
-      <c r="G19" s="5">
-        <f>ROUND(E19*F19,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="14" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Makine ve ekipman alımı</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>İşçilik ve nakliye</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>tk</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>250000</v>
-      </c>
-      <c r="G20" s="5">
-        <f>ROUND(E20*F20,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n"/>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="22" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>MAKİNE-EKİPMAN TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="21" t="n"/>
-      <c r="G21" s="9">
-        <f>SUM(G5:G20)</f>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="9">
+        <f>SUM(G5:G12)</f>
         <v/>
       </c>
     </row>
@@ -7174,7 +6934,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24974467.25</v>
+        <v>24988354.46</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7231,7 +6991,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>2871960</v>
+        <v>2885847.21</v>
       </c>
       <c r="C8" s="6">
         <f>B8/52.7585</f>
@@ -7269,7 +7029,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9200012.75</v>
+        <v>9213899.960000001</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7307,7 +7067,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4994893.45</v>
+        <v>4997670.89</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Diğer altı yapı ve iki bloktan çıkarılan pozlar — proforma ile beyan</t>
+          <t>Diğer 7 yapı ve iki bloktan çıkarılan pozlar — proforma ile beyan</t>
         </is>
       </c>
     </row>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -4471,7 +4471,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Klape sistemi — 40 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h, 2 aktüatörlü açma-kapama, 161 m hat</t>
+          <t>Klape sistemi — 30 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h (30 x 1.750 = 52.500 m³/h, mekanik projedeki 46.717 m³/h ihtiyacının üzerinde), 2 aktüatörlü açma-kapama, 161 m hat</t>
         </is>
       </c>
       <c r="E10" s="19" t="n">

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>'A3.4-EK Yapım'!H56</f>
+        <f>'A3.4-EK Yapım'!H72</f>
         <v/>
       </c>
       <c r="C12" s="6">
@@ -4591,7 +4591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4614,7 +4614,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kümes A ve B blokları dışındaki yapılar ile bu iki bloktan hibe kapsamı dışına çıkarılan pozlar. Bu imalatlar yapılmaya devam eder; teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir ve tamamı öz kaynaktan karşılanır. Birim fiyatlar, hibe kapsamındaki işlerle aynı esasa göre kurulmuştur: ÇŞB 2026 ve TKDK 17.02.2026 kitap fiyatlarına %16 tenzilat uygulanmıştır.</t>
+          <t>Kümes A ve B blokları dışındaki yapılar ile bu iki bloktan hibe kapsamı dışına çıkarılan pozlar. Bu imalatlar yapılmaya devam eder; teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir ve tamamı öz kaynaktan karşılanır. Birim fiyatlar, hibe kapsamındaki işlerle aynı esasa göre kurulmuştur: ÇŞB 2026 ve TKDK 17.02.2026 kitap fiyatlarına %16 tenzilat uygulanmıştır. Sayfanın sonundaki SIHHİ TESİSAT bölümü keşif özetinde yer almaz: miktarları onaylı sıhhi tesisat projesinden, birim fiyatları piyasa araştırmasından gelir; kitap fiyatı olmadığı için o kalemlere tenzilat uygulanmaz. Bu sayfa 36 numaralı proforma ile kuruşu kuruşuna aynıdır.</t>
         </is>
       </c>
     </row>
@@ -6548,25 +6548,588 @@
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="21" t="n"/>
-      <c r="B56" s="21" t="n"/>
-      <c r="C56" s="21" t="n"/>
-      <c r="D56" s="22" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>SIHHİ TESİSAT — keşif özetinde yer almaz; miktarlar onaylı sıhhi tesisat projesinden, birim fiyatlar piyasa araştırmasından (kitap fiyatı olmadığı için %16 tenzilat uygulanmaz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, 1/2" - 1 1/4" kolon ve kat tesisatı, küresel vanalar, boru askı ve kılıfları (kolon şemasına göre)</t>
+        </is>
+      </c>
+      <c r="E57" s="19" t="inlineStr">
+        <is>
+          <t>tk</t>
+        </is>
+      </c>
+      <c r="F57" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H57" s="5">
+        <f>ROUND(F57*G57,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, kolon ve yatay hatlar, temizleme kapakları, yer süzgeçleri</t>
+        </is>
+      </c>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t>tk</t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H58" s="5">
+        <f>ROUND(F58*G58,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>Vitrifiye ve armatür grubu — lavabo, klozet, alaturka hela taşı, duş teknesi, evye, pisuvar ve bataryaları (servis bölümü)</t>
+        </is>
+      </c>
+      <c r="E59" s="19" t="inlineStr">
+        <is>
+          <t>tk</t>
+        </is>
+      </c>
+      <c r="F59" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H59" s="5">
+        <f>ROUND(F59*G59,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
+        </is>
+      </c>
+      <c r="E60" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F60" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H60" s="5">
+        <f>ROUND(F60*G60,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, 1/2" - 1 1/4" kolon ve kat tesisatı, küresel vanalar, boru askı ve kılıfları (kolon şemasına göre)</t>
+        </is>
+      </c>
+      <c r="E61" s="19" t="inlineStr">
+        <is>
+          <t>tk</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H61" s="5">
+        <f>ROUND(F61*G61,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, kolon ve yatay hatlar, temizleme kapakları, yer süzgeçleri</t>
+        </is>
+      </c>
+      <c r="E62" s="19" t="inlineStr">
+        <is>
+          <t>tk</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H62" s="5">
+        <f>ROUND(F62*G62,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>Vitrifiye ve armatür grubu — lavabo, klozet, alaturka hela taşı, duş teknesi, evye, pisuvar ve bataryaları (servis bölümü)</t>
+        </is>
+      </c>
+      <c r="E63" s="19" t="inlineStr">
+        <is>
+          <t>tk</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H63" s="5">
+        <f>ROUND(F63*G63,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
+        </is>
+      </c>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F64" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H64" s="5">
+        <f>ROUND(F64*G64,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C65" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>Şebeke su bağlantısı ve 2" su sayacı — temiz su girişi 80 YB</t>
+        </is>
+      </c>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F65" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>26000</v>
+      </c>
+      <c r="H65" s="5">
+        <f>ROUND(F65*G65,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>Hidrofor — Q = 2 m³/h, P = 33-38 mSS</t>
+        </is>
+      </c>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F66" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H66" s="5">
+        <f>ROUND(F66*G66,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C67" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>Tesisat hidroforu — 0,3 m³/h, 30 mSS (3A)</t>
+        </is>
+      </c>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F67" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H67" s="5">
+        <f>ROUND(F67*G67,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>Modüler galvaniz su deposu — 3 ton (3A)</t>
+        </is>
+      </c>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>36000</v>
+      </c>
+      <c r="H68" s="5">
+        <f>ROUND(F68*G68,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>Yağmur suyu geri kazanım deposu — modüler galvaniz 10 ton, 1,08 x 1,08 x 2,66 m</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F69" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>88000</v>
+      </c>
+      <c r="H69" s="5">
+        <f>ROUND(F69*G69,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t>Yağmur suyu geri kazanım donanımı — pislik tutucu ve emiş filtresi, akış yavaşlatıcı, taşkan sifonu (4 m³/h), tam otomatik kum filtresi DN160, su sayacı ve otomatik kontrol</t>
+        </is>
+      </c>
+      <c r="E70" s="19" t="inlineStr">
+        <is>
+          <t>tk</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>125000</v>
+      </c>
+      <c r="H70" s="5">
+        <f>ROUND(F70*G70,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="inlineStr">
+        <is>
+          <t>Bahçe sulama pompası — 0,5 m³/h, 40 mSS, 0,5 kW</t>
+        </is>
+      </c>
+      <c r="E71" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F71" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>16000</v>
+      </c>
+      <c r="H71" s="5">
+        <f>ROUND(F71*G71,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="n"/>
+      <c r="B72" s="21" t="n"/>
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="22" t="inlineStr">
         <is>
           <t>HİBE DIŞI YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E56" s="21" t="n"/>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="n"/>
-      <c r="H56" s="9">
-        <f>SUM(H5:H55)</f>
+      <c r="E72" s="21" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="9">
+        <f>SUM(H5:H71)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6934,7 +7497,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>24988354.46</v>
+        <v>25586354.46</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -6972,7 +7535,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5618052.75</v>
+        <v>6216052.75</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7029,7 +7592,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9213899.960000001</v>
+        <v>9811899.960000001</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7067,7 +7630,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4997670.89</v>
+        <v>5117270.89</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>'A3.4-EK Yapım'!H72</f>
+        <f>'A3.4-EK Yapım'!H66</f>
         <v/>
       </c>
       <c r="C12" s="6">
@@ -4591,7 +4591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6647,26 +6647,26 @@
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>Vitrifiye ve armatür grubu — lavabo, klozet, alaturka hela taşı, duş teknesi, evye, pisuvar ve bataryaları (servis bölümü)</t>
+          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>tk</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F59" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>42000</v>
+        <v>13000</v>
       </c>
       <c r="H59" s="5">
         <f>ROUND(F59*G59,2)</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
+    <row r="60" ht="30" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
           <t>Sıhhi tesisat</t>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C60" s="19" t="inlineStr">
@@ -6684,26 +6684,26 @@
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
+          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, 1/2" - 1 1/4" kolon ve kat tesisatı, küresel vanalar, boru askı ve kılıfları (kolon şemasına göre)</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>tk</t>
         </is>
       </c>
       <c r="F60" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>13000</v>
+        <v>38000</v>
       </c>
       <c r="H60" s="5">
         <f>ROUND(F60*G60,2)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
+    <row r="61" ht="20" customHeight="1">
       <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Sıhhi tesisat</t>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, 1/2" - 1 1/4" kolon ve kat tesisatı, küresel vanalar, boru askı ve kılıfları (kolon şemasına göre)</t>
+          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, kolon ve yatay hatlar, temizleme kapakları, yer süzgeçleri</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
@@ -6733,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>38000</v>
+        <v>27000</v>
       </c>
       <c r="H61" s="5">
         <f>ROUND(F61*G61,2)</f>
@@ -6758,26 +6758,26 @@
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, kolon ve yatay hatlar, temizleme kapakları, yer süzgeçleri</t>
+          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>tk</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F62" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>27000</v>
+        <v>13000</v>
       </c>
       <c r="H62" s="5">
         <f>ROUND(F62*G62,2)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
+    <row r="63" ht="14" customHeight="1">
       <c r="A63" s="17" t="inlineStr">
         <is>
           <t>Sıhhi tesisat</t>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
         </is>
       </c>
       <c r="C63" s="19" t="inlineStr">
@@ -6795,26 +6795,26 @@
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>Vitrifiye ve armatür grubu — lavabo, klozet, alaturka hela taşı, duş teknesi, evye, pisuvar ve bataryaları (servis bölümü)</t>
+          <t>Şebeke su bağlantısı ve 2" su sayacı — temiz su girişi 80 YB</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
         <is>
-          <t>tk</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F63" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>42000</v>
+        <v>26000</v>
       </c>
       <c r="H63" s="5">
         <f>ROUND(F63*G63,2)</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
+    <row r="64" ht="14" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
         <is>
           <t>Sıhhi tesisat</t>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
         </is>
       </c>
       <c r="C64" s="19" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
+          <t>Hidrofor — Q = 2 m³/h, P = 33-38 mSS</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
@@ -6844,7 +6844,7 @@
         <v>1</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>13000</v>
+        <v>48000</v>
       </c>
       <c r="H64" s="5">
         <f>ROUND(F64*G64,2)</f>
@@ -6869,7 +6869,7 @@
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>Şebeke su bağlantısı ve 2" su sayacı — temiz su girişi 80 YB</t>
+          <t>Tesisat hidroforu — 0,3 m³/h, 30 mSS (3A)</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -6881,249 +6881,27 @@
         <v>1</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>26000</v>
+        <v>19000</v>
       </c>
       <c r="H65" s="5">
         <f>ROUND(F65*G65,2)</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B66" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C66" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>Hidrofor — Q = 2 m³/h, P = 33-38 mSS</t>
-        </is>
-      </c>
-      <c r="E66" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F66" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>48000</v>
-      </c>
-      <c r="H66" s="5">
-        <f>ROUND(F66*G66,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C67" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D67" s="16" t="inlineStr">
-        <is>
-          <t>Tesisat hidroforu — 0,3 m³/h, 30 mSS (3A)</t>
-        </is>
-      </c>
-      <c r="E67" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F67" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>19000</v>
-      </c>
-      <c r="H67" s="5">
-        <f>ROUND(F67*G67,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="14" customHeight="1">
-      <c r="A68" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D68" s="16" t="inlineStr">
-        <is>
-          <t>Modüler galvaniz su deposu — 3 ton (3A)</t>
-        </is>
-      </c>
-      <c r="E68" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F68" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>36000</v>
-      </c>
-      <c r="H68" s="5">
-        <f>ROUND(F68*G68,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C69" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D69" s="16" t="inlineStr">
-        <is>
-          <t>Yağmur suyu geri kazanım deposu — modüler galvaniz 10 ton, 1,08 x 1,08 x 2,66 m</t>
-        </is>
-      </c>
-      <c r="E69" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F69" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>88000</v>
-      </c>
-      <c r="H69" s="5">
-        <f>ROUND(F69*G69,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B70" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C70" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>Yağmur suyu geri kazanım donanımı — pislik tutucu ve emiş filtresi, akış yavaşlatıcı, taşkan sifonu (4 m³/h), tam otomatik kum filtresi DN160, su sayacı ve otomatik kontrol</t>
-        </is>
-      </c>
-      <c r="E70" s="19" t="inlineStr">
-        <is>
-          <t>tk</t>
-        </is>
-      </c>
-      <c r="F70" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>125000</v>
-      </c>
-      <c r="H70" s="5">
-        <f>ROUND(F70*G70,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C71" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D71" s="16" t="inlineStr">
-        <is>
-          <t>Bahçe sulama pompası — 0,5 m³/h, 40 mSS, 0,5 kW</t>
-        </is>
-      </c>
-      <c r="E71" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F71" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>16000</v>
-      </c>
-      <c r="H71" s="5">
-        <f>ROUND(F71*G71,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="21" t="n"/>
-      <c r="B72" s="21" t="n"/>
-      <c r="C72" s="21" t="n"/>
-      <c r="D72" s="22" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="21" t="n"/>
+      <c r="B66" s="21" t="n"/>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="22" t="inlineStr">
         <is>
           <t>HİBE DIŞI YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E72" s="21" t="n"/>
-      <c r="F72" s="21" t="n"/>
-      <c r="G72" s="21" t="n"/>
-      <c r="H72" s="9">
-        <f>SUM(H5:H71)</f>
+      <c r="E66" s="21" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="9">
+        <f>SUM(H5:H65)</f>
         <v/>
       </c>
     </row>
@@ -7497,7 +7275,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25586354.46</v>
+        <v>25237354.46</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7535,7 +7313,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6216052.75</v>
+        <v>5867052.75</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7592,7 +7370,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9811899.960000001</v>
+        <v>9462899.960000001</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7630,7 +7408,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>5117270.89</v>
+        <v>5047470.89</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H91</f>
+        <f>'A3.1.1 Yapım İşleri'!H101</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>35.100.2105</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>35.110.1102</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>35.140.3104</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>35.170.1602</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>35.170.1601</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
@@ -2129,14 +2129,14 @@
         <v>186</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>115.96</v>
+        <v>105.37</v>
       </c>
       <c r="H38" s="5">
         <f>ROUND(F38*G38,2)</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
+    <row r="39" ht="14" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2147,26 +2147,26 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>30.750.1502</t>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>35.750.3002 (montaj)</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F39" s="20" t="n">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>15595.61</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="H39" s="5">
         <f>ROUND(F39*G39,2)</f>
@@ -2186,31 +2186,31 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>426.72</v>
+        <v>14132.58</v>
       </c>
       <c r="H40" s="5">
         <f>ROUND(F40*G40,2)</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" ht="20" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2221,14 +2221,14 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
-        <is>
-          <t>30.740.1106</t>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>35.750.1502 (montaj)</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
         </is>
       </c>
       <c r="E41" s="19" t="inlineStr">
@@ -2240,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>467349.29</v>
+        <v>2131.5</v>
       </c>
       <c r="H41" s="5">
         <f>ROUND(F41*G41,2)</f>
@@ -2260,31 +2260,31 @@
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>79653.55</v>
+        <v>387.72</v>
       </c>
       <c r="H42" s="5">
         <f>ROUND(F42*G42,2)</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
+    <row r="43" ht="14" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2295,26 +2295,26 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>35.750.2001 (montaj)</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>502</v>
+        <v>16</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>199.42</v>
+        <v>63.21</v>
       </c>
       <c r="H43" s="5">
         <f>ROUND(F43*G43,2)</f>
@@ -2332,33 +2332,33 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C44" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>502</v>
+        <v>1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>38.72</v>
+        <v>423507</v>
       </c>
       <c r="H44" s="5">
         <f>ROUND(F44*G44,2)</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
+    <row r="45" ht="20" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2369,33 +2369,33 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>35.740.1106 (montaj)</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>361.2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>162.37</v>
+        <v>20872.19</v>
       </c>
       <c r="H45" s="5">
         <f>ROUND(F45*G45,2)</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46" ht="20" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2406,33 +2406,33 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>361.2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>21.3</v>
+        <v>72181.2</v>
       </c>
       <c r="H46" s="5">
         <f>ROUND(F46*G46,2)</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
+    <row r="47" ht="14" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2443,63 +2443,63 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>30.190.1304</t>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>35.740.5406 (montaj)</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabininin montajı</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>233.28</v>
+        <v>6208.76</v>
       </c>
       <c r="H47" s="5">
         <f>ROUND(F47*G47,2)</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
+    <row r="48" ht="20" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>1684.385</v>
+        <v>502</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>52.37</v>
+        <v>199.42</v>
       </c>
       <c r="H48" s="5">
         <f>ROUND(F48*G48,2)</f>
@@ -2509,34 +2509,34 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>15.150.1003</t>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>31.429</v>
+        <v>502</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2750.45</v>
+        <v>38.72</v>
       </c>
       <c r="H49" s="5">
         <f>ROUND(F49*G49,2)</f>
@@ -2546,71 +2546,71 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>278.34</v>
+        <v>361.2</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2960.45</v>
+        <v>162.37</v>
       </c>
       <c r="H50" s="5">
         <f>ROUND(F50*G50,2)</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="14" customHeight="1">
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>15.180.1003</t>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>551.26</v>
+        <v>361.2</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>863.8</v>
+        <v>21.3</v>
       </c>
       <c r="H51" s="5">
         <f>ROUND(F51*G51,2)</f>
@@ -2620,44 +2620,44 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>4.16</v>
+        <v>123</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>39045.24</v>
+        <v>233.28</v>
       </c>
       <c r="H52" s="5">
         <f>ROUND(F52*G52,2)</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
+    <row r="53" ht="14" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2667,34 +2667,34 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>7.288</v>
+        <v>1684.385</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>37532.19</v>
+        <v>52.37</v>
       </c>
       <c r="H53" s="5">
         <f>ROUND(F53*G53,2)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="14" customHeight="1">
+    <row r="54" ht="30" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
@@ -2704,34 +2704,34 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F54" s="20" t="n">
-        <v>3.637</v>
+        <v>31.429</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>36949.5</v>
+        <v>2750.45</v>
       </c>
       <c r="H54" s="5">
         <f>ROUND(F54*G54,2)</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
+    <row r="55" ht="30" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2741,34 +2741,34 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>44.048</v>
+        <v>278.34</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>72192.55</v>
+        <v>2960.45</v>
       </c>
       <c r="H55" s="5">
         <f>ROUND(F55*G55,2)</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
+    <row r="56" ht="14" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>674</v>
+        <v>551.26</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>147.67</v>
+        <v>863.8</v>
       </c>
       <c r="H56" s="5">
         <f>ROUND(F56*G56,2)</f>
@@ -2805,7 +2805,7 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -2815,24 +2815,24 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>507.91</v>
+        <v>4.16</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>929.28</v>
+        <v>39045.24</v>
       </c>
       <c r="H57" s="5">
         <f>ROUND(F57*G57,2)</f>
@@ -2842,7 +2842,7 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2852,34 +2852,34 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>49.85</v>
+        <v>7.288</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1777.52</v>
+        <v>37532.19</v>
       </c>
       <c r="H58" s="5">
         <f>ROUND(F58*G58,2)</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
+    <row r="59" ht="14" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,34 +2889,34 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>Nervürlü çelik hasırın yerine konulması</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F59" s="20" t="n">
-        <v>45</v>
+        <v>3.637</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>36949.5</v>
       </c>
       <c r="H59" s="5">
         <f>ROUND(F59*G59,2)</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="14" customHeight="1">
+    <row r="60" ht="20" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,24 +2926,24 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>319.2</v>
+        <v>44.048</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>227.85</v>
+        <v>72192.55</v>
       </c>
       <c r="H60" s="5">
         <f>ROUND(F60*G60,2)</f>
@@ -2953,7 +2953,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,34 +2963,34 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F61" s="20" t="n">
-        <v>51.2</v>
+        <v>674</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>174.22</v>
+        <v>147.67</v>
       </c>
       <c r="H61" s="5">
         <f>ROUND(F61*G61,2)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
+    <row r="62" ht="20" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
@@ -3014,20 +3014,20 @@
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>13.4</v>
+        <v>507.91</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>870.14</v>
+        <v>929.28</v>
       </c>
       <c r="H62" s="5">
         <f>ROUND(F62*G62,2)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
+    <row r="63" ht="20" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>5.67</v>
+        <v>49.85</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>2687.73</v>
+        <v>1777.52</v>
       </c>
       <c r="H63" s="5">
         <f>ROUND(F63*G63,2)</f>
@@ -3064,7 +3064,7 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>54.315</v>
+        <v>45</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>183.57</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H64" s="5">
         <f>ROUND(F64*G64,2)</f>
@@ -3101,7 +3101,7 @@
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3111,24 +3111,24 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>557.76</v>
+        <v>319.2</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>372.55</v>
+        <v>227.85</v>
       </c>
       <c r="H65" s="5">
         <f>ROUND(F65*G65,2)</f>
@@ -3138,7 +3138,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3148,34 +3148,34 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>647.76</v>
+        <v>51.2</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>381.49</v>
+        <v>174.22</v>
       </c>
       <c r="H66" s="5">
         <f>ROUND(F66*G66,2)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
+    <row r="67" ht="30" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3199,20 +3199,20 @@
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>557.76</v>
+        <v>13.4</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>324.27</v>
+        <v>870.14</v>
       </c>
       <c r="H67" s="5">
         <f>ROUND(F67*G67,2)</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
+    <row r="68" ht="30" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
@@ -3236,20 +3236,20 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>612.76</v>
+        <v>5.67</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>248.75</v>
+        <v>2687.73</v>
       </c>
       <c r="H68" s="5">
         <f>ROUND(F68*G68,2)</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="40" customHeight="1">
+    <row r="69" ht="20" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,34 +3259,34 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>60</v>
+        <v>54.315</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>701.48</v>
+        <v>183.57</v>
       </c>
       <c r="H69" s="5">
         <f>ROUND(F69*G69,2)</f>
         <v/>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
+    <row r="70" ht="14" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>25</v>
+        <v>557.76</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>330.7</v>
+        <v>372.55</v>
       </c>
       <c r="H70" s="5">
         <f>ROUND(F70*G70,2)</f>
@@ -3323,7 +3323,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -3333,24 +3333,24 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>30.100.2105</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>1</v>
+        <v>647.76</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>7084.16</v>
+        <v>381.49</v>
       </c>
       <c r="H71" s="5">
         <f>ROUND(F71*G71,2)</f>
@@ -3360,7 +3360,7 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>30.110.1102</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>1</v>
+        <v>557.76</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>3528.05</v>
+        <v>324.27</v>
       </c>
       <c r="H72" s="5">
         <f>ROUND(F72*G72,2)</f>
@@ -3397,7 +3397,7 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -3407,34 +3407,34 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>2</v>
+        <v>612.76</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1079.2</v>
+        <v>248.75</v>
       </c>
       <c r="H73" s="5">
         <f>ROUND(F73*G73,2)</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
+    <row r="74" ht="40" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
@@ -3444,34 +3444,34 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>30.140.3104</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>200</v>
+        <v>701.48</v>
       </c>
       <c r="H74" s="5">
         <f>ROUND(F74*G74,2)</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="30" customHeight="1">
+    <row r="75" ht="20" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -3481,24 +3481,24 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>30.170.1602</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1996.08</v>
+        <v>330.7</v>
       </c>
       <c r="H75" s="5">
         <f>ROUND(F75*G75,2)</f>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>30.170.1601</t>
+          <t>35.100.2105</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1370.96</v>
+        <v>7084.16</v>
       </c>
       <c r="H76" s="5">
         <f>ROUND(F76*G76,2)</f>
@@ -3555,24 +3555,24 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>30.160.6102</t>
+          <t>35.110.1102</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F77" s="20" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>29.06</v>
+        <v>3528.05</v>
       </c>
       <c r="H77" s="5">
         <f>ROUND(F77*G77,2)</f>
@@ -3592,24 +3592,24 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>30.150.1402</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F78" s="20" t="n">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>19.5</v>
+        <v>1079.2</v>
       </c>
       <c r="H78" s="5">
         <f>ROUND(F78*G78,2)</f>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>30.150.1401</t>
+          <t>35.140.3104</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3643,17 +3643,17 @@
         </is>
       </c>
       <c r="F79" s="20" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>12.22</v>
+        <v>200</v>
       </c>
       <c r="H79" s="5">
         <f>ROUND(F79*G79,2)</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1">
+    <row r="80" ht="30" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>30.140.1105</t>
+          <t>35.170.1602</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>157.05</v>
+        <v>1996.08</v>
       </c>
       <c r="H80" s="5">
         <f>ROUND(F80*G80,2)</f>
@@ -3703,24 +3703,24 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>30.750.3002</t>
+          <t>35.170.1601</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F81" s="20" t="n">
-        <v>186</v>
+        <v>2</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>115.96</v>
+        <v>1370.96</v>
       </c>
       <c r="H81" s="5">
         <f>ROUND(F81*G81,2)</f>
@@ -3740,24 +3740,24 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>30.750.1502</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F82" s="20" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>15595.61</v>
+        <v>29.06</v>
       </c>
       <c r="H82" s="5">
         <f>ROUND(F82*G82,2)</f>
@@ -3777,12 +3777,12 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>30.750.2001</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -3791,17 +3791,17 @@
         </is>
       </c>
       <c r="F83" s="20" t="n">
-        <v>16</v>
+        <v>2000</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>426.72</v>
+        <v>19.5</v>
       </c>
       <c r="H83" s="5">
         <f>ROUND(F83*G83,2)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="30" customHeight="1">
+    <row r="84" ht="20" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3814,24 +3814,24 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>30.740.1106</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F84" s="20" t="n">
-        <v>1</v>
+        <v>600</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>467349.29</v>
+        <v>12.22</v>
       </c>
       <c r="H84" s="5">
         <f>ROUND(F84*G84,2)</f>
@@ -3851,24 +3851,24 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>30.740.5406</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F85" s="20" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>79653.55</v>
+        <v>157.05</v>
       </c>
       <c r="H85" s="5">
         <f>ROUND(F85*G85,2)</f>
@@ -3888,31 +3888,31 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F86" s="20" t="n">
-        <v>502</v>
+        <v>186</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>199.42</v>
+        <v>105.37</v>
       </c>
       <c r="H86" s="5">
         <f>ROUND(F86*G86,2)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="30" customHeight="1">
+    <row r="87" ht="14" customHeight="1">
       <c r="A87" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3925,31 +3925,31 @@
       </c>
       <c r="C87" s="19" t="inlineStr">
         <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>35.750.3002 (montaj)</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F87" s="20" t="n">
-        <v>502</v>
+        <v>186</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>38.72</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="H87" s="5">
         <f>ROUND(F87*G87,2)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="30" customHeight="1">
+    <row r="88" ht="20" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3962,31 +3962,31 @@
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F88" s="20" t="n">
-        <v>361.2</v>
+        <v>1</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>162.37</v>
+        <v>14132.58</v>
       </c>
       <c r="H88" s="5">
         <f>ROUND(F88*G88,2)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="30" customHeight="1">
+    <row r="89" ht="20" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3999,24 +3999,24 @@
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>35.750.1502 (montaj)</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F89" s="20" t="n">
-        <v>361.2</v>
+        <v>1</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>21.3</v>
+        <v>2131.5</v>
       </c>
       <c r="H89" s="5">
         <f>ROUND(F89*G89,2)</f>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>30.190.1304</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr">
@@ -4050,30 +4050,400 @@
         </is>
       </c>
       <c r="F90" s="20" t="n">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>233.28</v>
+        <v>387.72</v>
       </c>
       <c r="H90" s="5">
         <f>ROUND(F90*G90,2)</f>
         <v/>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="21" t="n"/>
-      <c r="B91" s="21" t="n"/>
-      <c r="C91" s="21" t="n"/>
-      <c r="D91" s="22" t="inlineStr">
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t>35.750.2001 (montaj)</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="inlineStr">
+        <is>
+          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
+        </is>
+      </c>
+      <c r="E91" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F91" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>63.21</v>
+      </c>
+      <c r="H91" s="5">
+        <f>ROUND(F91*G91,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>35.740.1106</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E92" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F92" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>423507</v>
+      </c>
+      <c r="H92" s="5">
+        <f>ROUND(F92*G92,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>35.740.1106 (montaj)</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="inlineStr">
+        <is>
+          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
+        </is>
+      </c>
+      <c r="E93" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>20872.19</v>
+      </c>
+      <c r="H93" s="5">
+        <f>ROUND(F93*G93,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>35.740.5406</t>
+        </is>
+      </c>
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E94" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F94" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>72181.2</v>
+      </c>
+      <c r="H94" s="5">
+        <f>ROUND(F94*G94,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>35.740.5406 (montaj)</t>
+        </is>
+      </c>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>Jeneratör ses izolasyon kabininin montajı</t>
+        </is>
+      </c>
+      <c r="E95" s="19" t="inlineStr">
+        <is>
+          <t>ad</t>
+        </is>
+      </c>
+      <c r="F95" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>6208.76</v>
+      </c>
+      <c r="H95" s="5">
+        <f>ROUND(F95*G95,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E96" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F96" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>199.42</v>
+      </c>
+      <c r="H96" s="5">
+        <f>ROUND(F96*G96,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
+        </is>
+      </c>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F97" s="20" t="n">
+        <v>502</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="H97" s="5">
+        <f>ROUND(F97*G97,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F98" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>162.37</v>
+      </c>
+      <c r="H98" s="5">
+        <f>ROUND(F98*G98,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C99" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
+        </is>
+      </c>
+      <c r="D99" s="16" t="inlineStr">
+        <is>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+        </is>
+      </c>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F99" s="20" t="n">
+        <v>361.2</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H99" s="5">
+        <f>ROUND(F99*G99,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Elektrik tesisatı ve aydınlatma</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="inlineStr">
+        <is>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1304</t>
+        </is>
+      </c>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+        </is>
+      </c>
+      <c r="E100" s="19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="F100" s="20" t="n">
+        <v>123</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>233.28</v>
+      </c>
+      <c r="H100" s="5">
+        <f>ROUND(F100*G100,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="n"/>
+      <c r="B101" s="21" t="n"/>
+      <c r="C101" s="21" t="n"/>
+      <c r="D101" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E91" s="21" t="n"/>
-      <c r="F91" s="21" t="n"/>
-      <c r="G91" s="21" t="n"/>
-      <c r="H91" s="9">
-        <f>SUM(H5:H90)</f>
+      <c r="E101" s="21" t="n"/>
+      <c r="F101" s="21" t="n"/>
+      <c r="G101" s="21" t="n"/>
+      <c r="H101" s="9">
+        <f>SUM(H5:H100)</f>
         <v/>
       </c>
     </row>
@@ -6154,7 +6524,7 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>30.100.1104</t>
+          <t>35.100.1104</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
@@ -6191,7 +6561,7 @@
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>30.100.2106</t>
+          <t>35.100.2106</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
@@ -6228,7 +6598,7 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>30.135.3201</t>
+          <t>35.135.3201</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
@@ -6265,7 +6635,7 @@
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>30.110.1104</t>
+          <t>35.110.1104</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
@@ -6302,7 +6672,7 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>30.115.1003</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
@@ -6339,7 +6709,7 @@
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>30.140.3105</t>
+          <t>35.140.3105</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
@@ -6376,7 +6746,7 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>30.140.3101</t>
+          <t>35.140.3101</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
@@ -6413,7 +6783,7 @@
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>30.172.1706</t>
+          <t>35.172.1706</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
@@ -6450,7 +6820,7 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>30.170.4002</t>
+          <t>35.170.4002</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
@@ -6487,7 +6857,7 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>30.120.2016</t>
+          <t>35.120.2016</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
@@ -6524,7 +6894,7 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>30.120.2016</t>
+          <t>35.120.2016</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
@@ -7275,7 +7645,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25237354.46</v>
+        <v>25215904.14</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7294,7 +7664,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15774454.5</v>
+        <v>15753004.18</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7408,7 +7778,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>5047470.89</v>
+        <v>5043180.83</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H101</f>
+        <f>'A3.1.1 Yapım İşleri'!H91</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2129,14 +2129,14 @@
         <v>186</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>105.37</v>
+        <v>115.96</v>
       </c>
       <c r="H38" s="5">
         <f>ROUND(F38*G38,2)</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="14" customHeight="1">
+    <row r="39" ht="20" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2147,26 +2147,26 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>35.750.3002 (montaj)</t>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F39" s="20" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>77.54000000000001</v>
+        <v>15595.61</v>
       </c>
       <c r="H39" s="5">
         <f>ROUND(F39*G39,2)</f>
@@ -2186,31 +2186,31 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>35.750.1502</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>14132.58</v>
+        <v>426.72</v>
       </c>
       <c r="H40" s="5">
         <f>ROUND(F40*G40,2)</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2221,14 +2221,14 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>35.750.1502 (montaj)</t>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E41" s="19" t="inlineStr">
@@ -2240,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>2131.5</v>
+        <v>467349.29</v>
       </c>
       <c r="H41" s="5">
         <f>ROUND(F41*G41,2)</f>
@@ -2260,31 +2260,31 @@
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>35.750.2001</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>387.72</v>
+        <v>79653.55</v>
       </c>
       <c r="H42" s="5">
         <f>ROUND(F42*G42,2)</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
+    <row r="43" ht="20" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2295,26 +2295,26 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C43" s="19" t="inlineStr">
-        <is>
-          <t>35.750.2001 (montaj)</t>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>16</v>
+        <v>502</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>63.21</v>
+        <v>199.42</v>
       </c>
       <c r="H43" s="5">
         <f>ROUND(F43*G43,2)</f>
@@ -2332,33 +2332,33 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>35.740.1106</t>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>1</v>
+        <v>502</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>423507</v>
+        <v>38.72</v>
       </c>
       <c r="H44" s="5">
         <f>ROUND(F44*G44,2)</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="30" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2369,33 +2369,33 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>35.740.1106 (montaj)</t>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>20872.19</v>
+        <v>162.37</v>
       </c>
       <c r="H45" s="5">
         <f>ROUND(F45*G45,2)</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2406,33 +2406,33 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
-        <is>
-          <t>35.740.5406</t>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>72181.2</v>
+        <v>21.3</v>
       </c>
       <c r="H46" s="5">
         <f>ROUND(F46*G46,2)</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1">
+    <row r="47" ht="20" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2443,63 +2443,63 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>35.740.5406 (montaj)</t>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabininin montajı</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>6208.76</v>
+        <v>233.28</v>
       </c>
       <c r="H47" s="5">
         <f>ROUND(F47*G47,2)</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
+    <row r="48" ht="14" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>502</v>
+        <v>1684.385</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>199.42</v>
+        <v>52.37</v>
       </c>
       <c r="H48" s="5">
         <f>ROUND(F48*G48,2)</f>
@@ -2509,34 +2509,34 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C49" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>502</v>
+        <v>31.429</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>38.72</v>
+        <v>2750.45</v>
       </c>
       <c r="H49" s="5">
         <f>ROUND(F49*G49,2)</f>
@@ -2546,71 +2546,71 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>361.2</v>
+        <v>278.34</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>162.37</v>
+        <v>2960.45</v>
       </c>
       <c r="H50" s="5">
         <f>ROUND(F50*G50,2)</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" ht="14" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>361.2</v>
+        <v>551.26</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>21.3</v>
+        <v>863.8</v>
       </c>
       <c r="H51" s="5">
         <f>ROUND(F51*G51,2)</f>
@@ -2620,44 +2620,44 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>35.190.1304</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>123</v>
+        <v>4.16</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>233.28</v>
+        <v>39045.24</v>
       </c>
       <c r="H52" s="5">
         <f>ROUND(F52*G52,2)</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="14" customHeight="1">
+    <row r="53" ht="20" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2667,34 +2667,34 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>1684.385</v>
+        <v>7.288</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>52.37</v>
+        <v>37532.19</v>
       </c>
       <c r="H53" s="5">
         <f>ROUND(F53*G53,2)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
+    <row r="54" ht="14" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
@@ -2704,34 +2704,34 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Nervürlü çelik hasırın yerine konulması</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F54" s="20" t="n">
-        <v>31.429</v>
+        <v>3.637</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>2750.45</v>
+        <v>36949.5</v>
       </c>
       <c r="H54" s="5">
         <f>ROUND(F54*G54,2)</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
+    <row r="55" ht="20" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2741,34 +2741,34 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>278.34</v>
+        <v>44.048</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2960.45</v>
+        <v>72192.55</v>
       </c>
       <c r="H55" s="5">
         <f>ROUND(F55*G55,2)</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="14" customHeight="1">
+    <row r="56" ht="20" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>551.26</v>
+        <v>674</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>863.8</v>
+        <v>147.67</v>
       </c>
       <c r="H56" s="5">
         <f>ROUND(F56*G56,2)</f>
@@ -2805,7 +2805,7 @@
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
@@ -2815,24 +2815,24 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>4.16</v>
+        <v>507.91</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>39045.24</v>
+        <v>929.28</v>
       </c>
       <c r="H57" s="5">
         <f>ROUND(F57*G57,2)</f>
@@ -2842,7 +2842,7 @@
     <row r="58" ht="20" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2852,34 +2852,34 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>7.288</v>
+        <v>49.85</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>37532.19</v>
+        <v>1777.52</v>
       </c>
       <c r="H58" s="5">
         <f>ROUND(F58*G58,2)</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="14" customHeight="1">
+    <row r="59" ht="20" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,34 +2889,34 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F59" s="20" t="n">
-        <v>3.637</v>
+        <v>45</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>36949.5</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H59" s="5">
         <f>ROUND(F59*G59,2)</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
+    <row r="60" ht="14" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,24 +2926,24 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>44.048</v>
+        <v>319.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>72192.55</v>
+        <v>227.85</v>
       </c>
       <c r="H60" s="5">
         <f>ROUND(F60*G60,2)</f>
@@ -2953,7 +2953,7 @@
     <row r="61" ht="20" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,34 +2963,34 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F61" s="20" t="n">
-        <v>674</v>
+        <v>51.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>147.67</v>
+        <v>174.22</v>
       </c>
       <c r="H61" s="5">
         <f>ROUND(F61*G61,2)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
+    <row r="62" ht="30" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B62" s="17" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
@@ -3014,20 +3014,20 @@
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>507.91</v>
+        <v>13.4</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>929.28</v>
+        <v>870.14</v>
       </c>
       <c r="H62" s="5">
         <f>ROUND(F62*G62,2)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
+    <row r="63" ht="30" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>49.85</v>
+        <v>5.67</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>1777.52</v>
+        <v>2687.73</v>
       </c>
       <c r="H63" s="5">
         <f>ROUND(F63*G63,2)</f>
@@ -3064,7 +3064,7 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -3074,24 +3074,24 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>45</v>
+        <v>54.315</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>183.57</v>
       </c>
       <c r="H64" s="5">
         <f>ROUND(F64*G64,2)</f>
@@ -3101,7 +3101,7 @@
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3111,24 +3111,24 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>319.2</v>
+        <v>557.76</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>227.85</v>
+        <v>372.55</v>
       </c>
       <c r="H65" s="5">
         <f>ROUND(F65*G65,2)</f>
@@ -3138,7 +3138,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3148,34 +3148,34 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>51.2</v>
+        <v>647.76</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>174.22</v>
+        <v>381.49</v>
       </c>
       <c r="H66" s="5">
         <f>ROUND(F66*G66,2)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="30" customHeight="1">
+    <row r="67" ht="20" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3199,20 +3199,20 @@
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>13.4</v>
+        <v>557.76</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>870.14</v>
+        <v>324.27</v>
       </c>
       <c r="H67" s="5">
         <f>ROUND(F67*G67,2)</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
+    <row r="68" ht="20" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
@@ -3236,20 +3236,20 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>5.67</v>
+        <v>612.76</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>2687.73</v>
+        <v>248.75</v>
       </c>
       <c r="H68" s="5">
         <f>ROUND(F68*G68,2)</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
+    <row r="69" ht="40" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,34 +3259,34 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>54.315</v>
+        <v>60</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>183.57</v>
+        <v>701.48</v>
       </c>
       <c r="H69" s="5">
         <f>ROUND(F69*G69,2)</f>
         <v/>
       </c>
     </row>
-    <row r="70" ht="14" customHeight="1">
+    <row r="70" ht="20" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>557.76</v>
+        <v>25</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>372.55</v>
+        <v>330.7</v>
       </c>
       <c r="H70" s="5">
         <f>ROUND(F70*G70,2)</f>
@@ -3323,7 +3323,7 @@
     <row r="71" ht="20" customHeight="1">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
@@ -3333,24 +3333,24 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>35.100.2105</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>647.76</v>
+        <v>1</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>381.49</v>
+        <v>7084.16</v>
       </c>
       <c r="H71" s="5">
         <f>ROUND(F71*G71,2)</f>
@@ -3360,7 +3360,7 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>35.110.1102</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>557.76</v>
+        <v>1</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>324.27</v>
+        <v>3528.05</v>
       </c>
       <c r="H72" s="5">
         <f>ROUND(F72*G72,2)</f>
@@ -3397,7 +3397,7 @@
     <row r="73" ht="20" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B73" s="17" t="inlineStr">
@@ -3407,34 +3407,34 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>612.76</v>
+        <v>2</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>248.75</v>
+        <v>1079.2</v>
       </c>
       <c r="H73" s="5">
         <f>ROUND(F73*G73,2)</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="40" customHeight="1">
+    <row r="74" ht="20" customHeight="1">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B74" s="17" t="inlineStr">
@@ -3444,34 +3444,34 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>35.140.3104</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>701.48</v>
+        <v>200</v>
       </c>
       <c r="H74" s="5">
         <f>ROUND(F74*G74,2)</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
+    <row r="75" ht="30" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -3481,24 +3481,24 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>35.170.1602</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>330.7</v>
+        <v>1996.08</v>
       </c>
       <c r="H75" s="5">
         <f>ROUND(F75*G75,2)</f>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>35.100.2105</t>
+          <t>35.170.1601</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>7084.16</v>
+        <v>1370.96</v>
       </c>
       <c r="H76" s="5">
         <f>ROUND(F76*G76,2)</f>
@@ -3555,24 +3555,24 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>35.110.1102</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F77" s="20" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>3528.05</v>
+        <v>29.06</v>
       </c>
       <c r="H77" s="5">
         <f>ROUND(F77*G77,2)</f>
@@ -3592,24 +3592,24 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F78" s="20" t="n">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1079.2</v>
+        <v>19.5</v>
       </c>
       <c r="H78" s="5">
         <f>ROUND(F78*G78,2)</f>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>35.140.3104</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3643,17 +3643,17 @@
         </is>
       </c>
       <c r="F79" s="20" t="n">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>200</v>
+        <v>12.22</v>
       </c>
       <c r="H79" s="5">
         <f>ROUND(F79*G79,2)</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="30" customHeight="1">
+    <row r="80" ht="20" customHeight="1">
       <c r="A80" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>35.170.1602</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1996.08</v>
+        <v>157.05</v>
       </c>
       <c r="H80" s="5">
         <f>ROUND(F80*G80,2)</f>
@@ -3703,24 +3703,24 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>35.170.1601</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F81" s="20" t="n">
-        <v>2</v>
+        <v>186</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1370.96</v>
+        <v>115.96</v>
       </c>
       <c r="H81" s="5">
         <f>ROUND(F81*G81,2)</f>
@@ -3740,24 +3740,24 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>35.160.6102</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F82" s="20" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>29.06</v>
+        <v>15595.61</v>
       </c>
       <c r="H82" s="5">
         <f>ROUND(F82*G82,2)</f>
@@ -3777,12 +3777,12 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>35.150.1402</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
@@ -3791,17 +3791,17 @@
         </is>
       </c>
       <c r="F83" s="20" t="n">
-        <v>2000</v>
+        <v>16</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>19.5</v>
+        <v>426.72</v>
       </c>
       <c r="H83" s="5">
         <f>ROUND(F83*G83,2)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="20" customHeight="1">
+    <row r="84" ht="30" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3814,24 +3814,24 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>35.150.1401</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F84" s="20" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>12.22</v>
+        <v>467349.29</v>
       </c>
       <c r="H84" s="5">
         <f>ROUND(F84*G84,2)</f>
@@ -3851,24 +3851,24 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>35.140.1105</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F85" s="20" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>157.05</v>
+        <v>79653.55</v>
       </c>
       <c r="H85" s="5">
         <f>ROUND(F85*G85,2)</f>
@@ -3888,31 +3888,31 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>35.750.3002</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F86" s="20" t="n">
-        <v>186</v>
+        <v>502</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>105.37</v>
+        <v>199.42</v>
       </c>
       <c r="H86" s="5">
         <f>ROUND(F86*G86,2)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="14" customHeight="1">
+    <row r="87" ht="30" customHeight="1">
       <c r="A87" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3925,31 +3925,31 @@
       </c>
       <c r="C87" s="19" t="inlineStr">
         <is>
-          <t>35.750.3002 (montaj)</t>
+          <t>35.190.1100 (montaj)</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatının montajı — temel topraklaması</t>
+          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F87" s="20" t="n">
-        <v>186</v>
+        <v>502</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>77.54000000000001</v>
+        <v>38.72</v>
       </c>
       <c r="H87" s="5">
         <f>ROUND(F87*G87,2)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
+    <row r="88" ht="30" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3962,31 +3962,31 @@
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>35.750.1502</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F88" s="20" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>14132.58</v>
+        <v>162.37</v>
       </c>
       <c r="H88" s="5">
         <f>ROUND(F88*G88,2)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="20" customHeight="1">
+    <row r="89" ht="30" customHeight="1">
       <c r="A89" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3999,24 +3999,24 @@
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
-          <t>35.750.1502 (montaj)</t>
+          <t>35.190.1101 (montaj)</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucunun montajı — direk, taşıyıcı ve bağlantı elemanlarıyla yerine konulması</t>
+          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F89" s="20" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>2131.5</v>
+        <v>21.3</v>
       </c>
       <c r="H89" s="5">
         <f>ROUND(F89*G89,2)</f>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>35.750.2001</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr">
@@ -4050,400 +4050,30 @@
         </is>
       </c>
       <c r="F90" s="20" t="n">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>387.72</v>
+        <v>233.28</v>
       </c>
       <c r="H90" s="5">
         <f>ROUND(F90*G90,2)</f>
         <v/>
       </c>
     </row>
-    <row r="91" ht="14" customHeight="1">
-      <c r="A91" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B91" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C91" s="19" t="inlineStr">
-        <is>
-          <t>35.750.2001 (montaj)</t>
-        </is>
-      </c>
-      <c r="D91" s="16" t="inlineStr">
-        <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatının montajı</t>
-        </is>
-      </c>
-      <c r="E91" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F91" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>63.21</v>
-      </c>
-      <c r="H91" s="5">
-        <f>ROUND(F91*G91,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B92" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C92" s="18" t="inlineStr">
-        <is>
-          <t>35.740.1106</t>
-        </is>
-      </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E92" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F92" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>423507</v>
-      </c>
-      <c r="H92" s="5">
-        <f>ROUND(F92*G92,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B93" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C93" s="19" t="inlineStr">
-        <is>
-          <t>35.740.1106 (montaj)</t>
-        </is>
-      </c>
-      <c r="D93" s="16" t="inlineStr">
-        <is>
-          <t>Dizel elektrojen grubunun montajı — yerine konulması, bağlantıları ve işler hâlde teslimi</t>
-        </is>
-      </c>
-      <c r="E93" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F93" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>20872.19</v>
-      </c>
-      <c r="H93" s="5">
-        <f>ROUND(F93*G93,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B94" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="inlineStr">
-        <is>
-          <t>35.740.5406</t>
-        </is>
-      </c>
-      <c r="D94" s="16" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E94" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F94" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>72181.2</v>
-      </c>
-      <c r="H94" s="5">
-        <f>ROUND(F94*G94,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="14" customHeight="1">
-      <c r="A95" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B95" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C95" s="19" t="inlineStr">
-        <is>
-          <t>35.740.5406 (montaj)</t>
-        </is>
-      </c>
-      <c r="D95" s="16" t="inlineStr">
-        <is>
-          <t>Jeneratör ses izolasyon kabininin montajı</t>
-        </is>
-      </c>
-      <c r="E95" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F95" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>6208.76</v>
-      </c>
-      <c r="H95" s="5">
-        <f>ROUND(F95*G95,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B96" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C96" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1100</t>
-        </is>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E96" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F96" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>199.42</v>
-      </c>
-      <c r="H96" s="5">
-        <f>ROUND(F96*G96,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B97" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C97" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="D97" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="E97" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F97" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="H97" s="5">
-        <f>ROUND(F97*G97,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C98" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E98" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F98" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>162.37</v>
-      </c>
-      <c r="H98" s="5">
-        <f>ROUND(F98*G98,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C99" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="D99" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="E99" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F99" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H99" s="5">
-        <f>ROUND(F99*G99,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C100" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1304</t>
-        </is>
-      </c>
-      <c r="D100" s="16" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E100" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F100" s="20" t="n">
-        <v>123</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>233.28</v>
-      </c>
-      <c r="H100" s="5">
-        <f>ROUND(F100*G100,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="21" t="n"/>
-      <c r="B101" s="21" t="n"/>
-      <c r="C101" s="21" t="n"/>
-      <c r="D101" s="22" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="21" t="n"/>
+      <c r="B91" s="21" t="n"/>
+      <c r="C91" s="21" t="n"/>
+      <c r="D91" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E101" s="21" t="n"/>
-      <c r="F101" s="21" t="n"/>
-      <c r="G101" s="21" t="n"/>
-      <c r="H101" s="9">
-        <f>SUM(H5:H100)</f>
+      <c r="E91" s="21" t="n"/>
+      <c r="F91" s="21" t="n"/>
+      <c r="G91" s="21" t="n"/>
+      <c r="H91" s="9">
+        <f>SUM(H5:H90)</f>
         <v/>
       </c>
     </row>
@@ -7645,7 +7275,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25215904.14</v>
+        <v>25237354.46</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7664,7 +7294,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15753004.18</v>
+        <v>15774454.5</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7778,7 +7408,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>5043180.83</v>
+        <v>5047470.89</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>'A3.1.1 Yapım İşleri'!H91</f>
+        <f>'A3.1.1 Yapım İşleri'!H87</f>
         <v/>
       </c>
       <c r="C5" s="6">
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2332,14 +2332,14 @@
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C44" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
@@ -2348,17 +2348,17 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>502</v>
+        <v>361.2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>38.72</v>
+        <v>162.37</v>
       </c>
       <c r="H44" s="5">
         <f>ROUND(F44*G44,2)</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="30" customHeight="1">
+    <row r="45" ht="20" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -2371,108 +2371,108 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>35.190.1101</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F45" s="20" t="n">
-        <v>361.2</v>
+        <v>123</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>162.37</v>
+        <v>233.28</v>
       </c>
       <c r="H45" s="5">
         <f>ROUND(F45*G45,2)</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46" ht="14" customHeight="1">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Kazı, dolgu ve reglaj işleri</t>
         </is>
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
+          <t>Kümes B Blok</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>15.120.1001</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
+          <t>Makine ile yumuşak ve sert toprak kazılması</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>361.2</v>
+        <v>1684.385</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>21.3</v>
+        <v>52.37</v>
       </c>
       <c r="H46" s="5">
         <f>ROUND(F46*G46,2)</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
+          <t>Beton işleri</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>35.190.1304</t>
+          <t>15.150.1003</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>123</v>
+        <v>31.429</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>233.28</v>
+        <v>2750.45</v>
       </c>
       <c r="H47" s="5">
         <f>ROUND(F47*G47,2)</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Kazı, dolgu ve reglaj işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B48" s="17" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>15.120.1001</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Makine ile yumuşak ve sert toprak kazılması</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
@@ -2496,20 +2496,20 @@
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>1684.385</v>
+        <v>278.34</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>52.37</v>
+        <v>2960.45</v>
       </c>
       <c r="H48" s="5">
         <f>ROUND(F48*G48,2)</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
+    <row r="49" ht="14" customHeight="1">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Beton işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
@@ -2519,34 +2519,34 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>15.150.1003</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 16/20 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>31.429</v>
+        <v>551.26</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2750.45</v>
+        <v>863.8</v>
       </c>
       <c r="H49" s="5">
         <f>ROUND(F49*G49,2)</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="20" customHeight="1">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B50" s="17" t="inlineStr">
@@ -2556,34 +2556,34 @@
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>278.34</v>
+        <v>4.16</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>2960.45</v>
+        <v>39045.24</v>
       </c>
       <c r="H50" s="5">
         <f>ROUND(F50*G50,2)</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="14" customHeight="1">
+    <row r="51" ht="20" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
@@ -2593,31 +2593,31 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>551.26</v>
+        <v>7.288</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>863.8</v>
+        <v>37532.19</v>
       </c>
       <c r="H51" s="5">
         <f>ROUND(F51*G51,2)</f>
         <v/>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
+    <row r="52" ht="14" customHeight="1">
       <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Demir-inşaat işleri</t>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>15.160.1002</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Nervürlü çelik hasırın yerine konulması</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>4.16</v>
+        <v>3.637</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>39045.24</v>
+        <v>36949.5</v>
       </c>
       <c r="H52" s="5">
         <f>ROUND(F52*G52,2)</f>
@@ -2657,7 +2657,7 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B53" s="17" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.165.1003</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -2681,20 +2681,20 @@
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>7.288</v>
+        <v>44.048</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>37532.19</v>
+        <v>72192.55</v>
       </c>
       <c r="H53" s="5">
         <f>ROUND(F53*G53,2)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="14" customHeight="1">
+    <row r="54" ht="20" customHeight="1">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Çelik yapım-imalat işleri</t>
         </is>
       </c>
       <c r="B54" s="17" t="inlineStr">
@@ -2704,24 +2704,24 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>15.160.1002</t>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>Nervürlü çelik hasırın yerine konulması</t>
+          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E54" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F54" s="20" t="n">
-        <v>3.637</v>
+        <v>674</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>36949.5</v>
+        <v>147.67</v>
       </c>
       <c r="H54" s="5">
         <f>ROUND(F54*G54,2)</f>
@@ -2731,7 +2731,7 @@
     <row r="55" ht="20" customHeight="1">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
@@ -2741,24 +2741,24 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>15.165.1003</t>
+          <t>15.225.1010</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Her çeşit profil, çelik çubuk ve çelik saclarla karkas (çerçeve) inşaat yapılması, yerine tespiti (boya bedeli hariç)</t>
+          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F55" s="20" t="n">
-        <v>44.048</v>
+        <v>507.91</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>72192.55</v>
+        <v>929.28</v>
       </c>
       <c r="H55" s="5">
         <f>ROUND(F55*G55,2)</f>
@@ -2768,7 +2768,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Çelik yapım-imalat işleri</t>
+          <t>Tuğla ve duvar işleri</t>
         </is>
       </c>
       <c r="B56" s="17" t="inlineStr">
@@ -2778,24 +2778,24 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>15.550.1202</t>
+          <t>15.225.1410</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>Lama ve profil demirlerden çeşitli demir işleri yapılması ve yerine konulması</t>
+          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E56" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F56" s="20" t="n">
-        <v>674</v>
+        <v>49.85</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>147.67</v>
+        <v>1777.52</v>
       </c>
       <c r="H56" s="5">
         <f>ROUND(F56*G56,2)</f>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>15.225.1010</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
@@ -2829,20 +2829,20 @@
         </is>
       </c>
       <c r="F57" s="20" t="n">
-        <v>507.91</v>
+        <v>45</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>929.28</v>
+        <v>607.9299999999999</v>
       </c>
       <c r="H57" s="5">
         <f>ROUND(F57*G57,2)</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
+    <row r="58" ht="14" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B58" s="17" t="inlineStr">
@@ -2852,24 +2852,24 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>15.225.1410</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>20 cm kalınlığındaki teçhizatlı gazbeton lento temini ve yerine konulması</t>
+          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>49.85</v>
+        <v>319.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1777.52</v>
+        <v>227.85</v>
       </c>
       <c r="H58" s="5">
         <f>ROUND(F58*G58,2)</f>
@@ -2879,7 +2879,7 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Tuğla ve duvar işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B59" s="17" t="inlineStr">
@@ -2889,34 +2889,34 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>15.225.1004</t>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>10 cm kalınlığındaki teçhizatsız gazbeton duvar blokları ile duvar yapılması (gazbeton tutkalı ile)</t>
+          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F59" s="20" t="n">
-        <v>45</v>
+        <v>51.2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>607.9299999999999</v>
+        <v>174.22</v>
       </c>
       <c r="H59" s="5">
         <f>ROUND(F59*G59,2)</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="14" customHeight="1">
+    <row r="60" ht="30" customHeight="1">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B60" s="17" t="inlineStr">
@@ -2926,34 +2926,34 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0115</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu veya iniş borusu yapılması</t>
+          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F60" s="20" t="n">
-        <v>319.2</v>
+        <v>13.4</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>227.85</v>
+        <v>870.14</v>
       </c>
       <c r="H60" s="5">
         <f>ROUND(F60*G60,2)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
@@ -2963,31 +2963,31 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>15.315.1001</t>
+          <t>TKDK-0175</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Ø 70 mm çapında bir ucu muflu sert PVC yağmur borusu temini ve yerine tesbiti</t>
+          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F61" s="20" t="n">
-        <v>51.2</v>
+        <v>5.67</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>174.22</v>
+        <v>2687.73</v>
       </c>
       <c r="H61" s="5">
         <f>ROUND(F61*G61,2)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
+    <row r="62" ht="20" customHeight="1">
       <c r="A62" s="16" t="inlineStr">
         <is>
           <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
@@ -3000,34 +3000,34 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>15.550.1002</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu (üst 0,50 mm düz, alt 0,40 mm düz) fabrikasyon rulo boyama sistemi ile boyanmış galvaniz levhalar ile ısı yalıtımlı kapı yapılması</t>
+          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F62" s="20" t="n">
-        <v>13.4</v>
+        <v>54.315</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>870.14</v>
+        <v>183.57</v>
       </c>
       <c r="H62" s="5">
         <f>ROUND(F62*G62,2)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
+    <row r="63" ht="14" customHeight="1">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B63" s="17" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0175</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>PVC kaplamalı, iki yüzü odun lifinden yapılmış levhalarla (MDF) presli, kraft dolgulu iç kapı kanadı yapılması, yerinde takılması</t>
+          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F63" s="20" t="n">
-        <v>5.67</v>
+        <v>557.76</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>2687.73</v>
+        <v>372.55</v>
       </c>
       <c r="H63" s="5">
         <f>ROUND(F63*G63,2)</f>
@@ -3064,7 +3064,7 @@
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Doğramacılık işleri (Demir, Alüminyum, PVC, Kompozit)</t>
+          <t>Sıva, alçı, derz ve şap işleri</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -3074,34 +3074,34 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>15.550.1002</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>1,50 mm kalınlığında sıcak haddelenmiş sacdan bükme kapı kasası yapılması ve yerine konulması</t>
+          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
         </is>
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F64" s="20" t="n">
-        <v>54.315</v>
+        <v>647.76</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>183.57</v>
+        <v>381.49</v>
       </c>
       <c r="H64" s="5">
         <f>ROUND(F64*G64,2)</f>
         <v/>
       </c>
     </row>
-    <row r="65" ht="14" customHeight="1">
+    <row r="65" ht="20" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu harç ile kaba sıva yapılması</t>
+          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E65" s="19" t="inlineStr">
@@ -3128,7 +3128,7 @@
         <v>557.76</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>372.55</v>
+        <v>324.27</v>
       </c>
       <c r="H65" s="5">
         <f>ROUND(F65*G65,2)</f>
@@ -3138,7 +3138,7 @@
     <row r="66" ht="20" customHeight="1">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Sıva, alçı, derz ve şap işleri</t>
+          <t>Boya, badana ve cila işleri</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı harç ile kaba sıva yapılması (iç cephe)</t>
+          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
         </is>
       </c>
       <c r="E66" s="19" t="inlineStr">
@@ -3162,20 +3162,20 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>647.76</v>
+        <v>612.76</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>381.49</v>
+        <v>248.75</v>
       </c>
       <c r="H66" s="5">
         <f>ROUND(F66*G66,2)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
+    <row r="67" ht="40" customHeight="1">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>İnce yapı ve tamamlayıcı imalatlar</t>
         </is>
       </c>
       <c r="B67" s="17" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>TKDK-0177</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>Brüt beton, sıvalı veya eski boyalı yüzeylere astar uygulanarak silikon esaslı su bazlı dış cephe boyası yapılması</t>
+          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
         </is>
       </c>
       <c r="E67" s="19" t="inlineStr">
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="F67" s="20" t="n">
-        <v>557.76</v>
+        <v>60</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>324.27</v>
+        <v>701.48</v>
       </c>
       <c r="H67" s="5">
         <f>ROUND(F67*G67,2)</f>
@@ -3212,7 +3212,7 @@
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Boya, badana ve cila işleri</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
@@ -3222,34 +3222,34 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>Yeni sıva yüzeylere astar uygulanarak iki kat su bazlı plastik antibakteriyel iç cephe boyası yapılması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E68" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>612.76</v>
+        <v>25</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>248.75</v>
+        <v>330.7</v>
       </c>
       <c r="H68" s="5">
         <f>ROUND(F68*G68,2)</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="40" customHeight="1">
+    <row r="69" ht="20" customHeight="1">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>İnce yapı ve tamamlayıcı imalatlar</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
@@ -3259,24 +3259,24 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0177</t>
+          <t>35.100.2105</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
         <is>
-          <t>(25x70 - 25x75 - 40x80 cm) anma ebatlarında, her türlü desen ve yüzey özelliğinde, renkli duvar karosu ile 3 mm derz aralıklı döşeme, duvar ve cephe kaplaması yapılması (karo yapıştırıcısı ile)</t>
+          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E69" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F69" s="20" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>701.48</v>
+        <v>7084.16</v>
       </c>
       <c r="H69" s="5">
         <f>ROUND(F69*G69,2)</f>
@@ -3286,7 +3286,7 @@
     <row r="70" ht="20" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B70" s="17" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>35.110.1102</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E70" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F70" s="20" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>330.7</v>
+        <v>3528.05</v>
       </c>
       <c r="H70" s="5">
         <f>ROUND(F70*G70,2)</f>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>35.100.2105</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
         <is>
-          <t>Kümes dağıtım panosu (sıva üstü galvanizli sac tablo, 0,40-0,50 m²) (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E71" s="19" t="inlineStr">
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="F71" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>7084.16</v>
+        <v>1079.2</v>
       </c>
       <c r="H71" s="5">
         <f>ROUND(F71*G71,2)</f>
@@ -3370,31 +3370,31 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>35.110.1102</t>
+          <t>35.140.3104</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x100 A, Icu 35 kA — kümes besleme (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F72" s="20" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>3528.05</v>
+        <v>200</v>
       </c>
       <c r="H72" s="5">
         <f>ROUND(F72*G72,2)</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
+    <row r="73" ht="30" customHeight="1">
       <c r="A73" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.170.1602</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E73" s="19" t="inlineStr">
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="F73" s="20" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>1079.2</v>
+        <v>1996.08</v>
       </c>
       <c r="H73" s="5">
         <f>ROUND(F73*G73,2)</f>
@@ -3444,31 +3444,31 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>35.140.3104</t>
+          <t>35.170.1601</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile kolon hattı tesisi — 1x25 mm² (%25 müteahhit kârı dahil)</t>
+          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F74" s="20" t="n">
-        <v>300</v>
+        <v>2</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>200</v>
+        <v>1370.96</v>
       </c>
       <c r="H74" s="5">
         <f>ROUND(F74*G74,2)</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="30" customHeight="1">
+    <row r="75" ht="20" customHeight="1">
       <c r="A75" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3481,24 +3481,24 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>35.170.1602</t>
+          <t>35.160.6102</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 2700 lm — kümes genel aydınlatması (%25 müteahhit kârı dahil)</t>
+          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F75" s="20" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1996.08</v>
+        <v>29.06</v>
       </c>
       <c r="H75" s="5">
         <f>ROUND(F75*G75,2)</f>
@@ -3518,24 +3518,24 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>35.170.1601</t>
+          <t>35.150.1402</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>LED sıva üstü etanj armatür (polikarbon gövdeli), ışık akısı en az 1800 lm — servis bölümü (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F76" s="20" t="n">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1370.96</v>
+        <v>19.5</v>
       </c>
       <c r="H76" s="5">
         <f>ROUND(F76*G76,2)</f>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>35.160.6102</t>
+          <t>35.150.1401</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
         <is>
-          <t>Boş boru döşemesi — 25-32 mm PVC boru (%25 müteahhit kârı dahil)</t>
+          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E77" s="19" t="inlineStr">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="F77" s="20" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>29.06</v>
+        <v>12.22</v>
       </c>
       <c r="H77" s="5">
         <f>ROUND(F77*G77,2)</f>
@@ -3592,12 +3592,12 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>35.150.1402</t>
+          <t>35.140.1105</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x2,5 mm² ile tesisat (%25 müteahhit kârı dahil)</t>
+          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E78" s="19" t="inlineStr">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="F78" s="20" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>19.5</v>
+        <v>157.05</v>
       </c>
       <c r="H78" s="5">
         <f>ROUND(F78*G78,2)</f>
@@ -3629,12 +3629,12 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>35.150.1401</t>
+          <t>35.750.3002</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>Halojensiz H07Z tipi iletken 1x1,5 mm² ile kumanda tesisatı (%25 müteahhit kârı dahil)</t>
+          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E79" s="19" t="inlineStr">
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="F79" s="20" t="n">
-        <v>600</v>
+        <v>186</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>12.22</v>
+        <v>115.96</v>
       </c>
       <c r="H79" s="5">
         <f>ROUND(F79*G79,2)</f>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>35.140.1105</t>
+          <t>35.750.1502</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>Çıplak bakır tel 25 mm² — eşpotansiyel bara ve topraklama iletkeni (%25 müteahhit kârı dahil)</t>
+          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F80" s="20" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>157.05</v>
+        <v>15595.61</v>
       </c>
       <c r="H80" s="5">
         <f>ROUND(F80*G80,2)</f>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>35.750.3002</t>
+          <t>35.750.2001</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>Bina ihata iletkeni tesisatı — 30x3,5 mm galvanizli çelik lama (temel topraklaması) (%25 müteahhit kârı dahil)</t>
+          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
@@ -3717,17 +3717,17 @@
         </is>
       </c>
       <c r="F81" s="20" t="n">
-        <v>186</v>
+        <v>16</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>115.96</v>
+        <v>426.72</v>
       </c>
       <c r="H81" s="5">
         <f>ROUND(F81*G81,2)</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
+    <row r="82" ht="30" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3740,12 +3740,12 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>35.750.1502</t>
+          <t>35.740.1106</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>Aktif yakalama ucu, ortalama uyarım yolu DL = 30-40 m (%25 müteahhit kârı dahil)</t>
+          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
@@ -3757,7 +3757,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>15595.61</v>
+        <v>467349.29</v>
       </c>
       <c r="H82" s="5">
         <f>ROUND(F82*G82,2)</f>
@@ -3777,31 +3777,31 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>35.750.2001</t>
+          <t>35.740.5406</t>
         </is>
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>Çatı ihata ve indirme iletkeni tesisatı — 50 mm² elektrolitik bakır tel (%25 müteahhit kârı dahil)</t>
+          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F83" s="20" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>426.72</v>
+        <v>79653.55</v>
       </c>
       <c r="H83" s="5">
         <f>ROUND(F83*G83,2)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="30" customHeight="1">
+    <row r="84" ht="20" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3814,31 +3814,31 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>35.740.1106</t>
+          <t>35.190.1100</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>Dizel elektrojen grubu (jeneratör) 63 kVA / 50 kW — dizel motoru su veya hava ile soğuyan cinsten, 1500 d/dak (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F84" s="20" t="n">
-        <v>1</v>
+        <v>502</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>467349.29</v>
+        <v>199.42</v>
       </c>
       <c r="H84" s="5">
         <f>ROUND(F84*G84,2)</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1">
+    <row r="85" ht="30" customHeight="1">
       <c r="A85" s="16" t="inlineStr">
         <is>
           <t>Elektrik tesisatı ve aydınlatma</t>
@@ -3851,24 +3851,24 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>35.740.5406</t>
+          <t>35.190.1101</t>
         </is>
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>Jeneratör ses izolasyon kabini — 63 kVA (%25 müteahhit kârı dahil)</t>
+          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="F85" s="20" t="n">
-        <v>1</v>
+        <v>361.2</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>79653.55</v>
+        <v>162.37</v>
       </c>
       <c r="H85" s="5">
         <f>ROUND(F85*G85,2)</f>
@@ -3888,192 +3888,44 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>35.190.1100</t>
+          <t>35.190.1304</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>Kablo tava sistemleri — 200x60x1,0 mm sıcak daldırma galvanizli perfore kablo tavası (malzeme) (%25 müteahhit kârı dahil)</t>
+          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F86" s="20" t="n">
-        <v>502</v>
+        <v>123</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>199.42</v>
+        <v>233.28</v>
       </c>
       <c r="H86" s="5">
         <f>ROUND(F86*G86,2)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B87" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1100 (montaj)</t>
-        </is>
-      </c>
-      <c r="D87" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemlerinin montajı — askı ve konsollarla tavana veya duvara tespiti; ek parça, konsol, askı tiji, vida ve somun bedelleri dâhildir, ayrıca ödenmez</t>
-        </is>
-      </c>
-      <c r="E87" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F87" s="20" t="n">
-        <v>502</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="H87" s="5">
-        <f>ROUND(F87*G87,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B88" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C88" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1101</t>
-        </is>
-      </c>
-      <c r="D88" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacı — 35.190.1100 pozuna uygun özellikte, 1,0 mm sıcak daldırma galvanizli (malzeme) (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E88" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F88" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>162.37</v>
-      </c>
-      <c r="H88" s="5">
-        <f>ROUND(F88*G88,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B89" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="inlineStr">
-        <is>
-          <t>35.190.1101 (montaj)</t>
-        </is>
-      </c>
-      <c r="D89" s="16" t="inlineStr">
-        <is>
-          <t>Kablo tava sistemleri kapak sacının montajı — onaylı projesinde belirtilen kanalların kapatılması; her türlü işçilik ve malzeme dâhil, işler hâlde teslim</t>
-        </is>
-      </c>
-      <c r="E89" s="19" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="F89" s="20" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="H89" s="5">
-        <f>ROUND(F89*G89,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B90" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C90" s="18" t="inlineStr">
-        <is>
-          <t>35.190.1304</t>
-        </is>
-      </c>
-      <c r="D90" s="16" t="inlineStr">
-        <is>
-          <t>Sıva üstü PVC kablo kanalı — en az 100 x 35 mm, üç bölmeli (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E90" s="19" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="F90" s="20" t="n">
-        <v>123</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>233.28</v>
-      </c>
-      <c r="H90" s="5">
-        <f>ROUND(F90*G90,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="21" t="n"/>
-      <c r="B91" s="21" t="n"/>
-      <c r="C91" s="21" t="n"/>
-      <c r="D91" s="22" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="21" t="n"/>
+      <c r="B87" s="21" t="n"/>
+      <c r="C87" s="21" t="n"/>
+      <c r="D87" s="22" t="inlineStr">
         <is>
           <t>A3.1.1 YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E91" s="21" t="n"/>
-      <c r="F91" s="21" t="n"/>
-      <c r="G91" s="21" t="n"/>
-      <c r="H91" s="9">
-        <f>SUM(H5:H90)</f>
+      <c r="E87" s="21" t="n"/>
+      <c r="F87" s="21" t="n"/>
+      <c r="G87" s="21" t="n"/>
+      <c r="H87" s="9">
+        <f>SUM(H5:H86)</f>
         <v/>
       </c>
     </row>
@@ -7275,7 +7127,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25237354.46</v>
+        <v>25183092.46</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7294,7 +7146,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15774454.5</v>
+        <v>15720192.5</v>
       </c>
       <c r="C6" s="6">
         <f>B6/52.7585</f>
@@ -7408,7 +7260,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>5047470.89</v>
+        <v>5036618.49</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>'A3.4-EK Yapım'!H66</f>
+        <f>'A3.4-EK Yapım'!H64</f>
         <v/>
       </c>
       <c r="C12" s="6">
@@ -4443,7 +4443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>Foseptik</t>
+          <t>Yem Silosu Betonarme Kaideleri</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="F22" s="20" t="n">
-        <v>6.175</v>
+        <v>8.41</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>2960.45</v>
@@ -5179,37 +5179,37 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="14" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
+          <t>Gübre Çukuru</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E23" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F23" s="20" t="n">
-        <v>8.41</v>
+        <v>363.26</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>2960.45</v>
+        <v>863.8</v>
       </c>
       <c r="H23" s="5">
         <f>ROUND(F23*G23,2)</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>Gübre Çukuru</t>
+          <t>Ölü Atma Çukuru</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="F24" s="20" t="n">
-        <v>363.26</v>
+        <v>127.2</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>863.8</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Ölü Atma Çukuru</t>
+          <t>Su Deposu</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="F25" s="20" t="n">
-        <v>127.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>863.8</v>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>Su Deposu</t>
+          <t>Yağmur Suyu Deposu</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="F26" s="20" t="n">
-        <v>95.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>863.8</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Yağmur Suyu Deposu</t>
+          <t>Yem Silosu Betonarme Kaideleri</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="F27" s="20" t="n">
-        <v>79.8</v>
+        <v>11.6</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>863.8</v>
@@ -5364,74 +5364,74 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="14" customHeight="1">
+    <row r="28" ht="20" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>Foseptik</t>
+          <t>Gübre Çukuru</t>
         </is>
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E28" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F28" s="20" t="n">
-        <v>41.4</v>
+        <v>7.599</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>863.8</v>
+        <v>39045.24</v>
       </c>
       <c r="H28" s="5">
         <f>ROUND(F28*G28,2)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="14" customHeight="1">
+    <row r="29" ht="20" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
+          <t>Gübre Çukuru</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>15.160.1004</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E29" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F29" s="20" t="n">
-        <v>11.6</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>863.8</v>
+        <v>37532.19</v>
       </c>
       <c r="H29" s="5">
         <f>ROUND(F29*G29,2)</f>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>Gübre Çukuru</t>
+          <t>Ölü Atma Çukuru</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="F30" s="20" t="n">
-        <v>7.599</v>
+        <v>1.657</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>39045.24</v>
@@ -5483,17 +5483,17 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Gübre Çukuru</t>
+          <t>Yem Silosu Betonarme Kaideleri</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>15.160.1004</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Ø 14 - Ø 28 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E31" s="19" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="F31" s="20" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.757</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>37532.19</v>
+        <v>39045.24</v>
       </c>
       <c r="H31" s="5">
         <f>ROUND(F31*G31,2)</f>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Ölü Atma Çukuru</t>
+          <t>Su Deposu</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="F32" s="20" t="n">
-        <v>1.657</v>
+        <v>1.232</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>39045.24</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>Foseptik</t>
+          <t>Yağmur Suyu Deposu</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>0.587</v>
+        <v>1.23</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>39045.24</v>
@@ -5586,148 +5586,148 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>Yem Silosu Betonarme Kaideleri</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>TKDK-0042</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
         </is>
       </c>
       <c r="E34" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>0.757</v>
+        <v>1204.98</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>39045.24</v>
+        <v>1364.72</v>
       </c>
       <c r="H34" s="5">
         <f>ROUND(F34*G34,2)</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Çatı ve sundurma işleri</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>Su Deposu</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>TKDK-0042</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F35" s="20" t="n">
-        <v>1.232</v>
+        <v>1204.98</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>39045.24</v>
+        <v>1364.72</v>
       </c>
       <c r="H35" s="5">
         <f>ROUND(F35*G35,2)</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
+    <row r="36" ht="14" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Çevre düzenlemesi ve çit işleri</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>Yağmur Suyu Deposu</t>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>TKDK-0091</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
         </is>
       </c>
       <c r="E36" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F36" s="20" t="n">
-        <v>1.23</v>
+        <v>361.04</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>39045.24</v>
+        <v>940.84</v>
       </c>
       <c r="H36" s="5">
         <f>ROUND(F36*G36,2)</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="20" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0042</t>
+          <t>43.527.1001</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F37" s="20" t="n">
-        <v>1204.98</v>
+        <v>50</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1364.72</v>
+        <v>330.7</v>
       </c>
       <c r="H37" s="5">
         <f>ROUND(F37*G37,2)</f>
@@ -5737,34 +5737,34 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Çatı ve sundurma işleri</t>
+          <t>Betonarme işleri</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0042</t>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu (üst min. 0,40 mm, alt min. 0,30 mm) boyalı galvanizli sac levhalar ile ısı yalıtımlı çatı kaplaması yapılması</t>
+          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="F38" s="20" t="n">
-        <v>1204.98</v>
+        <v>1.566</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1364.72</v>
+        <v>2960.45</v>
       </c>
       <c r="H38" s="5">
         <f>ROUND(F38*G38,2)</f>
@@ -5774,7 +5774,7 @@
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Çevre düzenlemesi ve çit işleri</t>
+          <t>Kalıp, yapı iskelesi işleri</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
@@ -5784,24 +5784,24 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>15.180.1003</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Betonarme direkli galvanizli tel örgü çit yapılması (Tip-1)</t>
+          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
         </is>
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="F39" s="20" t="n">
-        <v>361.04</v>
+        <v>14.4</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>940.84</v>
+        <v>863.8</v>
       </c>
       <c r="H39" s="5">
         <f>ROUND(F39*G39,2)</f>
@@ -5811,7 +5811,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Demir-inşaat işleri</t>
         </is>
       </c>
       <c r="B40" s="17" t="inlineStr">
@@ -5821,34 +5821,34 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>43.527.1001</t>
+          <t>15.160.1003</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>Çapı 150 mm HDPE koruge boru döşenmesi (SN 8, lastik conta ve boru bedeli dahil)</t>
+          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
         </is>
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ton</t>
         </is>
       </c>
       <c r="F40" s="20" t="n">
-        <v>50</v>
+        <v>0.141</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>330.7</v>
+        <v>39045.24</v>
       </c>
       <c r="H40" s="5">
         <f>ROUND(F40*G40,2)</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" ht="14" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Betonarme işleri</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
@@ -5858,61 +5858,61 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.560.1003</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>Beton santralinde üretilen veya satın alınan ve beton pompasıyla basılan, C 25/30 basınç dayanım sınıfında, gri renkte, normal hazır beton dökülmesi (beton nakli dahil)</t>
+          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
         </is>
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F41" s="20" t="n">
-        <v>1.566</v>
+        <v>4</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>2960.45</v>
+        <v>3744.3</v>
       </c>
       <c r="H41" s="5">
         <f>ROUND(F41*G41,2)</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="14" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Kalıp, yapı iskelesi işleri</t>
+          <t>Kanalizasyon işleri</t>
         </is>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+          <t>Foseptik</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>15.180.1003</t>
+          <t>ÖP-15</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Plywood ile düz yüzeyli betonarme kalıbı yapılması</t>
+          <t>Prefabrik polietilen sızdırmaz foseptik tankı — 6 m³, rotasyon kalıplı, temini, yerine konulması ve giriş-çıkış bağlantılarının yapılması</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>14.4</v>
+        <v>1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>863.8</v>
+        <v>55000</v>
       </c>
       <c r="H42" s="5">
         <f>ROUND(F42*G42,2)</f>
@@ -5922,7 +5922,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Demir-inşaat işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
@@ -5932,34 +5932,34 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>15.160.1003</t>
+          <t>35.100.1104</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Ø 8 - Ø 12 mm nervürlü beton çelik çubuğu, çubukların kesilmesi, bükülmesi ve yerine konulması</t>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr">
         <is>
-          <t>ton</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F43" s="20" t="n">
-        <v>0.141</v>
+        <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>39045.24</v>
+        <v>31602.33</v>
       </c>
       <c r="H43" s="5">
         <f>ROUND(F43*G43,2)</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="14" customHeight="1">
+    <row r="44" ht="20" customHeight="1">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>15.560.1003</t>
+          <t>35.100.2106</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Betonarme kompozit rögar kapağı temini ve yerine konulması</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="F44" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>3744.3</v>
+        <v>8179.25</v>
       </c>
       <c r="H44" s="5">
         <f>ROUND(F44*G44,2)</f>
@@ -6006,12 +6006,12 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>35.100.1104</t>
+          <t>35.135.3201</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -6023,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>31602.33</v>
+        <v>1504.15</v>
       </c>
       <c r="H45" s="5">
         <f>ROUND(F45*G45,2)</f>
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>35.100.2106</t>
+          <t>35.110.1104</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
@@ -6060,7 +6060,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>8179.25</v>
+        <v>4753.16</v>
       </c>
       <c r="H46" s="5">
         <f>ROUND(F46*G46,2)</f>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>35.135.3201</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1504.15</v>
+        <v>1079.2</v>
       </c>
       <c r="H47" s="5">
         <f>ROUND(F47*G47,2)</f>
@@ -6117,24 +6117,24 @@
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>35.110.1104</t>
+          <t>35.140.3105</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F48" s="20" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>4753.16</v>
+        <v>277.15</v>
       </c>
       <c r="H48" s="5">
         <f>ROUND(F48*G48,2)</f>
@@ -6154,24 +6154,24 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.140.3101</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1079.2</v>
+        <v>51.25</v>
       </c>
       <c r="H49" s="5">
         <f>ROUND(F49*G49,2)</f>
@@ -6191,24 +6191,24 @@
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>35.140.3105</t>
+          <t>35.172.1706</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>277.15</v>
+        <v>6229.12</v>
       </c>
       <c r="H50" s="5">
         <f>ROUND(F50*G50,2)</f>
@@ -6228,24 +6228,24 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>35.140.3101</t>
+          <t>35.170.4002</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
+          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>51.25</v>
+        <v>7632.76</v>
       </c>
       <c r="H51" s="5">
         <f>ROUND(F51*G51,2)</f>
@@ -6260,17 +6260,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>35.172.1706</t>
+          <t>35.120.2016</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E52" s="19" t="inlineStr">
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="F52" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>6229.12</v>
+        <v>38544.21</v>
       </c>
       <c r="H52" s="5">
         <f>ROUND(F52*G52,2)</f>
@@ -6297,17 +6297,17 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>35.170.4002</t>
+          <t>35.120.2016</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E53" s="19" t="inlineStr">
@@ -6316,98 +6316,98 @@
         </is>
       </c>
       <c r="F53" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>7632.76</v>
+        <v>38544.21</v>
       </c>
       <c r="H53" s="5">
         <f>ROUND(F53*G53,2)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SIHHİ TESİSAT — keşif özetinde yer almaz; miktarlar onaylı sıhhi tesisat projesinden, birim fiyatlar piyasa araştırmasından (kitap fiyatı olmadığı için %16 tenzilat uygulanmaz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>Kümes A Blok</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
-        <is>
-          <t>35.120.2016</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E54" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F54" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>38544.21</v>
-      </c>
-      <c r="H54" s="5">
-        <f>ROUND(F54*G54,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C55" s="18" t="inlineStr">
-        <is>
-          <t>35.120.2016</t>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
+          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, 1/2" - 1 1/4" kolon ve kat tesisatı, küresel vanalar, boru askı ve kılıfları (kolon şemasına göre)</t>
         </is>
       </c>
       <c r="E55" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>tk</t>
         </is>
       </c>
       <c r="F55" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>38544.21</v>
+        <v>38000</v>
       </c>
       <c r="H55" s="5">
         <f>ROUND(F55*G55,2)</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>SIHHİ TESİSAT — keşif özetinde yer almaz; miktarlar onaylı sıhhi tesisat projesinden, birim fiyatlar piyasa araştırmasından (kitap fiyatı olmadığı için %16 tenzilat uygulanmaz)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Sıhhi tesisat</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>Kümes A Blok</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, kolon ve yatay hatlar, temizleme kapakları, yer süzgeçleri</t>
+        </is>
+      </c>
+      <c r="E56" s="19" t="inlineStr">
+        <is>
+          <t>tk</t>
+        </is>
+      </c>
+      <c r="F56" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H56" s="5">
+        <f>ROUND(F56*G56,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
       <c r="A57" s="17" t="inlineStr">
         <is>
           <t>Sıhhi tesisat</t>
@@ -6425,26 +6425,26 @@
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, 1/2" - 1 1/4" kolon ve kat tesisatı, küresel vanalar, boru askı ve kılıfları (kolon şemasına göre)</t>
+          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
         </is>
       </c>
       <c r="E57" s="19" t="inlineStr">
         <is>
-          <t>tk</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F57" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>38000</v>
+        <v>13000</v>
       </c>
       <c r="H57" s="5">
         <f>ROUND(F57*G57,2)</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
+    <row r="58" ht="30" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
         <is>
           <t>Sıhhi tesisat</t>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, kolon ve yatay hatlar, temizleme kapakları, yer süzgeçleri</t>
+          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, 1/2" - 1 1/4" kolon ve kat tesisatı, küresel vanalar, boru askı ve kılıfları (kolon şemasına göre)</t>
         </is>
       </c>
       <c r="E58" s="19" t="inlineStr">
@@ -6474,7 +6474,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>27000</v>
+        <v>38000</v>
       </c>
       <c r="H58" s="5">
         <f>ROUND(F58*G58,2)</f>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C59" s="19" t="inlineStr">
@@ -6499,26 +6499,26 @@
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
+          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, kolon ve yatay hatlar, temizleme kapakları, yer süzgeçleri</t>
         </is>
       </c>
       <c r="E59" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>tk</t>
         </is>
       </c>
       <c r="F59" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>13000</v>
+        <v>27000</v>
       </c>
       <c r="H59" s="5">
         <f>ROUND(F59*G59,2)</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
+    <row r="60" ht="20" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
         <is>
           <t>Sıhhi tesisat</t>
@@ -6536,26 +6536,26 @@
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, 1/2" - 1 1/4" kolon ve kat tesisatı, küresel vanalar, boru askı ve kılıfları (kolon şemasına göre)</t>
+          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
         </is>
       </c>
       <c r="E60" s="19" t="inlineStr">
         <is>
-          <t>tk</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F60" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>38000</v>
+        <v>13000</v>
       </c>
       <c r="H60" s="5">
         <f>ROUND(F60*G60,2)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
+    <row r="61" ht="14" customHeight="1">
       <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Sıhhi tesisat</t>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
         </is>
       </c>
       <c r="C61" s="19" t="inlineStr">
@@ -6573,26 +6573,26 @@
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, kolon ve yatay hatlar, temizleme kapakları, yer süzgeçleri</t>
+          <t>Şebeke su bağlantısı ve 2" su sayacı — temiz su girişi 80 YB</t>
         </is>
       </c>
       <c r="E61" s="19" t="inlineStr">
         <is>
-          <t>tk</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F61" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="H61" s="5">
         <f>ROUND(F61*G61,2)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
+    <row r="62" ht="14" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
         <is>
           <t>Sıhhi tesisat</t>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>Kümes B Blok</t>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
         </is>
       </c>
       <c r="C62" s="19" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
+          <t>Hidrofor — Q = 2 m³/h, P = 33-38 mSS</t>
         </is>
       </c>
       <c r="E62" s="19" t="inlineStr">
@@ -6622,7 +6622,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>13000</v>
+        <v>48000</v>
       </c>
       <c r="H62" s="5">
         <f>ROUND(F62*G62,2)</f>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>Şebeke su bağlantısı ve 2" su sayacı — temiz su girişi 80 YB</t>
+          <t>Tesisat hidroforu — 0,3 m³/h, 30 mSS (3A)</t>
         </is>
       </c>
       <c r="E63" s="19" t="inlineStr">
@@ -6659,107 +6659,33 @@
         <v>1</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>26000</v>
+        <v>19000</v>
       </c>
       <c r="H63" s="5">
         <f>ROUND(F63*G63,2)</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="14" customHeight="1">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C64" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>Hidrofor — Q = 2 m³/h, P = 33-38 mSS</t>
-        </is>
-      </c>
-      <c r="E64" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F64" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>48000</v>
-      </c>
-      <c r="H64" s="5">
-        <f>ROUND(F64*G64,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C65" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D65" s="16" t="inlineStr">
-        <is>
-          <t>Tesisat hidroforu — 0,3 m³/h, 30 mSS (3A)</t>
-        </is>
-      </c>
-      <c r="E65" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F65" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>19000</v>
-      </c>
-      <c r="H65" s="5">
-        <f>ROUND(F65*G65,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="21" t="n"/>
-      <c r="B66" s="21" t="n"/>
-      <c r="C66" s="21" t="n"/>
-      <c r="D66" s="22" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="21" t="n"/>
+      <c r="B64" s="21" t="n"/>
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="22" t="inlineStr">
         <is>
           <t>HİBE DIŞI YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E66" s="21" t="n"/>
-      <c r="F66" s="21" t="n"/>
-      <c r="G66" s="21" t="n"/>
-      <c r="H66" s="9">
-        <f>SUM(H5:H65)</f>
+      <c r="E64" s="21" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="n"/>
+      <c r="H64" s="9">
+        <f>SUM(H5:H63)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A54:H54"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7127,7 +7053,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25183092.46</v>
+        <v>25161130.8</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7165,7 +7091,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5867052.75</v>
+        <v>5845091.09</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7222,7 +7148,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9462899.960000001</v>
+        <v>9440938.300000001</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7260,7 +7186,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>5036618.49</v>
+        <v>5032226.16</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -5912,7 +5912,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>55000</v>
+        <v>76961.66</v>
       </c>
       <c r="H42" s="5">
         <f>ROUND(F42*G42,2)</f>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25161130.8</v>
+        <v>25183092.46</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7091,7 +7091,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5845091.09</v>
+        <v>5867052.75</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>9440938.300000001</v>
+        <v>9462899.960000001</v>
       </c>
       <c r="C10" s="10">
         <f>B10/52.7585</f>
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>5032226.16</v>
+        <v>5036618.49</v>
       </c>
       <c r="C12" s="6">
         <f>B12/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -511,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>'A3.4-EK Makine-Ekipman'!G13</f>
+        <f>'A3.4-EK Makine-Ekipman'!G15</f>
         <v/>
       </c>
       <c r="C13" s="6">
@@ -736,59 +736,40 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Hibe dışı kümes ısıtma sistemi</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>710000</v>
-      </c>
-      <c r="C14" s="6">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>UYGUN OLMAYAN HARCAMA (öz kaynak)</t>
+        </is>
+      </c>
+      <c r="B14" s="9">
+        <f>B12+B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="10">
         <f>B14/52.7585</f>
         <v/>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Ayrı lot; proforma ile beyan</t>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Tamamı öz kaynaktan karşılanır</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>UYGUN OLMAYAN HARCAMA (öz kaynak)</t>
-        </is>
-      </c>
-      <c r="B15" s="9">
-        <f>B12+B13+B14</f>
-        <v/>
-      </c>
-      <c r="C15" s="10">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>TOPLAM YATIRIM (KDV hariç)</t>
+        </is>
+      </c>
+      <c r="B15" s="13">
+        <f>B9+B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="14">
         <f>B15/52.7585</f>
         <v/>
       </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>Tamamı öz kaynaktan karşılanır</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>TOPLAM YATIRIM (KDV hariç)</t>
-        </is>
-      </c>
-      <c r="B16" s="13">
-        <f>B9+B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="14">
-        <f>B16/52.7585</f>
-        <v/>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>Uygun harcama + uygun olmayan harcama</t>
         </is>
@@ -4109,7 +4090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4189,14 +4170,14 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Yemleme sistemi — 3 hat, 243 m hat uzunluğu, 150 kg galvanizli yem deposu x 3, 0,55 kW yemlik motoru x 3, 35 cm çapında 324 plastik yemlik, 1,1 kW çift redüktörlü frenli otomatik kaldırma</t>
+          <t>Otomatik spiral yemlik sistemi (depo motor grubu ve kaldırma dâhil) — 3 hat, 243 m yemlik hattı, 150 kg galvanizli yem deposu x 3, 0,55 kW yemlik motoru x 3, 35 cm çapında 324 plastik yemlik, 1,1 kW çift redüktörlü frenli otomatik kaldırma</t>
         </is>
       </c>
       <c r="E5" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>250062.04</v>
+        <v>251748</v>
       </c>
       <c r="G5" s="5">
         <f>ROUND(E5*F5,2)</f>
@@ -4214,26 +4195,26 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>HZC-COM-004</t>
+          <t>HZC-WTR-005</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Kümes kontrol panosu — HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
+          <t>Otomatik nipel suluk sistemi (regülatör, hat sonu ve kaldırma dâhil) — Kümes başına 4 hat, toplam 312 m hat, 22 x 22 mm hat çapı, 1.560 metal 360° nipel suluk, 4 regülatör, 4 hat sonu, 0,75 kW çift redüktörlü frenli otomatik kaldırma</t>
         </is>
       </c>
       <c r="E6" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>262674.92</v>
+        <v>145080</v>
       </c>
       <c r="G6" s="5">
         <f>ROUND(E6*F6,2)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
@@ -4249,14 +4230,14 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>Tünel havalandırma fanı — 4 adet, 138 x 138 x 42 cm, 40.000 m³/h, 1,5 kW, galvanizli çelik kanat, ahtapot sistemli otomatik panjur</t>
+          <t>Havalandırma fanları — Kümes başına 4 adet tünel fanı, 138 x 138 x 42 cm, 40.000 m³/h, 1,5 kW, galvanizli çelik kanat, ahtapot sistemli otomatik panjur</t>
         </is>
       </c>
       <c r="E7" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>76982.48</v>
+        <v>76980</v>
       </c>
       <c r="G7" s="5">
         <f>ROUND(E7*F7,2)</f>
@@ -4274,26 +4255,26 @@
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>HZC-WTR-005</t>
+          <t>HZC-WNT-024</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Sulama sistemi — 4 hat, hat başına 312 m, 22 x 22 mm hat çapı, 1.560 metal 360° nipel suluk, 4 regülatör, 0,75 kW çift redüktörlü frenli otomatik kaldırma</t>
+          <t>Soğutma petek sistemi (açma-kapama ve petek panelleri dâhil) — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, kümes başına 2 x 15 m (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
         </is>
       </c>
       <c r="E8" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>145353.3</v>
+        <v>269280</v>
       </c>
       <c r="G8" s="5">
         <f>ROUND(E8*F8,2)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="20" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
@@ -4304,26 +4285,26 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>HZC-WNT-024</t>
+          <t>HZC-WNT-001</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Soğutma pedi sistemi — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, 2 x 15 m uzunluk (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
+          <t>Hava klape sistemi (açma-kapama hattı dâhil) — Kümes başına 30 adet 26 x 56 cm izolasyonlu plastik klape, 2 aktüatörlü açma-kapama, 161 m hat</t>
         </is>
       </c>
       <c r="E9" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>269272.63</v>
+        <v>40581.3</v>
       </c>
       <c r="G9" s="5">
         <f>ROUND(E9*F9,2)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="20" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
@@ -4334,19 +4315,19 @@
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>HZC-WNT-001</t>
+          <t>HZC-SLO-004</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Klape sistemi — 30 adet 26 x 56 cm izolasyonlu plastik klape, klape başına 1.750 m³/h (30 x 1.750 = 52.500 m³/h, mekanik projedeki 46.717 m³/h ihtiyacının üzerinde), 2 aktüatörlü açma-kapama, 161 m hat</t>
+          <t>17,67 ton silo ve aktarma grubu — Kümes başına 1 adet galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
         </is>
       </c>
       <c r="E10" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>40581.31</v>
+        <v>172995</v>
       </c>
       <c r="G10" s="5">
         <f>ROUND(E10*F10,2)</f>
@@ -4364,68 +4345,128 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>HZC-SLO-004</t>
+          <t>HZC-LGHT-01</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Yem silosu ve nakil sistemi — En az 17,77 ton galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
+          <t>Aydınlatma sistemi — Kümes başına 56 adet E27 / LED lamba (7-12 W), contalı duy, 266 m kablo</t>
         </is>
       </c>
       <c r="E11" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>172996.93</v>
+        <v>29260</v>
       </c>
       <c r="G11" s="5">
         <f>ROUND(E11*F11,2)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="14" customHeight="1">
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
         </is>
       </c>
       <c r="B12" s="19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HZC-HEA-004</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Montaj ve nakliye — Kümes montajı ve nakliye bedelleri</t>
+          <t>Isıtma sistemi — 350.000 kcal/h — Kümes başına 1 adet; en az 1.700 m² ısıtma alanı, 350.000 kcal/h, 5,5 kW fan motoru, 21.000 m³/h basma, üç geçişli kazan, 10 mm cehennemlik</t>
         </is>
       </c>
       <c r="E12" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>225000</v>
+        <v>472210</v>
       </c>
       <c r="G12" s="5">
         <f>ROUND(E12*F12,2)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="21" t="n"/>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="22" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>Makine ve ekipman alımı</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>HZC-COM-004</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Kümes otomasyonu ve bilgisayar sistemi — HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>263300</v>
+      </c>
+      <c r="G13" s="5">
+        <f>ROUND(E13*F13,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>Makine ve ekipman alımı</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>İşçilik ve nakliye — Kümes montajı ve nakliye bedelleri</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>225000</v>
+      </c>
+      <c r="G14" s="5">
+        <f>ROUND(E14*F14,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="n"/>
+      <c r="B15" s="21" t="n"/>
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>MAKİNE-EKİPMAN TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="21" t="n"/>
-      <c r="G13" s="9">
-        <f>SUM(G5:G12)</f>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="9">
+        <f>SUM(G5:G14)</f>
         <v/>
       </c>
     </row>
@@ -7000,7 +7041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -7053,7 +7094,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25183092.46</v>
+        <v>25480113.85</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7110,7 +7151,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>2885847.21</v>
+        <v>3892868.6</v>
       </c>
       <c r="C8" s="6">
         <f>B8/52.7585</f>
@@ -7123,76 +7164,57 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Hibe dışı kümes ısıtma sistemi — ayrı lot</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>710000</v>
-      </c>
-      <c r="C9" s="6">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>UYGUN OLMAYAN HARCAMA — toplam</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>9759921.35</v>
+      </c>
+      <c r="C9" s="10">
         <f>B9/52.7585</f>
         <v/>
       </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Proforma fatura</t>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Öz kaynak</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>UYGUN OLMAYAN HARCAMA — toplam</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>9462899.960000001</v>
-      </c>
-      <c r="C10" s="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>IPARD III broyler uygun harcama üst limiti (375.000,00 Avro) — uygun harcama limitin altındadır</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>19784437.5</v>
+      </c>
+      <c r="C10" s="6">
         <f>B10/52.7585</f>
         <v/>
       </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>Öz kaynak</t>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>Çağrı rehberi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>IPARD III broyler uygun harcama üst limiti (375.000,00 Avro) — uygun harcama limitin altındadır</t>
+          <t>KDV — IPARD'da uygun harcama değildir</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>19784437.5</v>
+        <v>5096022.77</v>
       </c>
       <c r="C11" s="6">
         <f>B11/52.7585</f>
         <v/>
       </c>
       <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>Çağrı rehberi</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>KDV — IPARD'da uygun harcama değildir</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>5036618.49</v>
-      </c>
-      <c r="C12" s="6">
-        <f>B12/52.7585</f>
-        <v/>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Öz kaynak</t>
         </is>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>'A3.4-EK Makine-Ekipman'!G15</f>
+        <f>'A3.4-EK Makine-Ekipman'!G14</f>
         <v/>
       </c>
       <c r="C13" s="6">
@@ -4090,7 +4090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4177,7 +4177,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>251748</v>
+        <v>250062.03</v>
       </c>
       <c r="G5" s="5">
         <f>ROUND(E5*F5,2)</f>
@@ -4207,7 +4207,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>145080</v>
+        <v>145353.3</v>
       </c>
       <c r="G6" s="5">
         <f>ROUND(E6*F6,2)</f>
@@ -4237,7 +4237,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>76980</v>
+        <v>76982.48</v>
       </c>
       <c r="G7" s="5">
         <f>ROUND(E7*F7,2)</f>
@@ -4260,14 +4260,14 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Soğutma petek sistemi (açma-kapama ve petek panelleri dâhil) — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, kümes başına 2 x 15 m (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
+          <t>Soğutma petekleri ve kapatma sistemi — Tüplü, dahili devridaimli; 15 cm kalınlık, 150 cm yükseklik, kümes başına 2 x 15 m (45 m² ped alanı), PVC çerçeve, XPS petek kapakları, 2 aktüatör, 2 adet 0,50 kW su pompası</t>
         </is>
       </c>
       <c r="E8" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>269280</v>
+        <v>269272.63</v>
       </c>
       <c r="G8" s="5">
         <f>ROUND(E8*F8,2)</f>
@@ -4320,21 +4320,21 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>17,67 ton silo ve aktarma grubu — Kümes başına 1 adet galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
+          <t>Silo ve aktarma sistemi — 17,67 ton — Kümes başına 1 adet galvaniz kaplama sac silo, helezonlu merdiven, 0,75 kW yem nakil motoru, 22 m PVC nakil hattı</t>
         </is>
       </c>
       <c r="E10" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>172995</v>
+        <v>172996.93</v>
       </c>
       <c r="G10" s="5">
         <f>ROUND(E10*F10,2)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
@@ -4345,19 +4345,19 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>HZC-LGHT-01</t>
+          <t>HZC-HEA-004</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Aydınlatma sistemi — Kümes başına 56 adet E27 / LED lamba (7-12 W), contalı duy, 266 m kablo</t>
+          <t>Isıtma sistemi — 350.000 kcal/h — Kümes başına 1 adet katı yakıtlı ısıtma kazanı, brandalı model, 171 m hava kanalı; en az 1.700 m² ısıtma alanı, 5,5 kW fan motoru, 21.000 m³/h basma, üç geçişli kazan</t>
         </is>
       </c>
       <c r="E11" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>29260</v>
+        <v>472211.18</v>
       </c>
       <c r="G11" s="5">
         <f>ROUND(E11*F11,2)</f>
@@ -4375,26 +4375,26 @@
       </c>
       <c r="C12" s="19" t="inlineStr">
         <is>
-          <t>HZC-HEA-004</t>
+          <t>HZC-COM-004</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Isıtma sistemi — 350.000 kcal/h — Kümes başına 1 adet; en az 1.700 m² ısıtma alanı, 350.000 kcal/h, 5,5 kW fan motoru, 21.000 m³/h basma, üç geçişli kazan, 10 mm cehennemlik</t>
+          <t>Kümes otomasyonu ve bilgisayar sistemi — HZC-70 işlemcili pano; 5 ısı, 1 nem, 1 basınç sensörü, ek alarm sensörü, sensör kablolamaları, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
         </is>
       </c>
       <c r="E12" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>472210</v>
+        <v>239684.38</v>
       </c>
       <c r="G12" s="5">
         <f>ROUND(E12*F12,2)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Makine ve ekipman alımı</t>
@@ -4405,68 +4405,38 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>HZC-COM-004</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>Kümes otomasyonu ve bilgisayar sistemi — HZC-70 işlemcili; 5 sıcaklık, 1 nem, 1 basınç ve 1 CO2 sensörü, alarm sistemi, uzaktan erişim, PLC kontrol, raporlama ve analiz</t>
+          <t>İşçilik ve nakliye — Kümes montajı ve nakliye bedelleri</t>
         </is>
       </c>
       <c r="E13" s="19" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>263300</v>
+        <v>225000</v>
       </c>
       <c r="G13" s="5">
         <f>ROUND(E13*F13,2)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Makine ve ekipman alımı</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>İşçilik ve nakliye — Kümes montajı ve nakliye bedelleri</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>225000</v>
-      </c>
-      <c r="G14" s="5">
-        <f>ROUND(E14*F14,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n"/>
-      <c r="B15" s="21" t="n"/>
-      <c r="C15" s="22" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>MAKİNE-EKİPMAN TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="9">
-        <f>SUM(G5:G14)</f>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="9">
+        <f>SUM(G5:G13)</f>
         <v/>
       </c>
     </row>
@@ -7094,7 +7064,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25480113.85</v>
+        <v>25371533.71</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7151,7 +7121,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3892868.6</v>
+        <v>3784288.46</v>
       </c>
       <c r="C8" s="6">
         <f>B8/52.7585</f>
@@ -7170,7 +7140,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>9759921.35</v>
+        <v>9651341.210000001</v>
       </c>
       <c r="C9" s="10">
         <f>B9/52.7585</f>
@@ -7208,7 +7178,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5096022.77</v>
+        <v>5074306.74</v>
       </c>
       <c r="C11" s="6">
         <f>B11/52.7585</f>

--- a/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
+++ b/belgeler/21_A3_UYGUN_HARCAMALAR.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>'A3.4-EK Yapım'!H64</f>
+        <f>'A3.4-EK Yapım'!H53</f>
         <v/>
       </c>
       <c r="C12" s="6">
@@ -4207,7 +4207,7 @@
         <v>2</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>145353.3</v>
+        <v>145353.32</v>
       </c>
       <c r="G6" s="5">
         <f>ROUND(E6*F6,2)</f>
@@ -4267,7 +4267,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>269272.63</v>
+        <v>269272.64</v>
       </c>
       <c r="G8" s="5">
         <f>ROUND(E8*F8,2)</f>
@@ -4327,7 +4327,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>172996.93</v>
+        <v>172996.92</v>
       </c>
       <c r="G10" s="5">
         <f>ROUND(E10*F10,2)</f>
@@ -4387,7 +4387,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>239684.38</v>
+        <v>239684.37</v>
       </c>
       <c r="G12" s="5">
         <f>ROUND(E12*F12,2)</f>
@@ -4454,7 +4454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4477,7 +4477,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Kümes A ve B blokları dışındaki yapılar ile bu iki bloktan hibe kapsamı dışına çıkarılan pozlar. Bu imalatlar yapılmaya devam eder; teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir ve tamamı öz kaynaktan karşılanır. Birim fiyatlar, hibe kapsamındaki işlerle aynı esasa göre kurulmuştur: ÇŞB 2026 ve TKDK 17.02.2026 kitap fiyatlarına %16 tenzilat uygulanmıştır. Sayfanın sonundaki SIHHİ TESİSAT bölümü keşif özetinde yer almaz: miktarları onaylı sıhhi tesisat projesinden, birim fiyatları piyasa araştırmasından gelir; kitap fiyatı olmadığı için o kalemlere tenzilat uygulanmaz. Bu sayfa 36 numaralı proforma ile kuruşu kuruşuna aynıdır.</t>
+          <t>Kümes A ve B blokları dışındaki yapılar ile bu iki bloktan hibe kapsamı dışına çıkarılan pozlar. Bu imalatlar yapılmaya devam eder; teklif alma usulüne tabi değildir, proforma fatura ile beyan edilir ve tamamı öz kaynaktan karşılanır. Birim fiyatlar, hibe kapsamındaki işlerle aynı esasa göre kurulmuştur: ÇŞB 2026 ve TKDK 17.02.2026 kitap fiyatlarına %16 tenzilat uygulanmıştır. Bu sayfa 36 numaralı proforma ile ve TKDK Online Başvuru Sistemine girilen uygun olmayan yapım işleri listesiyle kuruşu kuruşuna aynıdır.</t>
         </is>
       </c>
     </row>
@@ -5893,25 +5893,25 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="20" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Kanalizasyon işleri</t>
+          <t>Elektrik tesisatı ve aydınlatma</t>
         </is>
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>Foseptik</t>
+          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>ÖP-15</t>
+          <t>35.100.1104</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Prefabrik polietilen sızdırmaz foseptik tankı — 6 m³, rotasyon kalıplı, temini, yerine konulması ve giriş-çıkış bağlantılarının yapılması</t>
+          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E42" s="19" t="inlineStr">
@@ -5923,7 +5923,7 @@
         <v>1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>76961.66</v>
+        <v>31602.33</v>
       </c>
       <c r="H42" s="5">
         <f>ROUND(F42*G42,2)</f>
@@ -5943,12 +5943,12 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>35.100.1104</t>
+          <t>35.100.2106</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu (dikili tip galvanizli sac, en az 700 mm en, 400 mm derinlik) (%25 müteahhit kârı dahil)</t>
+          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr">
@@ -5960,7 +5960,7 @@
         <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>31602.33</v>
+        <v>8179.25</v>
       </c>
       <c r="H43" s="5">
         <f>ROUND(F43*G43,2)</f>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>35.100.2106</t>
+          <t>35.135.3201</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Sayaç panosu (sıva üstü galvanizli sac tablo, 0,50-0,60 m²) (%25 müteahhit kârı dahil)</t>
+          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E44" s="19" t="inlineStr">
@@ -5997,7 +5997,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>8179.25</v>
+        <v>1504.15</v>
       </c>
       <c r="H44" s="5">
         <f>ROUND(F44*G44,2)</f>
@@ -6017,12 +6017,12 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>35.135.3201</t>
+          <t>35.110.1104</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Üç fazlı zaman tarifeli elektronik aktif sayaç, en az 5(100) A, 3x230/400 V (%25 müteahhit kârı dahil)</t>
+          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E45" s="19" t="inlineStr">
@@ -6034,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>1504.15</v>
+        <v>4753.16</v>
       </c>
       <c r="H45" s="5">
         <f>ROUND(F45*G45,2)</f>
@@ -6054,12 +6054,12 @@
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>35.110.1104</t>
+          <t>35.115.1003</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>Termik-manyetik kompakt şalter 3x160 A, Icu 35 kA — ana giriş (%25 müteahhit kârı dahil)</t>
+          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E46" s="19" t="inlineStr">
@@ -6068,10 +6068,10 @@
         </is>
       </c>
       <c r="F46" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>4753.16</v>
+        <v>1079.2</v>
       </c>
       <c r="H46" s="5">
         <f>ROUND(F46*G46,2)</f>
@@ -6091,24 +6091,24 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>35.115.1003</t>
+          <t>35.140.3105</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>Kaçak akım koruma şalteri 2x63 A, 30 mA (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E47" s="19" t="inlineStr">
         <is>
-          <t>ad</t>
+          <t>m</t>
         </is>
       </c>
       <c r="F47" s="20" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1079.2</v>
+        <v>277.15</v>
       </c>
       <c r="H47" s="5">
         <f>ROUND(F47*G47,2)</f>
@@ -6128,12 +6128,12 @@
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>35.140.3105</t>
+          <t>35.140.3101</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x35 mm² (%25 müteahhit kârı dahil)</t>
+          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E48" s="19" t="inlineStr">
@@ -6145,7 +6145,7 @@
         <v>50</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>277.15</v>
+        <v>51.25</v>
       </c>
       <c r="H48" s="5">
         <f>ROUND(F48*G48,2)</f>
@@ -6165,24 +6165,24 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>35.140.3101</t>
+          <t>35.172.1706</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>YVV (NYY) 1 kV yeraltı kablosu ile besleme hattı tesisi — 1x6 mm² (%25 müteahhit kârı dahil)</t>
+          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ad</t>
         </is>
       </c>
       <c r="F49" s="20" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>51.25</v>
+        <v>6229.12</v>
       </c>
       <c r="H49" s="5">
         <f>ROUND(F49*G49,2)</f>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>35.172.1706</t>
+          <t>35.170.4002</t>
         </is>
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Aydınlatma direği — taban çapı en az 80 mm, yükseklik en az 4,00 m (%25 müteahhit kârı dahil)</t>
+          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E50" s="19" t="inlineStr">
@@ -6219,7 +6219,7 @@
         <v>4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>6229.12</v>
+        <v>7632.76</v>
       </c>
       <c r="H50" s="5">
         <f>ROUND(F50*G50,2)</f>
@@ -6234,17 +6234,17 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
+          <t>Kümes A Blok</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>35.170.4002</t>
+          <t>35.120.2016</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>LED projektör, ışık akısı en az 5100 lm (%25 müteahhit kârı dahil)</t>
+          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
         </is>
       </c>
       <c r="E51" s="19" t="inlineStr">
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>7632.76</v>
+        <v>38544.21</v>
       </c>
       <c r="H51" s="5">
         <f>ROUND(F51*G51,2)</f>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>Kümes A Blok</t>
+          <t>Kümes B Blok</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
@@ -6300,403 +6300,25 @@
         <v/>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>Elektrik tesisatı ve aydınlatma</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>35.120.2016</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>Otomatik transfer şalteri 4 x 200 A (%25 müteahhit kârı dahil)</t>
-        </is>
-      </c>
-      <c r="E53" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F53" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>38544.21</v>
-      </c>
-      <c r="H53" s="5">
-        <f>ROUND(F53*G53,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>SIHHİ TESİSAT — keşif özetinde yer almaz; miktarlar onaylı sıhhi tesisat projesinden, birim fiyatlar piyasa araştırmasından (kitap fiyatı olmadığı için %16 tenzilat uygulanmaz)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B55" s="17" t="inlineStr">
-        <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, 1/2" - 1 1/4" kolon ve kat tesisatı, küresel vanalar, boru askı ve kılıfları (kolon şemasına göre)</t>
-        </is>
-      </c>
-      <c r="E55" s="19" t="inlineStr">
-        <is>
-          <t>tk</t>
-        </is>
-      </c>
-      <c r="F55" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H55" s="5">
-        <f>ROUND(F55*G55,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C56" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, kolon ve yatay hatlar, temizleme kapakları, yer süzgeçleri</t>
-        </is>
-      </c>
-      <c r="E56" s="19" t="inlineStr">
-        <is>
-          <t>tk</t>
-        </is>
-      </c>
-      <c r="F56" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>27000</v>
-      </c>
-      <c r="H56" s="5">
-        <f>ROUND(F56*G56,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>Kümes A Blok</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr">
-        <is>
-          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
-        </is>
-      </c>
-      <c r="E57" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F57" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="H57" s="5">
-        <f>ROUND(F57*G57,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, 1/2" - 1 1/4" kolon ve kat tesisatı, küresel vanalar, boru askı ve kılıfları (kolon şemasına göre)</t>
-        </is>
-      </c>
-      <c r="E58" s="19" t="inlineStr">
-        <is>
-          <t>tk</t>
-        </is>
-      </c>
-      <c r="F58" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>38000</v>
-      </c>
-      <c r="H58" s="5">
-        <f>ROUND(F58*G58,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C59" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="inlineStr">
-        <is>
-          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, kolon ve yatay hatlar, temizleme kapakları, yer süzgeçleri</t>
-        </is>
-      </c>
-      <c r="E59" s="19" t="inlineStr">
-        <is>
-          <t>tk</t>
-        </is>
-      </c>
-      <c r="F59" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>27000</v>
-      </c>
-      <c r="H59" s="5">
-        <f>ROUND(F59*G59,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>Kümes B Blok</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <t>Termosifon — sıcak su üretimi (proje raporu: sıcak su hatları termosifon vasıtasıyla)</t>
-        </is>
-      </c>
-      <c r="E60" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F60" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>13000</v>
-      </c>
-      <c r="H60" s="5">
-        <f>ROUND(F60*G60,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="14" customHeight="1">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D61" s="16" t="inlineStr">
-        <is>
-          <t>Şebeke su bağlantısı ve 2" su sayacı — temiz su girişi 80 YB</t>
-        </is>
-      </c>
-      <c r="E61" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F61" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>26000</v>
-      </c>
-      <c r="H61" s="5">
-        <f>ROUND(F61*G61,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="14" customHeight="1">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C62" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>Hidrofor — Q = 2 m³/h, P = 33-38 mSS</t>
-        </is>
-      </c>
-      <c r="E62" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F62" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>48000</v>
-      </c>
-      <c r="H62" s="5">
-        <f>ROUND(F62*G62,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="14" customHeight="1">
-      <c r="A63" s="17" t="inlineStr">
-        <is>
-          <t>Sıhhi tesisat</t>
-        </is>
-      </c>
-      <c r="B63" s="17" t="inlineStr">
-        <is>
-          <t>Çevre Düzenlemesi ve Saha Altyapısı</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>Tesisat hidroforu — 0,3 m³/h, 30 mSS (3A)</t>
-        </is>
-      </c>
-      <c r="E63" s="19" t="inlineStr">
-        <is>
-          <t>ad</t>
-        </is>
-      </c>
-      <c r="F63" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>19000</v>
-      </c>
-      <c r="H63" s="5">
-        <f>ROUND(F63*G63,2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="21" t="n"/>
-      <c r="B64" s="21" t="n"/>
-      <c r="C64" s="21" t="n"/>
-      <c r="D64" s="22" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="21" t="n"/>
+      <c r="B53" s="21" t="n"/>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="22" t="inlineStr">
         <is>
           <t>HİBE DIŞI YAPIM İŞLERİ TOPLAMI (KDV hariç)</t>
         </is>
       </c>
-      <c r="E64" s="21" t="n"/>
-      <c r="F64" s="21" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="9">
-        <f>SUM(H5:H63)</f>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="9">
+        <f>SUM(H5:H52)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A54:H54"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7064,7 +6686,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>25371533.71</v>
+        <v>25045572.07</v>
       </c>
       <c r="C5" s="6">
         <f>B5/52.7585</f>
@@ -7102,7 +6724,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>5867052.75</v>
+        <v>5541091.09</v>
       </c>
       <c r="C7" s="6">
         <f>B7/52.7585</f>
@@ -7121,7 +6743,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3784288.46</v>
+        <v>3784288.48</v>
       </c>
       <c r="C8" s="6">
         <f>B8/52.7585</f>
@@ -7140,7 +6762,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>9651341.210000001</v>
+        <v>9325379.57</v>
       </c>
       <c r="C9" s="10">
         <f>B9/52.7585</f>
@@ -7178,7 +6800,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5074306.74</v>
+        <v>5009114.41</v>
       </c>
       <c r="C11" s="6">
         <f>B11/52.7585</f>
